--- a/workspaces/nasdaq_hourly_24hrs/rsi/rsi_spread_7_14.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/rsi/rsi_spread_7_14.xlsx
@@ -618,739 +618,739 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -37.92</t>
+          <t>X ≈ -37.91</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>19</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>4.193126968101694</v>
+        <v>4.226209526959579</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>3.859855171997637</v>
+        <v>3.893343474652852</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>7.66165626163265</v>
+        <v>7.696851742778932</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>6.952500686677915</v>
+        <v>6.990745649666486</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-9.108290407171253</v>
+        <v>-9.045634893462214</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>6.778813031409797</v>
+        <v>6.8461865385094</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.7756027163798223</v>
+        <v>0.8420719838848427</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.4990173204370549</v>
+        <v>0.5654302351507994</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.5409560217801612</v>
+        <v>0.6073595151389384</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-5.470652782859226</v>
+        <v>-5.403343388466737</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-15.68399825578253</v>
+        <v>-15.61701321890901</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-10.72243400625525</v>
+        <v>-10.65505837107495</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-11.84671337833506</v>
+        <v>-11.7779922980207</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-6.823282177117825</v>
+        <v>-6.754241245000259</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-7.482498893767215</v>
+        <v>-7.412650609473346</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-6.89127342438254</v>
+        <v>-6.822070339617667</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-12.27943606127465</v>
+        <v>-12.21004618977633</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-7.134068674564006</v>
+        <v>-7.064499842213699</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-12.17555808697936</v>
+        <v>-12.10620604747096</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-6.73560318594977</v>
+        <v>-6.666415185831099</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-7.280280805742976</v>
+        <v>-7.210416151754089</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-7.358301323069469</v>
+        <v>-7.288303726744758</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-7.085756950553773</v>
+        <v>-7.016035537932204</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-7.163742690058484</v>
+        <v>-7.093888342351207</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -35.25</t>
+          <t>X ≈ -35.23</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>35</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.6076719008081355</v>
+        <v>0.6407228513376921</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.2733463515211341</v>
+        <v>0.3068044247806796</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-1.157590596843761</v>
+        <v>-1.122461717048061</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.9731774301164506</v>
+        <v>1.00960460860307</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>3.451466816683578</v>
+        <v>3.517959020725783</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.7959403803547289</v>
+        <v>0.8614957356852102</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>2.86993598382282</v>
+        <v>2.937053623758729</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>5.437307501700147</v>
+        <v>5.503744344114359</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.2075537888245407</v>
+        <v>-0.1411593281119465</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-6.668186700850065</v>
+        <v>-6.600889116479422</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-12.08820665674033</v>
+        <v>-12.02121117273575</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-9.523175349539081</v>
+        <v>-9.455800003178403</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-7.799482690898166</v>
+        <v>-7.730750513265448</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-8.02230384830105</v>
+        <v>-7.953271633149896</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-2.983221188011356</v>
+        <v>-2.913361910400312</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-2.390691888018523</v>
+        <v>-2.321478931356431</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-11.07857178935905</v>
+        <v>-11.00918225882914</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-14.0385412986582</v>
+        <v>-13.96899038418067</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-5.26848406178437</v>
+        <v>-5.19912171337625</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-7.937018796329276</v>
+        <v>-7.867834278645411</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-11.33662137135831</v>
+        <v>-11.26676252881605</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-8.560506384310884</v>
+        <v>-8.490510553421622</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-8.288364650441395</v>
+        <v>-8.218644115629488</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>0.2046783625730981</v>
+        <v>0.2745327102810293</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -32.57</t>
+          <t>X ≈ -32.56</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>40</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>2.467751600682433</v>
+        <v>2.501683793494749</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>9.585368025766158</v>
+        <v>9.619766871782986</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>3.150401815144022</v>
+        <v>3.186476440670766</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>7.393093791933175</v>
+        <v>7.43205525791312</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>5.936439096014873</v>
+        <v>4.604135060905243</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>6.123383624259588</v>
+        <v>4.800062254994018</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.3825938645071716</v>
+        <v>-0.9630334281807436</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>7.56901445517164</v>
+        <v>6.218137192767628</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>5.124941041601332</v>
+        <v>5.191358548285777</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>4.356308426678815</v>
+        <v>4.423656009463642</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>9.611652406653292</v>
+        <v>9.67874558961352</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>11.82722183025537</v>
+        <v>11.89468629458615</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>8.21822848124912</v>
+        <v>8.287020423580948</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>5.507978892745648</v>
+        <v>5.577055965047307</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>4.852369588532277</v>
+        <v>4.9222505743654</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>5.447249990790219</v>
+        <v>5.516482391482697</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>2.820543699077909</v>
+        <v>2.889965282103908</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>2.716768744042916</v>
+        <v>2.786353316925876</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>5.429494167132795</v>
+        <v>5.498873846808699</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>10.61175584001433</v>
+        <v>10.68096596533788</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>7.574695844303115</v>
+        <v>7.644574121922339</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>7.501137210757996</v>
+        <v>7.571143933509425</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>5.278938154536114</v>
+        <v>5.348663197980912</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>0.2046783625730981</v>
+        <v>0.2745327102803756</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -29.9</t>
+          <t>X ≈ -29.88</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-1.035810075187641</v>
+        <v>-1.904277759024623</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>2.115688317327582</v>
+        <v>1.187250673071787</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>7.661703814501308</v>
+        <v>8.328331206385876</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>3.464110265238006</v>
+        <v>4.193171571421011</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.130583163943605</v>
+        <v>-2.99902653337395</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-5.435228186661178</v>
+        <v>-4.530378271341611</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-6.205183740324827</v>
+        <v>-5.299674544771321</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-4.738793467963767</v>
+        <v>-3.86081332255366</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-4.69798555340904</v>
+        <v>-3.818752412511799</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-3.722816289303474</v>
+        <v>-2.872503398120692</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-3.45026093669108</v>
+        <v>-2.599978671384839</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-3.729558524848024</v>
+        <v>-2.87866604062782</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-3.103193967925691</v>
+        <v>-2.280850726110593</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.575569284202182</v>
+        <v>-0.7828397653307775</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.4838485666134531</v>
+        <v>0.2797562879219555</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.1093562037330287</v>
+        <v>0.8725316652144528</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.02427598520704066</v>
+        <v>0.7393149161656751</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.1289051835744814</v>
+        <v>0.6350677088180419</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-5.168172074149759</v>
+        <v>-4.3135953697521</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-3.230922454532738</v>
+        <v>-2.406480812583226</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-3.774486230247483</v>
+        <v>-2.949131448035196</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-3.851530824634928</v>
+        <v>-3.025806298043165</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-1.824147414564905</v>
+        <v>-1.028700253294218</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-1.900584795321635</v>
+        <v>-1.104777634547219</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -27.23</t>
+          <t>X ≈ -27.21</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2.310316637347846</v>
+        <v>2.918542782842394</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-3.32369020360688</v>
+        <v>-2.645169998458456</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.7799861571961557</v>
+        <v>-1.459881432758259</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>5.137163562738841</v>
+        <v>4.372544609207267</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>6.100353756306525</v>
+        <v>6.658518843095962</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>8.938978660752753</v>
+        <v>8.154889585833274</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>12.15200757599134</v>
+        <v>11.31820627309846</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1.266350272788415</v>
+        <v>0.5650382108653744</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.01788871558431282</v>
+        <v>0.6071236909213127</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.7879783626277117</v>
+        <v>-0.1618466218568955</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>6.124373274104386</v>
+        <v>6.663075637137474</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>5.848131943256064</v>
+        <v>6.387354156216659</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.071933553006311</v>
+        <v>2.64761431783667</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>3.181283396238832</v>
+        <v>3.739945036711212</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>2.525043473257604</v>
+        <v>3.084674249685165</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-2.200523980164412</v>
+        <v>-1.571392369573005</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>5.647168306208897</v>
+        <v>6.171667861277811</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>5.544373040179423</v>
+        <v>6.069187282606578</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>4.430775918084677</v>
+        <v>4.973045974138763</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>1.955551654491195</v>
+        <v>1.218742118963753</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>2.745686704792874</v>
+        <v>1.991773114998054</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>4.003166736978201</v>
+        <v>3.23159321188983</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>2.946270539661029</v>
+        <v>2.191691737210711</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>2.871345029240068</v>
+        <v>2.116637973438273</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -24.55</t>
+          <t>X ≈ -24.54</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.9651027548614692</v>
+        <v>-0.8575108902273527</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>5.412518616529127</v>
+        <v>5.707063430058533</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.297227788903854</v>
+        <v>1.518900482627636</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>5.959214102521869</v>
+        <v>6.333304604899197</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.2253109306517302</v>
+        <v>0.4778094352066447</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.9330797183948931</v>
+        <v>-0.7186770019368538</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-4.389374700748697</v>
+        <v>-4.250996413727577</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-3.322487015805009</v>
+        <v>-3.144938506372675</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.936364917215279</v>
+        <v>-3.102824060623341</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.32855718502325</v>
+        <v>0.2747612437499569</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>4.293128272021981</v>
+        <v>3.313471447062199</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>2.670391329015189</v>
+        <v>1.653368344773064</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.550927788702793</v>
+        <v>0.5349024487811178</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>1.331019414215575</v>
+        <v>0.3149472853436279</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.6743038568742534</v>
+        <v>-0.3413067419928382</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>1.268076224780572</v>
+        <v>0.2514727302641404</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.2138376281248924</v>
+        <v>-1.268043296929989</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-0.3184512159588166</v>
+        <v>-1.372850126465629</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-0.1026555721620355</v>
+        <v>-1.157621055671399</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>1.43357996035234</v>
+        <v>1.802679306385059</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>2.24154371299197</v>
+        <v>2.648919148530382</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>2.16640675562698</v>
+        <v>2.574024167107318</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>5.143695603047554</v>
+        <v>5.626197347803426</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>2.366840524734961</v>
+        <v>2.774532710280376</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -21.88</t>
+          <t>X ≈ -21.86</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>88</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.474922808050948</v>
+        <v>-1.44105536887853</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-1.809254199009089</v>
+        <v>-1.774975467057693</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>5.764833387248565</v>
+        <v>5.800897883817157</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>3.912359263523356</v>
+        <v>3.950488491215005</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>5.795759484422568</v>
+        <v>5.866251211394868</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>3.230415145959284</v>
+        <v>2.668981374288045</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.963413216384509</v>
+        <v>0.7508604003758776</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.5578249447445174</v>
+        <v>-0.6664949138833975</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-2.791471876674329</v>
+        <v>-4.021549066311586</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.300587274949613</v>
+        <v>-1.889744097120733</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.159809089644796</v>
+        <v>-2.092825020686433</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.9568531832341165</v>
+        <v>1.024223480926658</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.295056078643384</v>
+        <v>-1.226348971336961</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.7492024784223403</v>
+        <v>0.818221812019992</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-3.306310327419993</v>
+        <v>-3.236496267860943</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.4473735795540676</v>
+        <v>-0.3781921561168815</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-1.715195324710912</v>
+        <v>-1.645814792274237</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-1.820296546347002</v>
+        <v>-1.750747416272645</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-6.142790517616604</v>
+        <v>-6.073455687209503</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-3.688589861347545</v>
+        <v>-3.619418591771662</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-4.23234943449205</v>
+        <v>-4.16249776764576</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-4.309634549455524</v>
+        <v>-4.239645543425553</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-5.172316004669824</v>
+        <v>-5.102599298977445</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-5.249867091972362</v>
+        <v>-5.180012744265085</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -19.2</t>
+          <t>X ≈ -19.19</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.6575850009159367</v>
+        <v>1.048207074348902</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-2.832812820571185</v>
+        <v>-2.416830439586427</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-2.264449526743455</v>
+        <v>-2.292323045518366</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.9696943951730788</v>
+        <v>0.9088527048199069</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>4.552563524008768</v>
+        <v>4.489530365663633</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2.371207810450088</v>
+        <v>2.327783162663764</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>6.33719744027924</v>
+        <v>6.699398175177109</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>4.485454814050172</v>
+        <v>4.85575209602046</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>10.0562005227042</v>
+        <v>10.38490013529241</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>6.130549865601928</v>
+        <v>6.480035235830528</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>5.615299736361408</v>
+        <v>5.968446255399094</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>2.968153555411256</v>
+        <v>3.340426253843461</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>4.221297588125779</v>
+        <v>4.57635623555899</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.04800617396592344</v>
+        <v>0.4345892531725042</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>3.347098993455141</v>
+        <v>3.703470818758184</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>3.94140917642035</v>
+        <v>4.297240820893116</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>3.01720236091456</v>
+        <v>3.37956973043201</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.2541081108204821</v>
+        <v>0.1334682443831881</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-0.03811037802218209</v>
+        <v>0.3493750927199315</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>2.525899442879641</v>
+        <v>2.894611534474066</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>1.984295804711117</v>
+        <v>2.353793642497166</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>1.909109774158743</v>
+        <v>2.278850321054499</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>0.5977685214269499</v>
+        <v>0.9798361175245134</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>2.109440267335003</v>
+        <v>2.479257119729198</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -16.52</t>
+          <t>X ≈ -16.51</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>123</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-5.296644634881112</v>
+        <v>-5.636102199484448</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>4.064762579422244</v>
+        <v>3.722545441014923</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.418665053644744</v>
+        <v>-1.747970623056851</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.099496984166613</v>
+        <v>0.775159642763505</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.7332235513280168</v>
+        <v>0.4422295757261381</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-2.312030408738053</v>
+        <v>-2.607770596668125</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2.57102532346547</v>
+        <v>2.287645666896644</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.483697799992399</v>
+        <v>1.203011682548926</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>2.334698225227754</v>
+        <v>2.053617003491937</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>3.177134723169651</v>
+        <v>2.903149479627842</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.835300856757755</v>
+        <v>1.557119619122105</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.8733239763269012</v>
+        <v>-1.147814289457685</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.426802634862419</v>
+        <v>0.162684372520971</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>2.634687196694195</v>
+        <v>2.373333570206093</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>2.784363497150444</v>
+        <v>2.528373515447669</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.1408778862012099</v>
+        <v>-0.1207861513759951</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.8176218471774845</v>
+        <v>0.5565267937091107</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.9120606171083878</v>
+        <v>-1.169629746989131</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.9277151844881999</v>
+        <v>0.668812626021456</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>1.118908324816047</v>
+        <v>0.8550994147392217</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>1.38405315089593</v>
+        <v>1.125794836620585</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>2.121243936496157</v>
+        <v>1.86288833887555</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>1.586325148276487</v>
+        <v>1.325355218234151</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>5.245328769077155</v>
+        <v>4.502174986703146</v>
       </c>
     </row>
     <row r="15">
@@ -1360,817 +1360,817 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.470212205662122</v>
+        <v>-0.7429410631307789</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-5.091741774294206</v>
+        <v>-4.704709851155187</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.8389581932949426</v>
+        <v>1.110405185701055</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.335441139054488</v>
+        <v>2.575396129399344</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>5.653889094579085</v>
+        <v>5.144916513824704</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>8.049049235325242</v>
+        <v>7.914902848392401</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.08212945297020013</v>
+        <v>0.6093087827027617</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>4.062024225926841</v>
+        <v>4.691744523110785</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.051794993930521</v>
+        <v>-0.3506973116643763</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.084438793631811</v>
+        <v>-0.3930984867603655</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.07447394213898662</v>
+        <v>-0.1207079221550984</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.564318960210556</v>
+        <v>-1.850383631095553</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.47169597149405</v>
+        <v>-0.7888783158401651</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.260224669651059</v>
+        <v>1.899483841222192</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.8732079496488936</v>
+        <v>-0.2105637313192901</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>2.674896574982633</v>
+        <v>3.292635978782073</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>2.542113868545641</v>
+        <v>3.160298286620318</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-2.735985715576085</v>
+        <v>-2.039720971830015</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-3.260673443630623</v>
+        <v>-2.553330476151906</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-2.335686221795022</v>
+        <v>-1.639562108628979</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>0.0814884102788298</v>
+        <v>0.7344269626874151</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-3.696577829843307</v>
+        <v>-2.987807767734282</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-3.423084001862136</v>
+        <v>-2.714436974427677</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-4.239766081871345</v>
+        <v>-4.251014734975101</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -11.17</t>
+          <t>X ≈ -11.16</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2.498662053920278</v>
+        <v>1.983547252519237</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>7.101625434147607</v>
+        <v>7.274826990397997</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-2.362531598894805</v>
+        <v>-2.289454052853124</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.6072475123560608</v>
+        <v>-0.5010930882189015</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-2.207045559858301</v>
+        <v>-2.088703265603819</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.4491865125107353</v>
+        <v>0.6017633602897732</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.2936123447297732</v>
+        <v>-0.1713437425258277</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.253027490786863</v>
+        <v>-1.075921366120454</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.2098021099221157</v>
+        <v>-1.034736380447015</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.361022092876361</v>
+        <v>-1.182947956970146</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.560586968552862</v>
+        <v>-2.785871477642246</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.9830808943629563</v>
+        <v>-1.4521216482417</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.484903602934196</v>
+        <v>-1.944829920137444</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.087290014345854</v>
+        <v>-1.539506021069236</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.1129068805962632</v>
+        <v>-0.3158180426641053</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.53279179679609</v>
+        <v>-0.9777333977838296</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-1.905888595211131</v>
+        <v>-2.365861430037441</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.7702651765375776</v>
+        <v>-1.214890547690885</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.5546347486982981</v>
+        <v>-0.9996914336419991</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-1.609373892160903</v>
+        <v>-2.070139786379741</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-2.152716766724772</v>
+        <v>-2.612793874664902</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-4.712790775584232</v>
+        <v>-5.203048021268962</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-5.060995204990732</v>
+        <v>-5.559402179864946</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-8.242526606371001</v>
+        <v>-8.153140245694466</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -8.495</t>
+          <t>X ≈ -8.486</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2.062071019696674</v>
+        <v>2.32182174662163</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>3.364469334482266</v>
+        <v>3.603526085544189</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.8341305291788217</v>
+        <v>1.098292690633407</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.304417714671587</v>
+        <v>2.547686466535005</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>4.669537181148648</v>
+        <v>4.918678397423747</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.05770198388474057</v>
+        <v>0.2385946374198653</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.99227371082457</v>
+        <v>3.255677493732989</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.076079263729355</v>
+        <v>1.358442550188144</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.118558082397463</v>
+        <v>0.8606987636044323</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>3.07788631689391</v>
+        <v>2.795247973082382</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.4732769466007127</v>
+        <v>-0.7159539106184596</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>4.170022959782493</v>
+        <v>3.872790163133601</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>2.498661742223447</v>
+        <v>2.216059297279905</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.730756082694327</v>
+        <v>1.455696526805063</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.02413960508092572</v>
+        <v>-0.2817996419246498</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.5731860470979768</v>
+        <v>0.8514233574143333</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>1.535527249077361</v>
+        <v>1.802137522217713</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.2164787376047883</v>
+        <v>0.07413692423960327</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.5487940021764004</v>
+        <v>-0.2524513427078503</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-3.104130559984739</v>
+        <v>-2.779386275776105</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-3.102072357080132</v>
+        <v>-2.779629322743354</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-3.730738914441019</v>
+        <v>-3.399282777489226</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-4.224874803652938</v>
+        <v>-4.212938703760905</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-2.103013945119216</v>
+        <v>-2.11677163754571</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -5.819</t>
+          <t>X ≈ -5.81</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.938926374113194</v>
+        <v>1.732087512667221</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.068133587323253</v>
+        <v>-1.287237281184311</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.3689686002865358</v>
+        <v>-0.5749457903814346</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-5.356696073502832</v>
+        <v>-5.586969320917689</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-3.050617422401196</v>
+        <v>-3.236599336487153</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.3418973086229187</v>
+        <v>0.1762073242310791</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-6.306729358907226</v>
+        <v>-6.509789776940856</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-7.653064030431288</v>
+        <v>-7.863288455347281</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-4.637417968295409</v>
+        <v>-4.595964100686885</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-4.339868744274931</v>
+        <v>-4.293607165659502</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.927911794808779</v>
+        <v>-1.868987678780002</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-4.34723292344642</v>
+        <v>-4.298298342034904</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-3.862342597077408</v>
+        <v>-3.492704672697478</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.94244963255057</v>
+        <v>-1.562662474916905</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-5.278532429154161</v>
+        <v>-4.908908191946388</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-7.368582568525461</v>
+        <v>-7.550704841429273</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-6.969503732691535</v>
+        <v>-7.149063169308171</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-6.539277888729188</v>
+        <v>-6.715522487555724</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-4.179138046589195</v>
+        <v>-4.346230298854216</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-6.143122019318405</v>
+        <v>-6.320374855473673</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-4.002247884999939</v>
+        <v>-4.166512113163073</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-3.542542561414749</v>
+        <v>-3.703948043898905</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-3.267767394932619</v>
+        <v>-3.431541993023345</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-3.881343142803253</v>
+        <v>-4.049791614043954</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -3.144</t>
+          <t>X ≈ -3.135</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-7.136616095000093</v>
+        <v>-6.902239417365003</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-5.737903812491254</v>
+        <v>-6.372195742500949</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.967579452110058</v>
+        <v>-2.4010990592529</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.7895933758088276</v>
+        <v>0.3432375929569602</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>3.027135625911278</v>
+        <v>3.272452229891464</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2.77983811993154</v>
+        <v>3.026682542678088</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>5.046556537953037</v>
+        <v>5.283026238563508</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>5.637476224684264</v>
+        <v>5.870572784898734</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2.208686261727067</v>
+        <v>2.452978176100828</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.5693772893807818</v>
+        <v>0.8160792246697639</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.02443162432767565</v>
+        <v>0.2251823602501091</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.3032153540684561</v>
+        <v>-0.05322354983770339</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.5581840425206082</v>
+        <v>-0.3102268833518451</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.954785067765506</v>
+        <v>-2.694521250457178</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-2.745806136002166</v>
+        <v>-2.488138520440103</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-1.28030966532733</v>
+        <v>-1.028620352933771</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.3276796930454537</v>
+        <v>0.5702564360599993</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>1.092371381405385</v>
+        <v>1.331529371684063</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.8733566184958335</v>
+        <v>1.114518077918603</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>3.503889756576804</v>
+        <v>3.472652096064877</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>0.3438316585623014</v>
+        <v>0.3248545035553718</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>1.141215714398733</v>
+        <v>1.116487622960825</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>0.9793096581734417</v>
+        <v>0.9573555858394798</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>2.21341198702725</v>
+        <v>2.448445753758634</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ -0.4684</t>
+          <t>X ≈ -0.4606</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>211</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.78617865835011</v>
+        <v>0.3487382871725302</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.843077649055196</v>
+        <v>-2.557358486654927</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>3.248055024147</v>
+        <v>3.542724879688961</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>10.07054014127704</v>
+        <v>10.37254924920649</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>8.764355350626928</v>
+        <v>8.622579009599747</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>5.655506970118417</v>
+        <v>5.510345492479296</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>6.763065612404183</v>
+        <v>6.624490383417147</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>4.126953814399812</v>
+        <v>3.990614040437549</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>6.050826854516394</v>
+        <v>5.917657977845415</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>2.921293001344921</v>
+        <v>2.789126205340104</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>6.970465081641933</v>
+        <v>6.833372125091962</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>4.80658115858693</v>
+        <v>4.669797992516408</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>4.622430660717299</v>
+        <v>4.490268334167006</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>3.457136812518151</v>
+        <v>3.329009457460621</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>3.738331435184939</v>
+        <v>3.616322590582968</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>1.503617605494547</v>
+        <v>1.380603058465091</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>2.318566150289676</v>
+        <v>2.192689302245142</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>3.627916441715549</v>
+        <v>3.505558575127282</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>4.131416933304486</v>
+        <v>3.72395742962135</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>3.847321806581284</v>
+        <v>3.441430147259126</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>3.303081281548828</v>
+        <v>2.898060492207485</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>3.039019890809627</v>
+        <v>2.348153349657323</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>3.7877287065809</v>
+        <v>3.383540318953997</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>0.8681854715778385</v>
+        <v>0.4641061699960147</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 2.207</t>
+          <t>X ≈ 2.214</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>4.506443050945975</v>
+        <v>3.949322965396682</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>3.661291802293007</v>
+        <v>3.109740084562993</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-3.932325980196588</v>
+        <v>-4.419328277174962</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.5403719676766485</v>
+        <v>-0.7978121543523145</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.929584213586281</v>
+        <v>-2.148370752635465</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-4.305696603823527</v>
+        <v>-4.497876343878588</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-3.545499753740756</v>
+        <v>-3.747299058332274</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-3.829755817642521</v>
+        <v>-4.024762941419858</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-4.302206479496895</v>
+        <v>-4.490398175790155</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.494777901630279</v>
+        <v>-1.711363765168045</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.75744754243852</v>
+        <v>-2.959568445859773</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-4.582965218927662</v>
+        <v>-4.759871988579199</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-3.149672425878848</v>
+        <v>-3.345739960262961</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.319193075247966</v>
+        <v>-1.538032841012914</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-3.532698797126244</v>
+        <v>-3.721899290526785</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-3.964726651844394</v>
+        <v>-4.145997294845401</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-2.760322053281662</v>
+        <v>-3.264562156714327</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.736909877183237</v>
+        <v>0.1899436708130438</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>2.501037633485495</v>
+        <v>1.935256789629271</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>1.660379275640935</v>
+        <v>1.106266266966259</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>2.968397529146316</v>
+        <v>2.394927121173971</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>2.89244247350382</v>
+        <v>2.320788210205272</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>2.651753722460121</v>
+        <v>2.085058841054668</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>2.575812383191654</v>
+        <v>2.009226587831336</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 4.883</t>
+          <t>X ≈ 4.889</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>166</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>5.290738251251028</v>
+        <v>5.323719138006112</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.035393911014793</v>
+        <v>-1.001990246686546</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.70923443622204</v>
+        <v>1.744301180847927</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.7893575716108998</v>
+        <v>-0.7534423202958465</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-4.75062277768788</v>
+        <v>-4.685214004151497</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.3704992275861443</v>
+        <v>-0.3053058373654665</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.749466655911455</v>
+        <v>-1.683354530295972</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.637676178901643</v>
+        <v>-2.571220132845866</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.599206040622022</v>
+        <v>-2.532779364151111</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.2174630022092643</v>
+        <v>0.2841933446809222</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.905772101814932</v>
+        <v>-1.836698388191685</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.8099147379049327</v>
+        <v>0.8754488817017858</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.9266351208492409</v>
+        <v>-0.2553292182040607</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.957106555826414</v>
+        <v>-2.278276400880721</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-3.26748801528759</v>
+        <v>-2.950814096918549</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-0.8650775598379354</v>
+        <v>-0.5512723768874537</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-3.405377274650682</v>
+        <v>-3.086316693645564</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-3.754070573010083</v>
+        <v>-3.800729512632174</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-4.742766687186624</v>
+        <v>-4.425211543740971</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-1.543674698795186</v>
+        <v>-1.226644377239573</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-1.484465469238913</v>
+        <v>-1.170645259286545</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.9580108863272443</v>
+        <v>-0.2855555321109335</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>0.5215835572632557</v>
+        <v>1.193738457479554</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.1567674205594329</v>
+        <v>0.5154965657021364</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 7.558</t>
+          <t>X ≈ 7.564</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.1277904596066008</v>
+        <v>0.4778991560781094</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>2.719881650806443</v>
+        <v>3.08770556893397</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>5.962485938810481</v>
+        <v>6.359658122314634</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.6039248769978656</v>
+        <v>-0.2404890796590422</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-3.311544481237696</v>
+        <v>-2.932498628337498</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.1969215714794359</v>
+        <v>0.199248092953674</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.556620499235052</v>
+        <v>-1.16303796589191</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.0807118712296031</v>
+        <v>0.3235470085966341</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-2.967228875680526</v>
+        <v>-2.580338316646753</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.986293756429063</v>
+        <v>-1.58717496751931</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-5.818569157073732</v>
+        <v>-5.43561075064062</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-4.343643220932371</v>
+        <v>-3.948281128924478</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-5.478373172097996</v>
+        <v>-5.661879232730023</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-5.352502447105714</v>
+        <v>-5.889009788341539</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-3.071498477338658</v>
+        <v>-3.60742258258658</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-4.244972201249219</v>
+        <v>-4.785698433409934</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-6.143771777751155</v>
+        <v>-6.696833942300863</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-5.072284605611067</v>
+        <v>-5.264937978187199</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-3.091455560326317</v>
+        <v>-3.276014953279457</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-2.316176470588303</v>
+        <v>-2.50098389179275</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-1.094670997233244</v>
+        <v>-1.268382130764572</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-2.935331935228866</v>
+        <v>-3.119376021167753</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-3.248792062864318</v>
+        <v>-3.436617285017064</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-2.14826281389756</v>
+        <v>-2.329017585577674</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 10.23</t>
+          <t>X ≈ 10.24</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>146</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.2926205972156666</v>
+        <v>-0.2593463048968374</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.423239516792762</v>
+        <v>1.456912525406103</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.7079062072063422</v>
+        <v>-0.6725517835378554</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.408107765599233</v>
+        <v>-1.371914048180329</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.415728861140785</v>
+        <v>-0.3500558312451076</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.4589976532646887</v>
+        <v>0.5244722562509594</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.01113877647375</v>
+        <v>-0.9447467253238031</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.05824687120456673</v>
+        <v>0.1249821231199988</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2.819914513335455</v>
+        <v>2.886620882142957</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>5.162256181874596</v>
+        <v>4.839681820986129</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>2.023503243542088</v>
+        <v>1.695348748727021</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>2.427889919236733</v>
+        <v>2.094452850391683</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>5.40482677766159</v>
+        <v>5.05200356901225</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>5.864553543662929</v>
+        <v>5.918377177881226</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>7.935728507488285</v>
+        <v>7.992742932436379</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>8.954060836623377</v>
+        <v>8.598020059910496</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>9.504898649323934</v>
+        <v>9.156967700313416</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>9.399915233228498</v>
+        <v>9.048920388314031</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>8.931106889310989</v>
+        <v>8.585652157109642</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>8.433219178082268</v>
+        <v>8.502501558478997</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>6.520155755385609</v>
+        <v>6.590092376814262</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>9.868858233989577</v>
+        <v>9.938903949651738</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>9.458701893622383</v>
+        <v>9.528447155284468</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>10.75262356805255</v>
+        <v>10.82247791575983</v>
       </c>
     </row>
     <row r="25">
@@ -2183,76 +2183,76 @@
         <v>162</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>4.330907006101768</v>
+        <v>4.364181298420597</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2.148613896308348</v>
+        <v>2.182286904921689</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.942881660941133</v>
+        <v>1.97823608460962</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-3.080852707600002</v>
+        <v>-3.044658990181098</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.8604098978979167</v>
+        <v>0.926082927793594</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.799543084244462</v>
+        <v>-0.7340684812581912</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.9507381878033101</v>
+        <v>-0.8843461366533631</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.83732920251304</v>
+        <v>-1.770593950597608</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.12599903497788</v>
+        <v>3.192705403785382</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.1068250880609867</v>
+        <v>-0.03919898452054582</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.7884908993796529</v>
+        <v>0.8539751875169728</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>1.74459498483359</v>
+        <v>1.806637514168408</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>4.326385065722548</v>
+        <v>4.376858471403999</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>3.487744304070837</v>
+        <v>3.543056311630409</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>4.680664916885455</v>
+        <v>4.739842376075636</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>4.658441015889558</v>
+        <v>4.722139575147978</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>2.672495469888744</v>
+        <v>2.74206490567127</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>3.184796004410785</v>
+        <v>3.254508152467409</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>5.252771019194419</v>
+        <v>5.322251385243554</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>5.43981481481481</v>
+        <v>5.509097195211538</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>8.600318109520565</v>
+        <v>8.670254730949218</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>8.524363053877956</v>
+        <v>8.594408769540117</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>6.947286368508223</v>
+        <v>7.017031630170308</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>6.871345029239798</v>
+        <v>6.941199376947075</v>
       </c>
     </row>
     <row r="26">
@@ -2265,158 +2265,158 @@
         <v>131</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.005709191438839</v>
+        <v>-0.9724348991200102</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-3.621944993394543</v>
+        <v>-3.588271984781201</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-5.056654005342423</v>
+        <v>-5.021299581673937</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-2.735896848810427</v>
+        <v>-2.699703131391523</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-9.179626546043956</v>
+        <v>-9.113953516148278</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-5.195686239656396</v>
+        <v>-5.130211636670126</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-3.680004906191606</v>
+        <v>-3.613612855041659</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>3.649342259948725</v>
+        <v>3.716077511864157</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.6513164031080407</v>
+        <v>0.7180227719155425</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.1193993500751205</v>
+        <v>-0.05177324653467963</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.9232159060194576</v>
+        <v>0.9876312768693154</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>2.933658048161824</v>
+        <v>2.989318229215442</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>2.578199220844525</v>
+        <v>2.628381386015022</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>3.120201188436127</v>
+        <v>3.170775596258601</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>3.987987506650676</v>
+        <v>4.044299903174853</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>3.056329999020207</v>
+        <v>3.11992311383748</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>1.395518747619327</v>
+        <v>1.465088183401853</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>2.817252888775954</v>
+        <v>2.886965036832578</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>3.033376051707862</v>
+        <v>3.102856417756996</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>0.9303435114503813</v>
+        <v>0.9996258918471099</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.3762156761735298</v>
+        <v>-0.306279054744877</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-1.215529510442089</v>
+        <v>-1.145483794779928</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-3.230830679837865</v>
+        <v>-3.16108541817578</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-1.780054461854341</v>
+        <v>-1.710200114147064</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 18.26</t>
+          <t>X ≈ 18.27</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-5.511600031762029</v>
+        <v>-5.914327990716359</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-5.846775546406356</v>
+        <v>-6.249104789066173</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.809739608755812</v>
+        <v>-2.260162526825283</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-4.342111825214715</v>
+        <v>-4.775223314301769</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-2.885442756262684</v>
+        <v>-3.305604457667997</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-5.43328639341393</v>
+        <v>-5.828816366059236</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-6.216232377598907</v>
+        <v>-6.610672733391432</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.8106081340159079</v>
+        <v>0.3500915846030779</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.9782145317132276</v>
+        <v>-1.422086965531442</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.8423404970109942</v>
+        <v>-1.29353643740761</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-3.321314352896692</v>
+        <v>-3.742865134323402</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.9829527031361494</v>
+        <v>0.5071831304874053</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.3791656750780064</v>
+        <v>-0.6184558572291152</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>2.910102442025355</v>
+        <v>1.873120281673373</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>1.33374001032751</v>
+        <v>0.3067925023578155</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>0.09393767462778868</v>
+        <v>-0.9077660548248971</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.9575872121817355</v>
+        <v>-1.421795924856305</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-1.980001820937517</v>
+        <v>-2.435727537768301</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>0.9884149199759023</v>
+        <v>0.5074365704287018</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>0.2580275229357767</v>
+        <v>-0.2148085286941779</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>0.6322583065983807</v>
+        <v>0.1517362124306985</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>4.226028021597919</v>
+        <v>3.712253887385231</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>2.665940802759046</v>
+        <v>2.168546781685521</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>3.507430656151023</v>
+        <v>3.001805437553109</v>
       </c>
     </row>
     <row r="28">
@@ -2426,161 +2426,161 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>3.168234316285044</v>
+        <v>3.762301499575102</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-5.948353524626292</v>
+        <v>-5.440832301539416</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-4.459084197414313</v>
+        <v>-3.920896476691205</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-8.108260524137499</v>
+        <v>-7.59823092536481</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-7.493236955442448</v>
+        <v>-6.944058715210836</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-7.310653215458402</v>
+        <v>-6.761682211507484</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-4.169675329472454</v>
+        <v>-3.581123656423522</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-7.376283591684533</v>
+        <v>-6.816372038576937</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-6.354474172942837</v>
+        <v>-5.784922173961078</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-7.124644885294003</v>
+        <v>-6.554166104082334</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.9864671608477735</v>
+        <v>-0.3577711588105927</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-2.247017688194134</v>
+        <v>-1.627401181438479</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>1.530451877632423</v>
+        <v>2.179055562677711</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-5.553650031441173</v>
+        <v>-4.937798442961558</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-3.271404799890213</v>
+        <v>-2.6355938567526</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-3.656736907131659</v>
+        <v>-3.034053405340558</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-2.810438444417755</v>
+        <v>-2.177871532416965</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-1.935029703650258</v>
+        <v>-1.292613226337181</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-7.601259481894914</v>
+        <v>-7.017315904818801</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-8.394607843137258</v>
+        <v>-7.820569104751783</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-8.937808252135177</v>
+        <v>-8.363115272717792</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-6.072586837189498</v>
+        <v>-5.468664204423924</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-3.837027356981942</v>
+        <v>-3.213991472139888</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-3.912968696250374</v>
+        <v>-3.289823725363192</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 23.61</t>
+          <t>X ≈ 23.62</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>86</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-8.288032091704515</v>
+        <v>-8.254757799385686</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.5196580891344666</v>
+        <v>-0.4859850805211252</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.3508219719790446</v>
+        <v>0.3861763956475315</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-9.618027585225221</v>
+        <v>-9.581833867806317</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-7.665949773443415</v>
+        <v>-7.600276743547738</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-7.485952232042841</v>
+        <v>-7.42047762905657</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-7.091544079766429</v>
+        <v>-7.025152028616482</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-3.899810987361136</v>
+        <v>-3.833075735445703</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.3851403557721795</v>
+        <v>-0.3184339869646777</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.002564860503817101</v>
+        <v>0.07019096404425795</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>2.605656275052048</v>
+        <v>2.663031617333388</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>4.661327045048012</v>
+        <v>4.688729081800069</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>4.699626524235292</v>
+        <v>4.718507156061861</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>6.803851108549701</v>
+        <v>6.821942948027342</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>4.982129171838018</v>
+        <v>5.033325887679787</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>4.414398523785017</v>
+        <v>4.483791402396093</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>5.443095527310476</v>
+        <v>5.512664963093002</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>1.849740018191937</v>
+        <v>1.919452166248561</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>3.22865387879817</v>
+        <v>3.298134244847304</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.07267441860464885</v>
+        <v>-0.003392038207920223</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>0.5469158700717784</v>
+        <v>0.6168524915004312</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>0.4709608144291693</v>
+        <v>0.5410065300913303</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>1.908526678585716</v>
+        <v>1.978271940247801</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>0.6697946416428948</v>
+        <v>0.7396489893501723</v>
       </c>
     </row>
     <row r="30">
@@ -2593,76 +2593,76 @@
         <v>81</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-4.261481252369883</v>
+        <v>-4.228206960051054</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-4.591890095580901</v>
+        <v>-4.558217086967559</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-2.364431336952258</v>
+        <v>-2.329076913283771</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-6.747767208576832</v>
+        <v>-6.711573491157928</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-5.883500578879314</v>
+        <v>-5.817827548983637</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.4155960719854477</v>
+        <v>0.4810706749717184</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.8841830332363756</v>
+        <v>0.9505750843863225</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.6215246912871564</v>
+        <v>-0.5547894393717243</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-4.251934520412611</v>
+        <v>-4.185228151605109</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-2.569080437455469</v>
+        <v>-2.501454333915028</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-3.520103739424222</v>
+        <v>-3.445014427891394</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-9.981222481222481</v>
+        <v>-9.864295897797398</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-11.10571369970969</v>
+        <v>-10.99460797180353</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-7.623366807040242</v>
+        <v>-7.524694268368606</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-7.047730144843001</v>
+        <v>-6.96116017078635</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-5.218102193987029</v>
+        <v>-5.148709315375953</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-2.883060085666813</v>
+        <v>-2.813490649884287</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-1.753475600527551</v>
+        <v>-1.683763452470927</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-1.537352437595814</v>
+        <v>-1.46787207154668</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-6.288580246913611</v>
+        <v>-6.219297866516882</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-6.831780655911565</v>
+        <v>-6.761844034482912</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-6.907735711554174</v>
+        <v>-6.837689995892013</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-4.163824742602912</v>
+        <v>-4.094079480940827</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-4.23976608187138</v>
+        <v>-4.169911734164103</v>
       </c>
     </row>
     <row r="31">
@@ -2675,76 +2675,76 @@
         <v>60</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-3.628651829031213</v>
+        <v>-3.595377536712384</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>2.641662074313913</v>
+        <v>2.675335082927255</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-5.420062199296076</v>
+        <v>-5.384707775627589</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3.782645810262082</v>
+        <v>3.818839527680986</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1.772204067566136</v>
+        <v>1.837877097461813</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>5.216643812847984</v>
+        <v>5.282118415834255</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>2.819273712540038</v>
+        <v>2.885665763689985</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>2.540719067021477</v>
+        <v>2.607454318936909</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>2.598769523578497</v>
+        <v>2.665475892385999</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-3.118848955974016</v>
+        <v>-3.051222852433575</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.4780156890866181</v>
+        <v>0.5379822923737834</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.2039627039627305</v>
+        <v>0.250965693158669</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.9205285145244133</v>
+        <v>-0.8845971673482111</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-1.141885325558846</v>
+        <v>-1.089141652260459</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.1341498979294471</v>
+        <v>-0.07159312173529742</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>2.12757681835857</v>
+        <v>2.196969696969646</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>1.993483124209646</v>
+        <v>2.063052559992173</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>3.555166374781017</v>
+        <v>3.624878522837641</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>0.4379562043795886</v>
+        <v>0.5074365704287231</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-2.708333333333314</v>
+        <v>-2.639050952936586</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-3.251533742331269</v>
+        <v>-3.181597120902616</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-1.660822131307185</v>
+        <v>-1.590776415645024</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-1.386046964825056</v>
+        <v>-1.316301703162971</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-4.795321637426895</v>
+        <v>-4.725467289719617</v>
       </c>
     </row>
     <row r="32">
@@ -2757,76 +2757,76 @@
         <v>55</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.483855421343648</v>
+        <v>3.517129713662477</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-2.254617776010093</v>
+        <v>-2.220944767396752</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-14.51205442547948</v>
+        <v>-14.47670000181099</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-6.196213157567463</v>
+        <v>-6.16001944014856</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-8.377436596780484</v>
+        <v>-8.311763566884807</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-15.34267840088595</v>
+        <v>-15.27720379789968</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-14.34972456859063</v>
+        <v>-14.28333251744068</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-12.82346637988459</v>
+        <v>-12.75673112796915</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-10.99941912056605</v>
+        <v>-10.93271275175854</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.9666591659166173</v>
+        <v>-0.8990330623761764</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>4.748485768154715</v>
+        <v>4.778324262495246</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>1.870629370629352</v>
+        <v>0.9010900105623634</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.7461381521422865</v>
+        <v>-0.2053608263472455</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-3.111582295255765</v>
+        <v>-4.058347011171705</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>1.684031920252416</v>
+        <v>0.6974582311586985</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>4.097273788055588</v>
+        <v>4.166666666666664</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>2.144998275724845</v>
+        <v>2.214567711507371</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>5.676378495993234</v>
+        <v>5.746090644049858</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>0.4379562043796241</v>
+        <v>0.5074365704287587</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>0.6250000000000284</v>
+        <v>0.694282380396757</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>0.08179959100207412</v>
+        <v>0.1517362124307269</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>1.824026353541278</v>
+        <v>1.894072069203439</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>2.098801520023407</v>
+        <v>2.168546781685492</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>0.2046783625731265</v>
+        <v>0.274532710280404</v>
       </c>
     </row>
     <row r="33">
@@ -2839,76 +2839,76 @@
         <v>30</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>19.48764330013158</v>
+        <v>19.52091759245041</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>22.46129131489898</v>
+        <v>22.49496432351232</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>14.44556421374298</v>
+        <v>14.48091863741147</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3.784490101437662</v>
+        <v>3.820683818856565</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>3.440030527290467</v>
+        <v>3.505703557186145</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-6.333959132732737</v>
+        <v>-6.268484529746466</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-3.763318050580303</v>
+        <v>-3.696925999430356</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-4.048809433057833</v>
+        <v>-3.982074181142401</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.6845963647055484</v>
+        <v>-0.6178899958980466</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-4.774192041845659</v>
+        <v>-4.706565938305218</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-4.516943392562389</v>
+        <v>-4.439443033102265</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-1.462703962703962</v>
+        <v>-1.416305644097463</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-12.58719518119116</v>
+        <v>-12.46593829918885</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-6.141885325558817</v>
+        <v>-6.041623168976159</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-10.13414989792943</v>
+        <v>-10.06408389163996</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-16.20575651497471</v>
+        <v>-16.13636363636363</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-9.673183542456968</v>
+        <v>-9.603614106674442</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-9.778166958552248</v>
+        <v>-9.708454810495624</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-12.89537712895382</v>
+        <v>-12.82589676290468</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-2.708333333333357</v>
+        <v>-2.639050952936628</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-6.584867075664619</v>
+        <v>-6.514930454235966</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-6.660822131307278</v>
+        <v>-6.590776415645117</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-6.386046964825148</v>
+        <v>-6.316301703163063</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-6.461988304093616</v>
+        <v>-6.392133956386338</v>
       </c>
     </row>
     <row r="34">
@@ -2921,76 +2921,76 @@
         <v>37</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2.98471134003848</v>
+        <v>3.017985632357309</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>5.313068923709864</v>
+        <v>5.346741932323205</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>3.95540291409457</v>
+        <v>3.990757337763057</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-2.126473822965409</v>
+        <v>-2.090280105546505</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>5.539872914193076</v>
+        <v>5.605545944088753</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>2.995142383491789</v>
+        <v>3.06061698647806</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>4.954171395145835</v>
+        <v>5.020563446295782</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.6651218560826067</v>
+        <v>-0.5983866041671746</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-3.259794071218735</v>
+        <v>-3.193087702411233</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-9.374368087698045</v>
+        <v>-9.306741984157604</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-11.90433077994977</v>
+        <v>-11.70988784938987</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-9.480721980721974</v>
+        <v>-9.338776563600597</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-13.30791590191184</v>
+        <v>-13.12547172877244</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.01575919943265092</v>
+        <v>0.02580452267342537</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-6.08009584387537</v>
+        <v>-6.010029837585904</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-8.187738496956698</v>
+        <v>-8.118345618345622</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-5.619129488402912</v>
+        <v>-5.549560052620386</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-8.426815607200901</v>
+        <v>-8.357103459144277</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-13.6160978496745</v>
+        <v>-13.54661748362537</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-10.72635135135131</v>
+        <v>-10.65706897095458</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-8.566849057646586</v>
+        <v>-8.496912436217933</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-11.34550681599191</v>
+        <v>-11.27546110032975</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-13.77343435221248</v>
+        <v>-13.7036890905504</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-11.14667298877825</v>
+        <v>-11.07681864107097</v>
       </c>
     </row>
   </sheetData>
@@ -3180,1641 +3180,1641 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -39.26</t>
+          <t>X &gt; -39.25</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3338</v>
+        <v>3342</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.04611668948729886</v>
+        <v>0.04524087705555502</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.1837536039318906</v>
+        <v>-0.1843661062510051</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.1780027448147905</v>
+        <v>-0.1786637817526895</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.1175256589608935</v>
+        <v>-0.1016044185179368</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1384268812686216</v>
+        <v>-0.1231017385170716</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.262230792218503</v>
+        <v>-0.2468413322010861</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.2732254890780439</v>
+        <v>-0.2576141435677641</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.2068664385582437</v>
+        <v>-0.2082496502624736</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.118471324860181</v>
+        <v>-0.1199595694067241</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.1592421982616656</v>
+        <v>-0.1607047643216362</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.1063196981428121</v>
+        <v>-0.1078384738362672</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.06966913683330489</v>
+        <v>-0.07124049750684236</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.1615954996941369</v>
+        <v>-0.1630901697452245</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.0666165083544854</v>
+        <v>-0.06823176351047522</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.08037039389596146</v>
+        <v>-0.08198899459430464</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.1547503384455169</v>
+        <v>-0.1562641338760713</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.2710908668216945</v>
+        <v>-0.272470481711764</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.208788968121624</v>
+        <v>-0.2102469251909724</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-0.1842394282857001</v>
+        <v>-0.1857214815581543</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.2487283064033576</v>
+        <v>-0.250128856901533</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.2654018456935532</v>
+        <v>-0.2667989146246086</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.2636165424848755</v>
+        <v>-0.265018839887496</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.3003925772839153</v>
+        <v>-0.3017439207320649</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.3285750826036562</v>
+        <v>-0.3298957756561833</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -36.59</t>
+          <t>X &gt; -36.57</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3319</v>
+        <v>3323</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.02237664872391321</v>
+        <v>0.0213352483019662</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.2069017108142859</v>
+        <v>-0.2076813280497305</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.2228817810071675</v>
+        <v>-0.2236938133404465</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.1579988438259576</v>
+        <v>-0.1421565254380397</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.08707785837252402</v>
+        <v>-0.07208514810359645</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.3025380632787389</v>
+        <v>-0.2873973146095992</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.2792296276449875</v>
+        <v>-0.2639018463729386</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.210907351911942</v>
+        <v>-0.2126733390445565</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.1222462930994581</v>
+        <v>-0.1241181798811013</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.1288364130530653</v>
+        <v>-0.1307287986704964</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.0171434725944053</v>
+        <v>-0.01916127848376448</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.008686150235227785</v>
+        <v>-0.01072513801307196</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.09470268869861087</v>
+        <v>-0.09667935408551642</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.02793719298644959</v>
+        <v>-0.03000300030002734</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.03799605177557908</v>
+        <v>-0.0400742877984257</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.1161863316263521</v>
+        <v>-0.1181508874393913</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.2023477036115082</v>
+        <v>-0.2042147072750424</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.1691444021612725</v>
+        <v>-0.1710561922919638</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.1155937354519594</v>
+        <v>-0.1175634295712982</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.2115934396629626</v>
+        <v>-0.2134422964893545</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.2252443584260106</v>
+        <v>-0.2270972211231168</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.2230021975523329</v>
+        <v>-0.224861628677651</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.2615489728572342</v>
+        <v>-0.2633534480486972</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.2894463737932753</v>
+        <v>-0.2912211266139906</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -33.91</t>
+          <t>X &gt; -33.9</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3284</v>
+        <v>3288</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.01613872734055377</v>
+        <v>0.01474201043509993</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.2120200671424683</v>
+        <v>-0.2131579099685439</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.2129199026410618</v>
+        <v>-0.2141266367498886</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.1700546201925732</v>
+        <v>-0.1544167564877483</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.1247907279300691</v>
+        <v>-0.1103003384652226</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.3142453548521829</v>
+        <v>-0.2996270155707634</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.3127925985345641</v>
+        <v>-0.2979752774722684</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.2711045260521487</v>
+        <v>-0.273523283968693</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.1213371084617023</v>
+        <v>-0.1239367807971377</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.05914175407836808</v>
+        <v>-0.06185543762325807</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.1115067135947214</v>
+        <v>0.1085977684441062</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.09271674927014573</v>
+        <v>0.08981550075846201</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.01258718928417579</v>
+        <v>-0.01541643116237168</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.05726464408297716</v>
+        <v>0.05433836288420224</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.006606624318742149</v>
+        <v>-0.009488805197740646</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.09194525535542653</v>
+        <v>-0.09469696969696884</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.08643179526766431</v>
+        <v>-0.08919832518733273</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.02132805277717154</v>
+        <v>-0.02418037212282798</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.06067559860006355</v>
+        <v>-0.06347141620962304</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.1292579075425806</v>
+        <v>-0.1319630631026598</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.1068222526243616</v>
+        <v>-0.1095825356701852</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.1341432917860246</v>
+        <v>-0.136875706425208</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.176001302724643</v>
+        <v>-0.1786712177064445</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.2947126240286053</v>
+        <v>-0.2972434454373882</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -31.24</t>
+          <t>X &gt; -31.22</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3244</v>
+        <v>3248</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.01409077787943858</v>
+        <v>-0.01588535142523995</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.3328263321598328</v>
+        <v>-0.3342530427487347</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.2543911938591279</v>
+        <v>-0.2560059849939833</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.2633116906256916</v>
+        <v>-0.2478462147931779</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.199528456955278</v>
+        <v>-0.1683598877185588</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.3936242571840154</v>
+        <v>-0.3624310706269824</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.3213670308778731</v>
+        <v>-0.2897849061581255</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.3677767699636476</v>
+        <v>-0.353469841563971</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.1860261115450967</v>
+        <v>-0.1893960828794334</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.1135862692541565</v>
+        <v>-0.1170957263804837</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.005634417022527316</v>
+        <v>-0.009261194870795464</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.05197505197504881</v>
+        <v>-0.05556468143154092</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.1140769016212104</v>
+        <v>-0.1176631904572361</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.00994514936538593</v>
+        <v>-0.01367540068923745</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.06652001781876038</v>
+        <v>-0.07022451184260348</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.1602460598701612</v>
+        <v>-0.1638001638001612</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.1222761293533097</v>
+        <v>-0.1258875321736781</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.05509003547532387</v>
+        <v>-0.0587928559781048</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.1283718965745706</v>
+        <v>-0.1319732051630567</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.2616995073891601</v>
+        <v>-0.2651272136992162</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.2015388752745153</v>
+        <v>-0.20507707578831</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.2282897838026017</v>
+        <v>-0.2318020566707162</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.2432631949226831</v>
+        <v>-0.2467418385893012</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.3008703427289987</v>
+        <v>-0.3042850237097738</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -28.56</t>
+          <t>X &gt; -28.55</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3187</v>
+        <v>3190</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.004182833650702378</v>
+        <v>0.0184490559856556</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.376618404648319</v>
+        <v>-0.3619167466727475</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.3959718074382153</v>
+        <v>-0.4120848430190662</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.3299772229395401</v>
+        <v>-0.3285919927243413</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.1649912375331439</v>
+        <v>-0.1168932214339122</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.3034543720317799</v>
+        <v>-0.2866502124321713</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.2161340367020088</v>
+        <v>-0.1986960036378846</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.2896004437050976</v>
+        <v>-0.2896999600914256</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.1053290019792925</v>
+        <v>-0.1234077859770366</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.04903461844060786</v>
+        <v>-0.06699740507611551</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.05597327410427511</v>
+        <v>0.03784275924765268</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.01379911117329158</v>
+        <v>-0.004235565809786124</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.06061606924613727</v>
+        <v>-0.07833250799081526</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.01805628636905965</v>
+        <v>0.0003094059406052452</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.05905603059525077</v>
+        <v>-0.07658779911104574</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.1650679390748664</v>
+        <v>-0.1826425606913418</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.1240288774600984</v>
+        <v>-0.1416184857798513</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-0.05376983985510009</v>
+        <v>-0.07140850261076537</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-0.03823427181090722</v>
+        <v>-0.05594371126144182</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.2085944844876195</v>
+        <v>-0.2261935119013287</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.1376361456750672</v>
+        <v>-0.155185178111104</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.1634875436621996</v>
+        <v>-0.1810019795548499</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.2149888301534233</v>
+        <v>-0.2325244128673916</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.272259196259661</v>
+        <v>-0.2897306126036341</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -25.89</t>
+          <t>X &gt; -25.87</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3112</v>
+        <v>3114</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.05139558385484833</v>
+        <v>-0.05233036702048111</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.3055932166914133</v>
+        <v>-0.3061918760447071</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.3867169628907092</v>
+        <v>-0.3865124150100243</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.4617367213090375</v>
+        <v>-0.4433275038825926</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.3159876625132227</v>
+        <v>-0.2822533103562819</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.5261993840686756</v>
+        <v>-0.4926736628715389</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.5142094290387718</v>
+        <v>-0.4797764702505987</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.3270992559599222</v>
+        <v>-0.3105606219388051</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.1074363353596297</v>
+        <v>-0.1412370705769916</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.03122588424586326</v>
+        <v>-0.06468252374171612</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.09027672589572688</v>
+        <v>-0.1238520701420853</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.1268098099084014</v>
+        <v>-0.1602281216460142</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.1120110633556877</v>
+        <v>-0.1448617176128053</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.05817830014772341</v>
+        <v>-0.09095980020536842</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.1213334929310363</v>
+        <v>-0.1537412723636251</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.1160129252311251</v>
+        <v>-0.148748859511187</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.2631162131847731</v>
+        <v>-0.295699976587926</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-0.1886865223752139</v>
+        <v>-0.2212753233161351</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-0.1459385662332053</v>
+        <v>-0.1786807748742874</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.2607509627727822</v>
+        <v>-0.2614584791286063</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.2071249675854361</v>
+        <v>-0.2075836464079259</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.2639049829449931</v>
+        <v>-0.2642894665650601</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-0.2911759936290395</v>
+        <v>-0.2916896111351903</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.3480208662186826</v>
+        <v>-0.3484602248512871</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -23.21</t>
+          <t>X &gt; -23.2</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3038</v>
+        <v>3042</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.0291393854827362</v>
+        <v>-0.03327283984398122</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.4448757300746564</v>
+        <v>-0.448517445419931</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.4277347086552794</v>
+        <v>-0.4316109451316237</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.6181390784398744</v>
+        <v>-0.6037211632620441</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.3291726842032077</v>
+        <v>-0.3002429611388422</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.5162885398487447</v>
+        <v>-0.4873244714143681</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.4198176482268821</v>
+        <v>-0.3905168266180041</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.2541372104600725</v>
+        <v>-0.2434747548516114</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.06288705456393728</v>
+        <v>-0.07114033708477052</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.06434765749336435</v>
+        <v>-0.07271669575334982</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.1970482762070915</v>
+        <v>-0.2052088397800631</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.194944399862429</v>
+        <v>-0.2031534817979477</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.152517144676402</v>
+        <v>-0.1609508103085204</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.09201655915459384</v>
+        <v>-0.1005670685023858</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.1407137312080593</v>
+        <v>-0.1493018529641219</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.1497267491616228</v>
+        <v>-0.1582215598608983</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-0.2643165473830749</v>
+        <v>-0.2726859335029133</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.1855256970542243</v>
+        <v>-0.1940191149575625</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.1469928590446798</v>
+        <v>-0.1555105907134049</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.3020216962524671</v>
+        <v>-0.3103138113301185</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.2667699584882541</v>
+        <v>-0.2751931800159326</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.3231028330616184</v>
+        <v>-0.3314684874803788</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.4235593044104959</v>
+        <v>-0.4317579415242747</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.4141498138587636</v>
+        <v>-0.4223772173987825</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -20.54</t>
+          <t>X &gt; -20.52</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2950</v>
+        <v>2954</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.01398906915658671</v>
+        <v>0.008665163729148162</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.4041756265945864</v>
+        <v>-0.4090021082824578</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.6124621637195418</v>
+        <v>-0.6172781004963781</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.7532861476238608</v>
+        <v>-0.7393915930501294</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.5118825251656034</v>
+        <v>-0.4839435322908301</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.6280546158999698</v>
+        <v>-0.5813511858428768</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.4909106367305327</v>
+        <v>-0.4245185855805857</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.2783584544119435</v>
+        <v>-0.2308729356252002</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.01850801809563052</v>
+        <v>0.04654279364372371</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.02747000110822739</v>
+        <v>-0.01858724033007775</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.1384981231282651</v>
+        <v>-0.1489765364896911</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.2293031074259915</v>
+        <v>-0.2397171827863573</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.1184346273241701</v>
+        <v>-0.1292124764661011</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.1171105507840124</v>
+        <v>-0.1279378950040666</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.04628237511766997</v>
+        <v>-0.05733397601390067</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.1408477928651806</v>
+        <v>-0.1516686104802218</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.2210360957204074</v>
+        <v>-0.2317802667555</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.1367596513803946</v>
+        <v>-0.14764399968481</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.03186483382119576</v>
+        <v>0.02078567485587257</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.2009986459038586</v>
+        <v>-0.2117351990488459</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.148474706322709</v>
+        <v>-0.159389928928789</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.2041825649115694</v>
+        <v>-0.2150434431597361</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-0.2819014774197015</v>
+        <v>-0.2926130398804361</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.2698979086133377</v>
+        <v>-0.2806467074582883</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -17.86</t>
+          <t>X &gt; -17.85</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2824</v>
+        <v>2827</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.01472661335107972</v>
+        <v>-0.03803516264110129</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.2958157517925173</v>
+        <v>-0.3188025334414135</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.5387545122531705</v>
+        <v>-0.5420284690786872</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.8301613418138132</v>
+        <v>-0.8134372335982292</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.737845769569283</v>
+        <v>-0.7073716133096468</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.7618743983787581</v>
+        <v>-0.712040985015264</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.7955641840758716</v>
+        <v>-0.74455304918731</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.4909081965600421</v>
+        <v>-0.4593842122502494</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.4293493670250115</v>
+        <v>-0.4178970303355456</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.302225845019521</v>
+        <v>-0.310531016231181</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.3952185658675305</v>
+        <v>-0.4237953177312406</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.3719658338840262</v>
+        <v>-0.4005513591047105</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.3120629060588342</v>
+        <v>-0.3406051989376948</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.1244776567749781</v>
+        <v>-0.1532088351591554</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.197686784621979</v>
+        <v>-0.2262841737274073</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.3229881533927852</v>
+        <v>-0.3515311848645126</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.3655184064626198</v>
+        <v>-0.3940163649666104</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.1315238490116144</v>
+        <v>-0.1602726714204366</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.03498695729579282</v>
+        <v>0.006024141050168907</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.3226661951909477</v>
+        <v>-0.3512845570811862</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.2436337305402247</v>
+        <v>-0.2722920561205413</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.2984725205499714</v>
+        <v>-0.3270789960621769</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.3211502096628607</v>
+        <v>-0.3497764792120464</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.3760581813362478</v>
+        <v>-0.4046324825034944</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -15.18</t>
+          <t>X &gt; -15.17</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2701</v>
+        <v>2704</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.2258050107319178</v>
+        <v>0.2166106382212263</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.4943907739100268</v>
+        <v>-0.5026360396759344</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.4986845394315722</v>
+        <v>-0.4871723725774757</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.9180354529191774</v>
+        <v>-0.8856995915096562</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.8048363384216941</v>
+        <v>-0.7596648626629801</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.691282325341291</v>
+        <v>-0.6258077223550202</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.948874257910596</v>
+        <v>-0.882482206760649</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.5808291656736913</v>
+        <v>-0.5350035521394148</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.5552204717443985</v>
+        <v>-0.5303216701879023</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.4606713651554912</v>
+        <v>-0.4567154470709198</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.4967934969978316</v>
+        <v>-0.5139035045777405</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.3491346411700391</v>
+        <v>-0.3665597391219393</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.3457098744162366</v>
+        <v>-0.3634989183494568</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.250126407969617</v>
+        <v>-0.2681366146931552</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.3334854461021806</v>
+        <v>-0.3515884990855938</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.3441120048811541</v>
+        <v>-0.362027353177794</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.4193970629593764</v>
+        <v>-0.4372548296548899</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-0.09597922758403143</v>
+        <v>-0.1143588695362112</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-0.005666716137994854</v>
+        <v>-0.02412489136531804</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.3883136094674597</v>
+        <v>-0.4061607510656131</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.31775645783258</v>
+        <v>-0.3358884643332445</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.4086632366612903</v>
+        <v>-0.4266965930286588</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.4080141374772026</v>
+        <v>-0.4259751474020774</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.6320487755239057</v>
+        <v>-0.6278341536249528</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -12.51</t>
+          <t>X &gt; -12.5</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2566</v>
+        <v>2567</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.3150342875102439</v>
+        <v>0.2678216172181891</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.2525192286832691</v>
+        <v>-0.2783726535549178</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.5690593519483471</v>
+        <v>-0.5724345952047187</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.08920433051717</v>
+        <v>-1.070417204974611</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.144636780142307</v>
+        <v>-1.074790553577976</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.151120501759841</v>
+        <v>-1.081622817092999</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.994474627617123</v>
+        <v>-0.9620986327663061</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.8250946402902315</v>
+        <v>-0.8139534883720856</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.5290951558850381</v>
+        <v>-0.5399081669225083</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.4278542946783759</v>
+        <v>-0.4601106646644268</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.5190121797359168</v>
+        <v>-0.5348882318048211</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.2325914287497497</v>
+        <v>-0.2873685146574303</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.2864705435099424</v>
+        <v>-0.3407965508168473</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.3295875909309558</v>
+        <v>-0.3838218513353056</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.3050900688695961</v>
+        <v>-0.3591149475405828</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.5029452699947896</v>
+        <v>-0.5570756104736603</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.5752053153963104</v>
+        <v>-0.629255132315464</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>0.04291433277408174</v>
+        <v>-0.01160288667129095</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.1655826635235371</v>
+        <v>0.1108580323260568</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.2858602569092952</v>
+        <v>-0.3403345001944871</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.338761156661505</v>
+        <v>-0.3930108692813619</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.2356825390464863</v>
+        <v>-0.2900108778223114</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.2493880923907028</v>
+        <v>-0.3038406439729826</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.4422429156809926</v>
+        <v>-0.4344661210402307</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -9.833</t>
+          <t>X &gt; -9.823</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2405</v>
+        <v>2408</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.1688538008607665</v>
+        <v>0.1545324245218254</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.7448341104777683</v>
+        <v>-0.7771096732345271</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.4489973844812525</v>
+        <v>-0.4590599715477097</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.12146838362483</v>
+        <v>-1.10800961966072</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.073515028153011</v>
+        <v>-1.007841998257334</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.258251241592504</v>
+        <v>-1.192776638606233</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.080704150506044</v>
+        <v>-1.014312099356097</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.8633910274295502</v>
+        <v>-0.7966557755141181</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.5504698670700776</v>
+        <v>-0.5072347093019047</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.4323283007033751</v>
+        <v>-0.4123817902970615</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.3823412687174041</v>
+        <v>-0.3862560324326623</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.1823507618209632</v>
+        <v>-0.2104599813352124</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.2062428002387193</v>
+        <v>-0.2348823873110319</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.2788640607148238</v>
+        <v>-0.307512140792241</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.3330724010375832</v>
+        <v>-0.3619738378542792</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.5009472280758729</v>
+        <v>-0.5292996187035897</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.4861242309679596</v>
+        <v>-0.5145871915605653</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.09735171364692263</v>
+        <v>0.06785007765682138</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.2137968021379706</v>
+        <v>0.1841875028779327</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.1972591362126224</v>
+        <v>-0.2261156295535258</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.2173279536593569</v>
+        <v>-0.2464388186767223</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>0.06403239903358582</v>
+        <v>0.03439647508798771</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>0.07271949394136357</v>
+        <v>0.04318356043184224</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>0.07993823783297671</v>
+        <v>0.07519716210762084</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -7.157</t>
+          <t>X &gt; -7.148</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2223</v>
+        <v>2224</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.01385356072215416</v>
+        <v>-0.02477568486053627</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.081268310649932</v>
+        <v>-1.139536372701833</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.5540487926171593</v>
+        <v>-0.5879056953972182</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.401950286409331</v>
+        <v>-1.410459295856768</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.543706437101683</v>
+        <v>-1.498165628115842</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.356541824094897</v>
+        <v>-1.311199442018463</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.414164326287505</v>
+        <v>-1.367584619647644</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.02217806881098</v>
+        <v>-0.9749552772808556</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.6871154301843916</v>
+        <v>-0.6204090613768898</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.7197142927873514</v>
+        <v>-0.6777612311521963</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.3748962424579503</v>
+        <v>-0.3589788698489471</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.5386854524785534</v>
+        <v>-0.548282835014291</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.4276969733058067</v>
+        <v>-0.4376581381944646</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.4433943648535745</v>
+        <v>-0.4533891168884097</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.3583651445661999</v>
+        <v>-0.3686069547837079</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-0.5888879640550186</v>
+        <v>-0.6435320951450052</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.6516395568196174</v>
+        <v>-0.7062586606861032</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>0.1230454348020373</v>
+        <v>0.06732994286760174</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.2762311369941202</v>
+        <v>0.2203122994551734</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.04073033707865648</v>
+        <v>-0.01487381349913619</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>0.01884995071427653</v>
+        <v>-0.03685830934747969</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>0.3747154305461251</v>
+        <v>0.3184778520997682</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>0.4245693194753954</v>
+        <v>0.3953087837283675</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>0.2586594691857869</v>
+        <v>0.2565470987695875</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -4.482</t>
+          <t>X &gt; -4.473</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2037</v>
+        <v>2039</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.1619262837995734</v>
+        <v>-0.1841772010658502</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.082467652102437</v>
+        <v>-1.126135358445204</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.5709486039934504</v>
+        <v>-0.5890815573039987</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.040839478162219</v>
+        <v>-1.031521407364238</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.406109263186266</v>
+        <v>-1.340436233290589</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.511627577008746</v>
+        <v>-1.446152974022475</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.9674205383310621</v>
+        <v>-0.9010284871811152</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.4167068911667116</v>
+        <v>-0.3499716392512795</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.3264103383392012</v>
+        <v>-0.2597039695316994</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.3891552707074979</v>
+        <v>-0.3496928162998927</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.2330892258957249</v>
+        <v>-0.2219746375526057</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.1909241222870861</v>
+        <v>-0.2080411141713299</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.1140769016212104</v>
+        <v>-0.1604714737103734</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.3065145024129095</v>
+        <v>-0.3527439127514498</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>0.0908990257496356</v>
+        <v>0.0433379833600398</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>0.03017104253875402</v>
+        <v>-0.01683912895442319</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.07475063354413436</v>
+        <v>-0.1216981731456031</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>0.7313871815751369</v>
+        <v>0.6827432335141523</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.6830542435952509</v>
+        <v>0.6346381359864353</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>0.605382540461008</v>
+        <v>0.5572290274843397</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>0.3860194143582802</v>
+        <v>0.3378282790320668</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>0.7324032000624285</v>
+        <v>0.6834355719427165</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>0.7617193581989525</v>
+        <v>0.7425218262487476</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>0.6366862172613637</v>
+        <v>0.6472644415211803</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -1.806</t>
+          <t>X &gt; -1.798</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.7214829898535982</v>
+        <v>0.6699711183088297</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.4928134039116046</v>
+        <v>-0.4591403952982631</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.3940523295362013</v>
+        <v>-0.3586979058677144</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.27268080756452</v>
+        <v>-1.206311108897623</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.967620922258909</v>
+        <v>-1.92692840937233</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-2.055181583977394</v>
+        <v>-2.014838528937403</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.729146617130318</v>
+        <v>-1.687281990177944</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.183525438473055</v>
+        <v>-1.140864517943662</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.6475038789449314</v>
+        <v>-0.6045999858365505</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.5105623261611427</v>
+        <v>-0.4979114837531995</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.2595176499881333</v>
+        <v>-0.2788271027237599</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.1767013943678748</v>
+        <v>-0.2277249393768201</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.05782660556702268</v>
+        <v>-0.1414312613181465</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.02891357251283466</v>
+        <v>-0.05500550055005249</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>0.450194093250289</v>
+        <v>0.3651951397304245</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.1961556012231185</v>
+        <v>0.111800827659863</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.1257221738035454</v>
+        <v>-0.209674712735044</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>0.6856651783886747</v>
+        <v>0.6002552225804507</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.6589506795176874</v>
+        <v>0.5736252080459181</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.2382596685082916</v>
+        <v>0.1865561110810603</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>0.3913628856399711</v>
+        <v>0.3394777916686849</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>0.6806232964213805</v>
+        <v>0.6283764388669013</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>0.7341595248504191</v>
+        <v>0.7152074178983483</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>0.4369792475288463</v>
+        <v>0.4182585256479854</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.8692</t>
+          <t>X &gt; 0.8769</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.7129352215049636</v>
+        <v>0.712386717413807</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.1822900753422303</v>
+        <v>-0.1820915734733219</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.8752574964912156</v>
+        <v>-0.8738419657878964</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-2.771378127668193</v>
+        <v>-2.735184410249289</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-3.385558927004624</v>
+        <v>-3.319885897108946</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-3.073938806841653</v>
+        <v>-3.008464203855382</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-2.851160881646145</v>
+        <v>-2.784768830496198</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.885160455602787</v>
+        <v>-1.818425203687354</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.532505622689669</v>
+        <v>-1.465799253882167</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.9639884214045935</v>
+        <v>-0.9319321047786531</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.214762707204137</v>
+        <v>-1.217922244819583</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.8351062902185049</v>
+        <v>-0.8743941124866197</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.676194973247668</v>
+        <v>-0.7530011077808254</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.424032641413973</v>
+        <v>-0.5018310050183032</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.01575641062773059</v>
+        <v>-0.0640838916399602</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.02341015169194804</v>
+        <v>-0.05573188241517357</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-0.448668220380668</v>
+        <v>-0.5268829775415682</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.2969269087819271</v>
+        <v>0.2166388224631817</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.2001589578213725</v>
+        <v>0.1576551837953488</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.2385794743429273</v>
+        <v>-0.2432176196032785</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>0.006658701834851399</v>
+        <v>0.001642403800303782</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>0.3690254996675222</v>
+        <v>0.4012970094696584</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>0.3307136279530241</v>
+        <v>0.3628806080593492</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.3800071039632087</v>
+        <v>0.4122048003930132</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 3.545</t>
+          <t>X &gt; 3.552</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.1883874532144816</v>
+        <v>0.2598621064261906</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.7137618388926441</v>
+        <v>-0.6422905784484456</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.4525409705903982</v>
+        <v>-0.3781819679049718</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-3.079870782720484</v>
+        <v>-3.006029604368983</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-3.586884012110225</v>
+        <v>-3.48366404854746</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-2.903617343823498</v>
+        <v>-2.800243961740868</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.755151087500487</v>
+        <v>-2.650206830028388</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.616271289362075</v>
+        <v>-1.509978558469406</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.149524891242343</v>
+        <v>-1.042959461661084</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.8905934398195754</v>
+        <v>-0.8229673362791345</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.001447769188836</v>
+        <v>-0.9744396090108296</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.3168706293706265</v>
+        <v>-0.3312031968559879</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.3341745699615331</v>
+        <v>-0.3905354764780569</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.3002542207697871</v>
+        <v>-0.3569696927109263</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>0.5064194970883733</v>
+        <v>0.4472797447236729</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>0.5748702656520734</v>
+        <v>0.5160883892227162</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-0.12902399829742</v>
+        <v>-0.1441546472149824</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>0.2360882089459722</v>
+        <v>0.22037081228018</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-0.1179953280509309</v>
+        <v>-0.09085402786189434</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.5011582323592307</v>
+        <v>-0.4318758519625021</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-0.4028761039373734</v>
+        <v>-0.3329394825087206</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>0.02009970285765661</v>
+        <v>0.1329515919631064</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>0.009771519375419757</v>
+        <v>0.1221195997376014</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>0.07638185508913864</v>
+        <v>0.1889406988681159</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 6.22</t>
+          <t>X &gt; 6.227</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.4963257500790306</v>
+        <v>-0.4202351971678766</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.6706002188665607</v>
+        <v>-0.5939813997044823</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.7426417931699234</v>
+        <v>-0.6632403843232382</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-3.387247656644647</v>
+        <v>-3.308561553524434</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-3.430715349955094</v>
+        <v>-3.322290834445297</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-3.243550736948308</v>
+        <v>-3.135324648347918</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-2.890109548004759</v>
+        <v>-2.780059161545843</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.479203212026938</v>
+        <v>-1.367449350260266</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.9549840094339075</v>
+        <v>-0.842870380905957</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.039289777230067</v>
+        <v>-0.9716636736896263</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.8800913914879942</v>
+        <v>-0.8586346273409049</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.4680803067899788</v>
+        <v>-0.4932616475360803</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.2546689503597861</v>
+        <v>-0.4086942457931713</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.05628376437120153</v>
+        <v>-0.09893011863635337</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>1.012861410632766</v>
+        <v>0.9036580438439046</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>0.7681049778843558</v>
+        <v>0.6594394306258664</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.3106483087960683</v>
+        <v>0.2509900936486602</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>0.7715500988446777</v>
+        <v>0.7604215031664694</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.502628799367443</v>
+        <v>0.4912684216817382</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.3612570735650777</v>
+        <v>-0.3251350953314329</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-0.2577315326842893</v>
+        <v>-0.2204320723589461</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>0.1513578740821444</v>
+        <v>0.1891588594358353</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-0.05891142184476905</v>
+        <v>-0.0218033212859936</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>0.1076694700912881</v>
+        <v>0.1450828720926722</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 8.896</t>
+          <t>X &gt; 8.902</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1067</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.5957631967955734</v>
+        <v>-0.5624889044767443</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.21078945770855</v>
+        <v>-1.177116449095209</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.810937682988722</v>
+        <v>-1.775583259320236</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-3.830701145435611</v>
+        <v>-3.794507428016708</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-3.449702273743242</v>
+        <v>-3.384029243847564</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-3.728955571184216</v>
+        <v>-3.663480968197945</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-3.102567971894956</v>
+        <v>-3.036175920745009</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.702018139801581</v>
+        <v>-1.635282887886149</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.6343826717938725</v>
+        <v>-0.5676763029863707</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.8884081685479472</v>
+        <v>-0.8741740685750941</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.09326738010133084</v>
+        <v>-0.1336965159654113</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.1493945717519125</v>
+        <v>0.05397199103435213</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.5775988262995284</v>
+        <v>0.4233472376110754</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.9180397680741663</v>
+        <v>0.8181490417949391</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>1.663602911059336</v>
+        <v>1.618159099014242</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>1.566814556565433</v>
+        <v>1.521883947047655</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>1.3390001501391</v>
+        <v>1.351442073100841</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>1.702620295430876</v>
+        <v>1.714766163287145</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>1.075257047865975</v>
+        <v>1.087960914997986</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-0.04978912839737148</v>
+        <v>0.01949325199935714</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.1243859760082628</v>
+        <v>-0.05444935457961009</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>0.6431453788458441</v>
+        <v>0.7131910945080051</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>0.4493169839409106</v>
+        <v>0.5190622456029956</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>0.4670963569498596</v>
+        <v>0.5369507046571371</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 11.57</t>
+          <t>X &gt; 11.58</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>921</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.6438183754477649</v>
+        <v>-0.6105440831289357</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.628344539442736</v>
+        <v>-1.594671530829395</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.985793921277789</v>
+        <v>-1.950439497609302</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-4.214738749622477</v>
+        <v>-4.178545032203573</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-3.930657885295865</v>
+        <v>-3.864984855400188</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-4.392843921639738</v>
+        <v>-4.327369318653467</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-3.434108322092023</v>
+        <v>-3.367716270942076</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.981061236008856</v>
+        <v>-1.914325984093423</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.181969413410464</v>
+        <v>-1.115263044602962</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.84757971595478</v>
+        <v>-1.779953612414339</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.4288249382467555</v>
+        <v>-0.4236428880013463</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.2118001304552237</v>
+        <v>-0.2694918585488963</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.1876294917231291</v>
+        <v>-0.3104028431539305</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.133901862280517</v>
+        <v>0.00964382152501031</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>0.6693245863268231</v>
+        <v>0.6076387519136688</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>0.3957635718874002</v>
+        <v>0.4001511864852461</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>0.04451461172327242</v>
+        <v>0.1140840475057985</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>0.4824193606660003</v>
+        <v>0.5521315087226242</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.1700785404629883</v>
+        <v>-0.1005981744138538</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-1.394543973941367</v>
+        <v>-1.325261593544639</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-1.177700951886116</v>
+        <v>-1.107764330457464</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-0.8193454754983236</v>
+        <v>-0.7492997598361626</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-0.9788808410465961</v>
+        <v>-0.9091355793845111</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-1.163399813322663</v>
+        <v>-1.093545465615385</v>
       </c>
     </row>
     <row r="26">
@@ -4827,158 +4827,158 @@
         <v>759</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.705617468742929</v>
+        <v>-1.6723431764241</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-2.434493770788826</v>
+        <v>-2.400820762175485</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-2.824325468470761</v>
+        <v>-2.788971044802274</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-4.45675395226759</v>
+        <v>-4.420560234848686</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-4.953257333092168</v>
+        <v>-4.887584303196491</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-5.159793507486953</v>
+        <v>-5.094318904500682</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-3.964155702533098</v>
+        <v>-3.897763651383151</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-2.011739219442745</v>
+        <v>-1.945003967527313</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-2.101456750220628</v>
+        <v>-2.034750381413126</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.219124181987439</v>
+        <v>-2.151498078446998</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.6886472909417165</v>
+        <v>-0.6963360740803495</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.6293706293706336</v>
+        <v>-0.7126182859272916</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.151095049438801</v>
+        <v>-1.310845969581315</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.5819380264810547</v>
+        <v>-0.7445232712247574</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.1868508201955663</v>
+        <v>-0.2743335631248485</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-0.5140569102316306</v>
+        <v>-0.5223285486443459</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.5163982987152096</v>
+        <v>-0.4468288629326835</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.09437249214908405</v>
+        <v>-0.02466034409246021</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-1.327524691536105</v>
+        <v>-1.258044325486971</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-2.853260869565219</v>
+        <v>-2.78397848916849</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-3.264708972897822</v>
+        <v>-3.194772351469169</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-2.81365480587904</v>
+        <v>-2.743609090216879</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-2.670631945062254</v>
+        <v>-2.600886683400169</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-2.878325589996066</v>
+        <v>-2.808471242288789</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 16.92</t>
+          <t>X &gt; 16.93</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>628</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.851617443785656</v>
+        <v>-1.818343151466827</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-2.186792958429983</v>
+        <v>-2.153119949816642</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-2.358664579409947</v>
+        <v>-2.32331015574146</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-4.815722551874103</v>
+        <v>-4.779528834455199</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-4.071642099180245</v>
+        <v>-4.005969069284568</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-5.152306329279632</v>
+        <v>-5.086831726293362</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-4.023429196674392</v>
+        <v>-3.957037145524446</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-3.192633604475041</v>
+        <v>-3.125898352559609</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-2.675681723287589</v>
+        <v>-2.608975354480087</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.657124107115656</v>
+        <v>-2.589498003575216</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.024879900498902</v>
+        <v>-1.047609518307112</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.372613872613869</v>
+        <v>-1.484837527143377</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.929021083526564</v>
+        <v>-2.132563777834683</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.354199550611867</v>
+        <v>-1.561249627339912</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-1.057716776910311</v>
+        <v>-1.175195002751067</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-1.258835071237982</v>
+        <v>-1.282097605627015</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.9152217590174772</v>
+        <v>-0.8456523232349511</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.7017338375331335</v>
+        <v>-0.6320216894765096</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-2.237203031289226</v>
+        <v>-2.167722665240092</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-3.642515923566883</v>
+        <v>-3.573233543170154</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-3.867244994985214</v>
+        <v>-3.797308373556561</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-3.147021706678778</v>
+        <v>-3.076975991016617</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-2.553775202617025</v>
+        <v>-2.48402994095494</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-3.107423548254928</v>
+        <v>-3.037569200547651</v>
       </c>
     </row>
     <row r="28">
@@ -4988,161 +4988,161 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-1.082950580414895</v>
+        <v>-0.9485394211242735</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-1.418126095059222</v>
+        <v>-1.283316219474088</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-2.473949399836343</v>
+        <v>-2.336719883889693</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-4.915189929920096</v>
+        <v>-4.780443134101674</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-4.3207668166716</v>
+        <v>-4.154695145110473</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-5.093295101937358</v>
+        <v>-4.929267420551568</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-3.562898278137261</v>
+        <v>-3.393523796749605</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-4.033391503310327</v>
+        <v>-3.864042933810374</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-3.03218254001515</v>
+        <v>-2.861017290357211</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-3.038263632166533</v>
+        <v>-2.864702197162927</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.5425844182034183</v>
+        <v>-0.475257939616391</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.867328240160603</v>
+        <v>-1.907853496910541</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-2.413784776566828</v>
+        <v>-2.454092486843585</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-2.249785132880568</v>
+        <v>-2.290555978674789</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-1.559968780395707</v>
+        <v>-1.489902774106241</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-1.542943412855259</v>
+        <v>-1.361588861588864</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.9063241975629381</v>
+        <v>-0.7233052263655537</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.4332729315772994</v>
+        <v>-0.2489953510361644</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-2.914644951689795</v>
+        <v>-2.73580667281454</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-4.461705202312139</v>
+        <v>-4.286412600298249</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-4.812227383949782</v>
+        <v>-4.635908575214089</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-4.69550421223208</v>
+        <v>-4.518704343572999</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-3.650016136308722</v>
+        <v>-3.47202885889017</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-4.496670385018419</v>
+        <v>-4.320061884314221</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 22.27</t>
+          <t>X &gt; 22.28</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>417</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-2.12280875658611</v>
+        <v>-2.089534464267281</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.3100129108485774</v>
+        <v>-0.276339902235236</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-1.988376859421592</v>
+        <v>-1.953022435753105</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-4.134151079535989</v>
+        <v>-4.097957362117086</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-3.544766926612546</v>
+        <v>-3.479093896716869</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-4.550919736040129</v>
+        <v>-4.485445133053858</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-3.41447799219916</v>
+        <v>-3.348085941049213</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-3.215705668743979</v>
+        <v>-3.148970416828547</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-2.219535665773847</v>
+        <v>-2.152829296966345</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-2.038717138595786</v>
+        <v>-1.971091035055345</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.4340087833119952</v>
+        <v>-0.503713970459053</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.774454562224335</v>
+        <v>-1.975780796341418</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-3.378562087665927</v>
+        <v>-3.576269832171285</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-1.44164551740532</v>
+        <v>-1.649377348236015</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-1.14134414253374</v>
+        <v>-1.212409250491639</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-1.025900399866792</v>
+        <v>-0.9565075212557161</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.4405696335840688</v>
+        <v>-0.3710001978015427</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.06593674272491512</v>
+        <v>0.003775405331708725</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-1.768278807610848</v>
+        <v>-1.698798441561713</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-3.499700239808156</v>
+        <v>-3.430417859411428</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-3.803092495328897</v>
+        <v>-3.733155873900245</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-4.35866385792594</v>
+        <v>-4.288618142263779</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-3.604272384489377</v>
+        <v>-3.534527122827292</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-4.639446337666712</v>
+        <v>-4.569591989959434</v>
       </c>
     </row>
     <row r="30">
@@ -5155,158 +5155,158 @@
         <v>331</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.5209682525976405</v>
+        <v>-0.4876939602788113</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.2555431666413668</v>
+        <v>-0.2218701580280253</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-2.596144531628411</v>
+        <v>-2.560790107959924</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-2.709337244220961</v>
+        <v>-2.673143526802058</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-2.474006428644408</v>
+        <v>-2.408333398748731</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-3.788343317139123</v>
+        <v>-3.722868714152852</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-2.459107347091049</v>
+        <v>-2.392715295941102</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-3.037962292909917</v>
+        <v>-2.971227040994485</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-2.696145927586976</v>
+        <v>-2.629439558779474</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-2.569080437455504</v>
+        <v>-2.501454333915063</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-1.223770701799332</v>
+        <v>-1.32649379085224</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-3.446591173177275</v>
+        <v>-3.707345296402345</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-5.477426802540556</v>
+        <v>-5.731408264159356</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-3.583979988197257</v>
+        <v>-3.850385038503845</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-2.732337209107676</v>
+        <v>-2.835168228989353</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-2.439391963111667</v>
+        <v>-2.369999084500591</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-1.969256050009839</v>
+        <v>-1.899686614227313</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.5636654479782379</v>
+        <v>-0.4939532999216141</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-3.066575517674821</v>
+        <v>-2.997095151625686</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-4.390105740181269</v>
+        <v>-4.320823359784541</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-4.933306149179224</v>
+        <v>-4.863369527750571</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-5.613490812072584</v>
+        <v>-5.543445096410423</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-5.036600841965083</v>
+        <v>-4.966855580302997</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-6.018886592109688</v>
+        <v>-5.94903224440241</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 27.62</t>
+          <t>X &gt; 27.63</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>250</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.6909579593285642</v>
+        <v>0.7242322516473934</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>1.149433238335043</v>
+        <v>1.183106246948384</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-2.671219606703481</v>
+        <v>-2.635865183034994</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-1.400885935769651</v>
+        <v>-1.364692218350747</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-1.369330323968299</v>
+        <v>-1.303657294072622</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-5.150419679215489</v>
+        <v>-5.084945076229218</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-3.542333430317136</v>
+        <v>-3.475941379167189</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-3.820888075835697</v>
+        <v>-3.754152823920265</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-2.192070423511467</v>
+        <v>-2.125364054703965</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-2.569080437455504</v>
+        <v>-2.501454333915063</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.4797587976088664</v>
+        <v>-0.6400931044515588</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-1.329370629370629</v>
+        <v>-1.712493301550346</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-3.653861847857762</v>
+        <v>-4.026131558882646</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-2.275218658892129</v>
+        <v>-2.659908848027655</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-1.334149897929429</v>
+        <v>-1.49834683984713</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-1.539089848308052</v>
+        <v>-1.469696969696976</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-1.673183542456975</v>
+        <v>-1.603614106674449</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.1781669585522536</v>
+        <v>-0.1084548104956298</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-3.562043795620426</v>
+        <v>-3.492563429571291</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-3.774999999999991</v>
+        <v>-3.705717619603263</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-4.318200408997946</v>
+        <v>-4.248263787569293</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-5.194155464640559</v>
+        <v>-5.124109748978398</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-5.319380298158428</v>
+        <v>-5.249635036496343</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-6.595321637426899</v>
+        <v>-6.525467289719622</v>
       </c>
     </row>
     <row r="32">
@@ -5319,76 +5319,76 @@
         <v>190</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2.055045260915868</v>
+        <v>2.088319553234697</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.6782030796048772</v>
+        <v>0.7118760882182187</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-1.803164051147924</v>
+        <v>-1.767809627479437</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-3.037790697674417</v>
+        <v>-3.001596980255513</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-2.3613938160318</v>
+        <v>-2.295720786136123</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-8.424229203025007</v>
+        <v>-8.358754600038736</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-5.551262001745705</v>
+        <v>-5.484869950595758</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-5.829816647264266</v>
+        <v>-5.763081395348834</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-3.704967248908297</v>
+        <v>-3.638260880100795</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-2.395469326344397</v>
+        <v>-2.327843222803956</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.782213898670598</v>
+        <v>-1.012116913975362</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-1.813581155686421</v>
+        <v>-2.33253298409003</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-4.517019742594606</v>
+        <v>-5.018195050946147</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-2.633113395734235</v>
+        <v>-3.155940594059402</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-1.713097266350474</v>
+        <v>-1.94890064556666</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-2.696984585150155</v>
+        <v>-2.627591706539079</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-2.831078279299078</v>
+        <v>-2.761508843516552</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-1.357114326973296</v>
+        <v>-1.287402178916672</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-4.825201690357268</v>
+        <v>-4.755721324308134</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-4.11184210526315</v>
+        <v>-4.042559724866422</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-4.655042514261105</v>
+        <v>-4.585105892832452</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-6.309944938324776</v>
+        <v>-6.239899222662615</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-6.561485561316331</v>
+        <v>-6.491740299654246</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-7.163742690058484</v>
+        <v>-7.093888342351207</v>
       </c>
     </row>
     <row r="33">
@@ -5401,76 +5401,76 @@
         <v>135</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.472937417778617</v>
+        <v>1.506211710097446</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>1.873056020781348</v>
+        <v>1.90672902939469</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>3.37453202728345</v>
+        <v>3.409886450951937</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-1.751025991792069</v>
+        <v>-1.714832274373165</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.08958657612506471</v>
+        <v>0.1552596060207421</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-5.60560175204462</v>
+        <v>-5.54012714905835</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-1.966703178216292</v>
+        <v>-1.900311127066345</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-2.980551941381918</v>
+        <v>-2.913816689466486</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.7331535234181032</v>
+        <v>-0.6664471546106014</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-2.977577169481648</v>
+        <v>-2.909951065941208</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-3.035461911080908</v>
+        <v>-3.37118554142635</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-3.31455581455581</v>
+        <v>-3.649934944874346</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-6.661269255265182</v>
+        <v>-6.97897936467163</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-2.438181621855087</v>
+        <v>-2.788293535235873</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-3.097112860892388</v>
+        <v>-3.027046854602922</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-5.465015774233969</v>
+        <v>-5.395622895622893</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-4.858368727642151</v>
+        <v>-4.788799291859625</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-4.222611402996691</v>
+        <v>-4.152899254940067</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-6.969451203027845</v>
+        <v>-6.89997083697871</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-6.041666666666664</v>
+        <v>-5.972384286269936</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-6.584867075664619</v>
+        <v>-6.514930454235966</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-9.623785094270197</v>
+        <v>-9.553739378608036</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-10.08975066852881</v>
+        <v>-10.02000540686672</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-10.16569200779728</v>
+        <v>-10.09583766009</v>
       </c>
     </row>
     <row r="34">
@@ -5483,76 +5483,76 @@
         <v>105</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-3.674121405750796</v>
+        <v>-3.640847113431967</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-4.009296920395123</v>
+        <v>-3.975623911781781</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.2113799740093043</v>
+        <v>0.2467343976777912</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-3.332602018429135</v>
+        <v>-3.296408301010231</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.8676831242079004</v>
+        <v>-0.802010094312223</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-5.397499643276582</v>
+        <v>-5.332025040290311</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-1.453384643255141</v>
+        <v>-1.386992592105194</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-2.675335515188799</v>
+        <v>-2.608600263273367</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.747026997335972</v>
+        <v>-0.6803206285284702</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-2.464258634520498</v>
+        <v>-2.396632530980057</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-2.612181487800484</v>
+        <v>-3.06596911523323</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-3.843656343656342</v>
+        <v>-4.288114745096316</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-4.968147562143486</v>
+        <v>-5.411276811952433</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-1.379980563654023</v>
+        <v>-1.858770782738645</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-1.086530850310375</v>
+        <v>-1.016464844020909</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-2.396232705450906</v>
+        <v>-2.32683982683983</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-3.482707351980778</v>
+        <v>-3.413137916198252</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-2.635309815695109</v>
+        <v>-2.565597667638485</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-5.276329509906148</v>
+        <v>-5.206849143857013</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-6.994047619047613</v>
+        <v>-6.924765238650885</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-6.584867075664619</v>
+        <v>-6.514930454235966</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-10.47034594083104</v>
+        <v>-10.40030022516888</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-11.14795172672986</v>
+        <v>-11.07820646506778</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-11.22389306599833</v>
+        <v>-11.15403871829105</v>
       </c>
     </row>
     <row r="35">
@@ -5565,76 +5565,76 @@
         <v>68</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-7.297309811547898</v>
+        <v>-7.264035519229068</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-9.081760688511068</v>
+        <v>-9.048087679897726</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-1.825808978684151</v>
+        <v>-1.790454555015664</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-3.988877654196159</v>
+        <v>-3.952683936777255</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-4.354147439220206</v>
+        <v>-4.288474409324529</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-9.96408427548878</v>
+        <v>-9.898609672502509</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-4.939848958267447</v>
+        <v>-4.8734569071175</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-3.769128241467158</v>
+        <v>-3.702392989551726</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.6202139105119926</v>
+        <v>0.6869202793194944</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>1.2956538620614</v>
+        <v>1.363279965601841</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>2.443840921163094</v>
+        <v>1.637339607763764</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.7764294529000395</v>
+        <v>-1.539960520321912</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.4303324360930603</v>
+        <v>-1.213847224859187</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-2.122277482421538</v>
+        <v>-2.88420146362462</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>1.630555984423516</v>
+        <v>1.700621990712982</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>0.7550277987507741</v>
+        <v>0.8244206773618501</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-2.320242365986381</v>
+        <v>-2.250672930203855</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>0.515950688506571</v>
+        <v>0.5856628365631948</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.7385143838557227</v>
+        <v>-0.6690340178065881</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-4.963235294117652</v>
+        <v>-4.893952913720923</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-5.506435703115606</v>
+        <v>-5.436499081686954</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-9.994155464640563</v>
+        <v>-9.924109748978402</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-9.719380298158434</v>
+        <v>-9.649635036496349</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-11.26590987272102</v>
+        <v>-11.19605552501374</v>
       </c>
     </row>
   </sheetData>
@@ -5824,1641 +5824,1641 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -39.26</t>
+          <t>X &lt; -39.25</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>68</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-5.848034449229054</v>
+        <v>-5.814760156910225</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>2.512442210039659</v>
+        <v>2.546115218653</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.072741745953522</v>
+        <v>1.108096169622009</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-3.221614227086178</v>
+        <v>-3.952683936777255</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-2.116295776816116</v>
+        <v>-2.839199047005678</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>3.953221777367141</v>
+        <v>3.144868588367054</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>4.650943880607237</v>
+        <v>3.822195266795553</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1.431212764500444</v>
+        <v>1.497948016415876</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-2.939035876359284</v>
+        <v>-2.872329507551783</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.7716948165404744</v>
+        <v>-0.7040687130000336</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-3.438512020013377</v>
+        <v>-3.37118554142635</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-5.188194158782387</v>
+        <v>-5.120523180168455</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.4303324360930603</v>
+        <v>-0.3613323058481015</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-5.063453953009777</v>
+        <v>-4.994175888177054</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-4.251796956752955</v>
+        <v>-4.181730950463489</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.7155604365433348</v>
+        <v>-0.6461675579322588</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>5.032698810484206</v>
+        <v>5.102268246266732</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>1.986538923800694</v>
+        <v>2.056251071857318</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.7320738514383862</v>
+        <v>0.8015542174875208</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>3.860294117647058</v>
+        <v>3.929576498043787</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>4.78768194394322</v>
+        <v>4.857618565371872</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>4.71172688830061</v>
+        <v>4.781772603962771</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>6.457090290076856</v>
+        <v>6.526835551738941</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>7.851737186102518</v>
+        <v>7.921591533809796</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -36.59</t>
+          <t>X &lt; -36.57</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>87</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-3.674121405750796</v>
+        <v>-3.640847113431967</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>2.808884897786697</v>
+        <v>2.842557906400039</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2.505548070064201</v>
+        <v>2.540902493732688</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.9903769045709723</v>
+        <v>-1.581142434800974</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-3.654497264307658</v>
+        <v>-4.189660180075514</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>4.57864436019338</v>
+        <v>3.951851460567319</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3.805778228139353</v>
+        <v>3.179902776676968</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1.228373007908139</v>
+        <v>1.295108259823571</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-2.178386789138187</v>
+        <v>-2.111680420330686</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-1.802796912551294</v>
+        <v>-1.735170809010853</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-6.126138794861241</v>
+        <v>-6.058812316274214</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-6.405232698336143</v>
+        <v>-6.33756171972221</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-2.932022767398003</v>
+        <v>-2.863022637153044</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-5.452230153144995</v>
+        <v>-5.382952088312273</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-4.961736104825981</v>
+        <v>-4.891670098536515</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-2.067825480491955</v>
+        <v>-1.998432601880879</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>1.24635668742809</v>
+        <v>1.315926123210616</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.008052016023505359</v>
+        <v>0.06166013203311849</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-2.090779427804343</v>
+        <v>-2.021299061755208</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>1.544540229885058</v>
+        <v>1.613822610281787</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>2.150765108243426</v>
+        <v>2.220701729672079</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>2.074810052600817</v>
+        <v>2.144855768262978</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>3.499010506439269</v>
+        <v>3.568755768101354</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>4.572494454527124</v>
+        <v>4.642348802234402</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -33.91</t>
+          <t>X &lt; -33.9</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>122</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-2.454609210628846</v>
+        <v>-2.421334918310016</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>2.088264055214637</v>
+        <v>2.121937063827978</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1.461571721209793</v>
+        <v>1.49692614487828</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.4250857796416341</v>
+        <v>-0.842044134727054</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-1.610027695813216</v>
+        <v>-1.990842737355635</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>3.495169704078812</v>
+        <v>3.074172229229553</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>3.541975703172326</v>
+        <v>3.11523167542051</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>2.443748926506224</v>
+        <v>2.510484178421656</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-1.613095664208849</v>
+        <v>-1.546389295401347</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-3.206603206125813</v>
+        <v>-3.138977102585372</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-7.850276725895725</v>
+        <v>-7.782950247308698</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-7.309698498223085</v>
+        <v>-7.242027519609152</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-4.335829060972522</v>
+        <v>-4.266828930727563</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-6.196530134301959</v>
+        <v>-6.127252069469236</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-4.396444979896643</v>
+        <v>-4.326378973607177</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-2.162040667980179</v>
+        <v>-2.092647789369103</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-2.296134362129102</v>
+        <v>-2.226564926346576</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-4.040462040519465</v>
+        <v>-3.970749892462841</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-3.004666746440108</v>
+        <v>-2.935186380390974</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-1.178278688524593</v>
+        <v>-1.108996308127864</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-1.721479097522547</v>
+        <v>-1.651542476093894</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.9777620220176146</v>
+        <v>-0.9077163063554536</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>0.1166852756120562</v>
+        <v>0.1864305372741413</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>3.319432460933754</v>
+        <v>3.389286808641032</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -31.24</t>
+          <t>X &lt; -31.22</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>162</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-1.235097015506895</v>
+        <v>-1.201822723188066</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>3.917532347897556</v>
+        <v>3.951205356510897</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1.868075786250444</v>
+        <v>1.90343020991893</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1.505920958767298</v>
+        <v>1.19047619047619</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.2620629740916556</v>
+        <v>-0.3648264771930272</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>4.152931290802151</v>
+        <v>3.480676294270197</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2.762781208130839</v>
+        <v>2.098971512818871</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>3.718794463846848</v>
+        <v>3.410614923669577</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.05660682516577253</v>
+        <v>0.1233131939732743</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-1.334512536220942</v>
+        <v>-1.266886432680501</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-3.529289071574738</v>
+        <v>-3.46196259298771</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-2.573815073815069</v>
+        <v>-2.506144095201137</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-1.229170489833074</v>
+        <v>-1.160170359588115</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-3.302379152719283</v>
+        <v>-3.23310108788656</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-2.109458539904729</v>
+        <v>-2.039392533615263</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.2798305890487924</v>
+        <v>-0.2104377104377164</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-1.031208233814986</v>
+        <v>-0.9616387980324603</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-2.370759551144843</v>
+        <v>-2.301047403088219</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.920068486978451</v>
+        <v>-0.8505881209293165</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>1.736111111111114</v>
+        <v>1.805393491507843</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>0.5756267514958751</v>
+        <v>0.6455633729245278</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>1.116955646470551</v>
+        <v>1.187001362132712</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>1.39173081295268</v>
+        <v>1.461476074614765</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>2.550357374918775</v>
+        <v>2.620211722626053</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -28.56</t>
+          <t>X &lt; -28.55</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-1.185433622945361</v>
+        <v>-1.388594861179719</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3.456766428021162</v>
+        <v>3.23158329542543</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3.37453202728345</v>
+        <v>3.595366048196233</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>2.019027484143763</v>
+        <v>1.981511127852592</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.3636769210546262</v>
+        <v>-1.056982047397383</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.649971710217002</v>
+        <v>1.382236390952251</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.4204845735967595</v>
+        <v>0.1598372566114534</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1.511792941776832</v>
+        <v>1.497948016415876</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-1.186417020597794</v>
+        <v>-0.9204578497977707</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-1.960252431367223</v>
+        <v>-1.693373525834261</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-3.51237718251673</v>
+        <v>-3.237495701854158</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-2.878229076859206</v>
+        <v>-2.607154196211241</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-1.719615272515306</v>
+        <v>-1.457588990340085</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-2.854214092682085</v>
+        <v>-2.587758775877582</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-1.686661313454543</v>
+        <v>-1.427720255276327</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.1783592547007444</v>
+        <v>0.07575757575757791</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.7690739534158695</v>
+        <v>-0.5127050157653485</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-1.787299378643567</v>
+        <v>-1.526636628677444</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-2.027797220277968</v>
+        <v>-1.765290702298572</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>0.4423515981735164</v>
+        <v>0.6942823803967286</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.5574698153906539</v>
+        <v>-0.3028092421147548</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.176803866467047</v>
+        <v>0.07589025102159752</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>0.5545923045812913</v>
+        <v>0.8049104180491042</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>1.391892974445241</v>
+        <v>1.638169073916742</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -25.89</t>
+          <t>X &lt; -25.87</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.2957430273724171</v>
+        <v>-0.2851424154453923</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.733946322848119</v>
+        <v>1.729074074795399</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.321272885789014</v>
+        <v>2.304477844556359</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2.820260149783216</v>
+        <v>2.598235234509588</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.295068769002214</v>
+        <v>0.9201628827676842</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>3.523049708539617</v>
+        <v>3.120551887657008</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.430455685329129</v>
+        <v>3.019744143363972</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.45122076770172</v>
+        <v>1.260277190509754</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.8882155482280325</v>
+        <v>-0.5273374566773725</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.662050958997462</v>
+        <v>-1.300253132713863</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.047555637460356</v>
+        <v>-0.688355652714101</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.6463774320917182</v>
+        <v>-0.2914293804864201</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.7504604873135534</v>
+        <v>-0.4010779338290291</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.311953352769677</v>
+        <v>-0.959994648113458</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.6103403741199003</v>
+        <v>-0.2667865943426548</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.6955524333420584</v>
+        <v>-0.3480753480753478</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.871034144617866</v>
+        <v>1.207196704136372</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.0857786196790471</v>
+        <v>0.4266803246395057</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-0.3783703262326767</v>
+        <v>-0.03310397011183852</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.8290816326530646</v>
+        <v>0.8294175155318584</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>0.2858812236551103</v>
+        <v>0.2868713475658282</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>0.890198276856033</v>
+        <v>0.8867010618324116</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>1.164973443338162</v>
+        <v>1.161175774314465</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>1.769304212913234</v>
+        <v>1.761019196766867</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -23.21</t>
+          <t>X &lt; -23.2</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>368</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.430878162507554</v>
+        <v>-0.3976038701887248</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>2.477189566091361</v>
+        <v>2.510862574704703</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.118570183086305</v>
+        <v>2.153924606754792</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>3.457805508287642</v>
+        <v>3.332862479203946</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.08063516947545</v>
+        <v>0.8349098444945113</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.62649543465615</v>
+        <v>2.373227381943238</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.853629302602123</v>
+        <v>1.601278698052887</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.4881181353444219</v>
+        <v>0.3979958404235262</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.100800582241632</v>
+        <v>-1.03409421343413</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.059418601706717</v>
+        <v>-0.9917924981662765</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.03015805671296334</v>
+        <v>0.09748453529999068</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.02280328367285733</v>
+        <v>0.09047426228679001</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.2864705435099424</v>
+        <v>-0.2174704132649836</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.7795664849790782</v>
+        <v>-0.7102884201463553</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.3515412022772537</v>
+        <v>-0.2814751959877881</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.2999594135254426</v>
+        <v>-0.2305665349143666</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.6529034140647738</v>
+        <v>0.7224728498472999</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.004441737099924126</v>
+        <v>0.07415388515654797</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.3229133608378305</v>
+        <v>-0.253432994788696</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.9510869565217419</v>
+        <v>1.020369336918471</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>0.6796256779585619</v>
+        <v>0.7495622993872146</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>1.147148883185523</v>
+        <v>1.217194598847684</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>1.965402310537222</v>
+        <v>2.035147572199307</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>1.889460971268754</v>
+        <v>1.959315318976032</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -20.54</t>
+          <t>X &lt; -20.52</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>456</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.6306431448812262</v>
+        <v>-0.597368852562397</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.642876992648354</v>
+        <v>1.676550001261695</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2.811872180736131</v>
+        <v>2.847226604404618</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>3.532198409079399</v>
+        <v>3.438620411048838</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.987223360096301</v>
+        <v>1.798482112414604</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2.740066931183591</v>
+        <v>2.420230907207639</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.877466068429733</v>
+        <v>1.430890918969453</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.502420194841001</v>
+        <v>0.1907584739322061</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.42974795066268</v>
+        <v>-1.60723831823762</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.107092133361938</v>
+        <v>-1.164230896035178</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.3941363750185332</v>
+        <v>-0.3268098964315058</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.2039627039627092</v>
+        <v>0.2716336825766419</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.4819320232963591</v>
+        <v>-0.4129318930514003</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.4839905887166864</v>
+        <v>-0.4147125238839635</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.9236235821399603</v>
+        <v>-0.8535575758504947</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.3285635325185794</v>
+        <v>-0.2591706539075034</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.1952375101746142</v>
+        <v>0.2648069459571403</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.3483423971487412</v>
+        <v>-0.2786302490921173</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-1.448008707901138</v>
+        <v>-1.378528341852004</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>0.05482456140350678</v>
+        <v>0.1241069418002354</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.2690776019804133</v>
+        <v>-0.1991409805517605</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>0.09356383360504594</v>
+        <v>0.1636095492672069</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>0.5876372457012167</v>
+        <v>0.6573825073633017</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>0.5116959064327489</v>
+        <v>0.5815502541400264</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -17.86</t>
+          <t>X &lt; -17.85</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.3521452558359783</v>
+        <v>-0.2394865692142787</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.6755412397411646</v>
+        <v>0.786280850122985</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.718238110399284</v>
+        <v>1.729214182044366</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2.982508447624731</v>
+        <v>2.887008461921361</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2.547281983054958</v>
+        <v>2.3811499621632</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2.664249927906944</v>
+        <v>2.398048121049698</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2.85187373708591</v>
+        <v>2.57784299659334</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.370569950673882</v>
+        <v>1.206841812842299</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.068443404012669</v>
+        <v>1.006504077164166</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.4664292990851635</v>
+        <v>0.504633946145816</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.9126098720424238</v>
+        <v>1.050668963669011</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.805337274409446</v>
+        <v>0.9434461468419286</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.5399525851319211</v>
+        <v>0.6779170130904504</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.3686894492701285</v>
+        <v>-0.2292682098398515</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.003307146744113254</v>
+        <v>0.1417480123051433</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.5983671963654942</v>
+        <v>0.7361349342481347</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.8079161139004185</v>
+        <v>0.9452709705125244</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.3279951372464041</v>
+        <v>-0.1887292530342108</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-1.142799809366132</v>
+        <v>-1.001997391835452</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>0.5906357388316152</v>
+        <v>0.7285876977209185</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>0.2192566356755847</v>
+        <v>0.357568116375802</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>0.4869441917168231</v>
+        <v>0.624775328208564</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>0.5898980523570287</v>
+        <v>0.7277234540696895</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>0.8575993247724085</v>
+        <v>0.99494437408827</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -15.18</t>
+          <t>X &lt; -15.17</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.212799324175549</v>
+        <v>-1.17952503185672</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.264964682980406</v>
+        <v>1.298637691593747</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.1707209253779</v>
+        <v>1.126441427372882</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.652442024469444</v>
+        <v>2.523192049280354</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2.229001664194193</v>
+        <v>2.046754600643062</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.792060283066455</v>
+        <v>1.53048590629038</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2.801252162560239</v>
+        <v>2.530094838136634</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.389553041121005</v>
+        <v>1.207563879686425</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1.289426046653553</v>
+        <v>1.190482057752313</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.9405198143543814</v>
+        <v>0.9246025574883632</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.073236021979625</v>
+        <v>1.140562500566652</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.5108559995245585</v>
+        <v>0.5785269781384912</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.519509256958095</v>
+        <v>0.5885093872030538</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.1565093864336546</v>
+        <v>0.2257874512663776</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.4890795638269552</v>
+        <v>0.5591455701164207</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.5175673754879924</v>
+        <v>0.5869602540990684</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.8084028598093198</v>
+        <v>0.8779722955918459</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-0.4297250322066404</v>
+        <v>-0.3600128841500165</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-0.7801741072351618</v>
+        <v>-0.7106937411860272</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>0.6816572237960372</v>
+        <v>0.7509396041927658</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>0.4217429337782477</v>
+        <v>0.4916795552069004</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>0.7707170566058963</v>
+        <v>0.8407627722680573</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>0.7622061041078538</v>
+        <v>0.8319513657699389</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>1.623118078885156</v>
+        <v>1.605977469487172</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -12.51</t>
+          <t>X &lt; -12.5</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.253814439989284</v>
+        <v>-1.108456065139862</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.2460222285410438</v>
+        <v>0.3235515888071419</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.119049952796843</v>
+        <v>1.123459512685464</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2.604981814173918</v>
+        <v>2.530646835998901</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>2.783920537467608</v>
+        <v>2.548213253910994</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2.803997241947272</v>
+        <v>2.568918355936098</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>2.339270102891632</v>
+        <v>2.220634771954415</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.822903328954524</v>
+        <v>1.776073450986857</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.9131708803029639</v>
+        <v>0.9407578575717892</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.6149597263706283</v>
+        <v>0.7107626223777146</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.8893189934859649</v>
+        <v>0.9359109626557185</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.01569476896469268</v>
+        <v>0.1826657110463898</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.199170256779567</v>
+        <v>0.3643672266339237</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.3345316383730363</v>
+        <v>0.4991602363083274</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.2701307203821059</v>
+        <v>0.4341367489294399</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.8651907700034869</v>
+        <v>1.028523670872431</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>1.087815268482395</v>
+        <v>1.250478420015952</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.8007591107520113</v>
+        <v>-0.6337217144102141</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-1.179166268866574</v>
+        <v>-1.010950143687552</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.1969381688466143</v>
+        <v>0.3621352866837952</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>0.3671741451043005</v>
+        <v>0.5313328909597672</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>0.05340696104314446</v>
+        <v>0.2182390054699894</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>0.09036999910672705</v>
+        <v>0.2554657938713802</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>0.6808688387635726</v>
+        <v>0.6541293888094444</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -9.833</t>
+          <t>X &lt; -9.823</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.6513265593682362</v>
+        <v>-0.6180522670494071</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.347845936747738</v>
+        <v>1.425763600606722</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.558947004793815</v>
+        <v>0.5823927180772159</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.087706320218224</v>
+        <v>2.04981530913993</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.979402203868702</v>
+        <v>1.813132864342904</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.424044369352153</v>
+        <v>2.256324765040624</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.008870101943224</v>
+        <v>1.840415550893816</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.489918881677852</v>
+        <v>1.322529936659123</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.7330317530877153</v>
+        <v>0.6263535477598978</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.4581983383262695</v>
+        <v>0.4091255686967159</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.3333560086352207</v>
+        <v>0.3426728832994783</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.1453386932428842</v>
+        <v>-0.0776677146289515</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.07222512131086489</v>
+        <v>-0.003224991065906124</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.105619664461166</v>
+        <v>0.1748977292938889</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.2450916190366357</v>
+        <v>0.3151576253261013</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.6405508702548346</v>
+        <v>0.7099437488659106</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.6062575753075095</v>
+        <v>0.6758270110900355</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.7961310304085316</v>
+        <v>-0.7264188823519078</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-1.0790098634847</v>
+        <v>-1.009529497435565</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.09356287425149645</v>
+        <v>-0.02428049385476783</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.03796088803987629</v>
+        <v>0.03197573338877646</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.7127183388920599</v>
+        <v>-0.6426726232298989</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.7373443700147178</v>
+        <v>-0.6675991083526327</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.754362596467864</v>
+        <v>-0.7434313615759081</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -7.157</t>
+          <t>X &lt; -7.148</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1183</v>
+        <v>1186</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.234524090314558</v>
+        <v>-0.1622217990983472</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.658209376834094</v>
+        <v>1.766203414286956</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.6014227835859671</v>
+        <v>0.6634735521796813</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>2.121481800222973</v>
+        <v>2.129899247741136</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2.394498439860456</v>
+        <v>2.297042555579445</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>2.041580962658784</v>
+        <v>1.946055243361705</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.161111522706236</v>
+        <v>2.062621653098617</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.426248753579614</v>
+        <v>1.32988078952512</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.7926593333701817</v>
+        <v>0.6637611271882378</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.862705779140839</v>
+        <v>0.7813739489132132</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.2087950040620754</v>
+        <v>0.1782965934663636</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.5204184001652408</v>
+        <v>0.5386376173714709</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.32419722387219</v>
+        <v>0.3429629029605437</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.3560049697998622</v>
+        <v>0.3748351226353677</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>0.2034028446866003</v>
+        <v>0.2225940172976451</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.6296865229999753</v>
+        <v>0.7326639072001626</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.7487573858130787</v>
+        <v>0.8516978663441108</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.706437000746341</v>
+        <v>-0.6022153501246308</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.9966429517385791</v>
+        <v>-0.8922261614431335</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.5564345991561197</v>
+        <v>-0.4524292553536924</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.5089177085760141</v>
+        <v>-0.4047561990364201</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-1.175590063796683</v>
+        <v>-1.070821384728823</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-1.27343435221249</v>
+        <v>-1.217931832449132</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.9618474193373032</v>
+        <v>-0.9564959575105192</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -4.482</t>
+          <t>X &lt; -4.473</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1369</v>
+        <v>1371</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.06046887706283854</v>
+        <v>0.09374316938166771</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.288235735628099</v>
+        <v>1.354325326796896</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.4696663773197542</v>
+        <v>0.4964368071350123</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.104651162790702</v>
+        <v>1.088776478772772</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.653757699119716</v>
+        <v>1.550665484108016</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.810486954180234</v>
+        <v>1.707162187576159</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.00714113008241</v>
+        <v>0.9046997661798386</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.1878582798494364</v>
+        <v>0.08720930232558999</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.0525546329297697</v>
+        <v>-0.04773057707048878</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.1539927451362786</v>
+        <v>0.09437293440129224</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.08222420948434461</v>
+        <v>-0.09904638714846214</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.1424997322152635</v>
+        <v>-0.1170932367625213</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.2458385072304878</v>
+        <v>-0.1768383769855291</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.04338090347111745</v>
+        <v>0.1126589683038404</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.5426108753181964</v>
+        <v>-0.4725448690287308</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.4581270474327752</v>
+        <v>-0.3887341688216992</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.3004629005897215</v>
+        <v>-0.2308934648071954</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-1.499538220404908</v>
+        <v>-1.429826072348284</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-1.429293977969081</v>
+        <v>-1.359813611919947</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-1.31518964259665</v>
+        <v>-1.245907262199921</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.9831165286186732</v>
+        <v>-0.9131799071900204</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-1.496708345749241</v>
+        <v>-1.42666263008708</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-1.544197816406616</v>
+        <v>-1.516885218844997</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-1.358506443854957</v>
+        <v>-1.37389909132429</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -1.806</t>
+          <t>X &lt; -1.798</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1598</v>
+        <v>1601</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.9705788327240654</v>
+        <v>-0.9113185774518158</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.2817478557242765</v>
+        <v>0.2427383710966282</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.1203865607583197</v>
+        <v>0.07983934831199235</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.06012337455472</v>
+        <v>0.9807897360697453</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.852001822597487</v>
+        <v>1.798482112414604</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.950874703874405</v>
+        <v>1.897356856352395</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.588670936495099</v>
+        <v>1.534719601643047</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.9722276723362313</v>
+        <v>0.9195959537488676</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.3631282122617989</v>
+        <v>0.3124188625309969</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.2139024204805082</v>
+        <v>0.1984418239250161</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.07388696949347917</v>
+        <v>-0.05227693060047045</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.1655979872719371</v>
+        <v>-0.1078630943000576</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.2907138153780764</v>
+        <v>-0.1960976726689907</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.3871487026148017</v>
+        <v>-0.2923326040469192</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.858697055955659</v>
+        <v>-0.7632099840244777</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.5759418158283509</v>
+        <v>-0.480932924753148</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.2103478147867648</v>
+        <v>-0.1154742814559668</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-1.127323735566613</v>
+        <v>-1.031800628223465</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-1.098583458331234</v>
+        <v>-1.003175164902139</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.625</v>
+        <v>-0.5666414647967812</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.7932004089979472</v>
+        <v>-0.7346557975568189</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-1.119155464640563</v>
+        <v>-1.060189649103243</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-1.18279493230478</v>
+        <v>-1.16024677182719</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.8466357801052524</v>
+        <v>-0.824780219138745</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.8692</t>
+          <t>X &lt; 0.8769</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1809</v>
+        <v>1812</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.765230077540032</v>
+        <v>-0.7641347846648401</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.08288286218535035</v>
+        <v>-0.08308005213265801</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.4850685495846747</v>
+        <v>0.4832303249798784</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>2.110986102765388</v>
+        <v>2.074170984637519</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2.657858109160721</v>
+        <v>2.593594984079758</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>2.382274190847674</v>
+        <v>2.318757755809692</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2.192405399135353</v>
+        <v>2.128454225228417</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.340465721881742</v>
+        <v>1.278046971885907</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.028471744108977</v>
+        <v>0.9667308690741194</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.5302702914431805</v>
+        <v>0.5010528513108952</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.7495027669377876</v>
+        <v>0.7522920434402067</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.4152820718421566</v>
+        <v>0.4506970434581774</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.283073102528121</v>
+        <v>0.3520732327730798</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.06171629149376656</v>
+        <v>0.1309943563264895</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.3215809894399015</v>
+        <v>-0.251514983150436</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-0.3329156476465229</v>
+        <v>-0.2635227690354469</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.08425857441182671</v>
+        <v>0.1538280101943528</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.571992757890726</v>
+        <v>-0.5022806098341022</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-0.488684722261354</v>
+        <v>-0.4517696037719574</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.1034768211920465</v>
+        <v>-0.09954341894174945</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-0.3155514023754336</v>
+        <v>-0.3113288371834102</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.6346855585113502</v>
+        <v>-0.6628087566961511</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.6033581987109145</v>
+        <v>-0.6314331611516124</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-0.6466206976811861</v>
+        <v>-0.6746946627880561</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 3.545</t>
+          <t>X &lt; 3.552</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2003</v>
+        <v>2008</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.2548944483672457</v>
+        <v>-0.3042183442772384</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.2792504271507354</v>
+        <v>0.2281347430154455</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.05695499647112712</v>
+        <v>0.00446688579781096</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.852097639794565</v>
+        <v>1.7941950989524</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2.210767719883464</v>
+        <v>2.130975598212572</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.731632694640162</v>
+        <v>1.653220953314417</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.633752908791074</v>
+        <v>1.554514035522239</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.8374198022633337</v>
+        <v>0.759736064968628</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.5098959351713006</v>
+        <v>0.4330273746551967</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.3330754497750021</v>
+        <v>0.2845988493575788</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.4084297417659641</v>
+        <v>0.3889325147380021</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.06966913683330489</v>
+        <v>-0.05971157918611425</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.0498817483552827</v>
+        <v>-0.01032168777691567</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.0722335842652555</v>
+        <v>-0.03249454731648171</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-0.6316623357403728</v>
+        <v>-0.5911848364435457</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-0.6833684552732251</v>
+        <v>-0.6432424694483316</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-0.1908540252842386</v>
+        <v>-0.1804415557047676</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-0.4451654652720123</v>
+        <v>-0.4344617722062196</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-0.1994939948236194</v>
+        <v>-0.2185703912818937</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.06695316392625017</v>
+        <v>0.01800192291288738</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>0.002038873155591148</v>
+        <v>-0.04726876269367608</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.2934073349647548</v>
+        <v>-0.3718709430082541</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-0.2882425736075334</v>
+        <v>-0.3664095511802685</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.3345128506071262</v>
+        <v>-0.4127182857355578</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 6.22</t>
+          <t>X &lt; 6.227</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2169</v>
+        <v>2174</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.1685135439289809</v>
+        <v>0.1245568117163671</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.1783461001998461</v>
+        <v>0.1339651293141131</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.1828707473868718</v>
+        <v>0.1368367102699111</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.647562027932544</v>
+        <v>1.597351831444676</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.675422560381278</v>
+        <v>1.608028642304674</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.56832008629182</v>
+        <v>1.501339940979861</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.372476530364388</v>
+        <v>1.305032795399669</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.5700514114782749</v>
+        <v>0.5040889343215014</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.2708706757932546</v>
+        <v>0.2055988694792887</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.3234815460155716</v>
+        <v>0.2839616962305769</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.2305313549123511</v>
+        <v>0.217966763236916</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.002648866285227314</v>
+        <v>0.01169484465614801</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.1170390746713537</v>
+        <v>-0.02928576534112182</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.2924822034283991</v>
+        <v>-0.2044720304981382</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.8323584417971333</v>
+        <v>-0.7708301054995275</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-0.6966461184045087</v>
+        <v>-0.6353692964523532</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-0.436051189515787</v>
+        <v>-0.4021455431131784</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-0.697707188437299</v>
+        <v>-0.6905566920926915</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-0.5464044211954118</v>
+        <v>-0.5393953854941671</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.05608605614357742</v>
+        <v>-0.07706748186222256</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-0.1115705747438085</v>
+        <v>-0.133059377831124</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-0.3442245572246279</v>
+        <v>-0.3652862195666415</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-0.2262927405547472</v>
+        <v>-0.2473361859216396</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-0.3209094659192928</v>
+        <v>-0.3418426347058272</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 8.896</t>
+          <t>X &lt; 8.902</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2339</v>
+        <v>2343</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.1655052382882332</v>
+        <v>0.1499195108797693</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.3625197179749975</v>
+        <v>0.3464099865233052</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.601958029531481</v>
+        <v>0.5846614054441162</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.483768350753785</v>
+        <v>1.46458198496925</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.312993490952195</v>
+        <v>1.280506055894712</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.439716375206274</v>
+        <v>1.407091466741115</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.15931328536616</v>
+        <v>1.126727713947766</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.5225769697570115</v>
+        <v>0.4909011874888876</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.03532117169621074</v>
+        <v>0.004473572371225032</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.1554832066483698</v>
+        <v>0.1487724234545453</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.2087271303231404</v>
+        <v>-0.1904364234039733</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.3175358060415476</v>
+        <v>-0.2744656082034993</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.5054582718679868</v>
+        <v>-0.436458141623028</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.6592050302720267</v>
+        <v>-0.6149657111304947</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-0.9948230977589958</v>
+        <v>-0.9751098601371879</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-0.9536616420873401</v>
+        <v>-0.9341499284028032</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.849654130692258</v>
+        <v>-0.8552105306846585</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-1.014840732539454</v>
+        <v>-1.020209495333788</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.7309857751426208</v>
+        <v>-0.7367048867506725</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-0.2200704225352155</v>
+        <v>-0.2516059877327947</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.182931408143979</v>
+        <v>-0.2148452027440655</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-0.5323869896298845</v>
+        <v>-0.5637685975924711</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-0.4458760246541615</v>
+        <v>-0.477280087690886</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-0.4537226635064187</v>
+        <v>-0.485177063513909</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 11.57</t>
+          <t>X &lt; 11.58</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2485</v>
+        <v>2489</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.1382538437502063</v>
+        <v>0.1255936996409659</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.4236104278476844</v>
+        <v>0.4103410004989243</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.5238352163976785</v>
+        <v>0.5097714787564342</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.311230085698888</v>
+        <v>1.295589771540179</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.208844755206371</v>
+        <v>1.182323126039527</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.379104130308328</v>
+        <v>1.352374260451136</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1.029495301175466</v>
+        <v>1.002969641893252</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.4939923999735285</v>
+        <v>0.4681835926607505</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.1982582884031459</v>
+        <v>0.1729229796886216</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.4490819557068875</v>
+        <v>0.4229901105293763</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.0778408284598342</v>
+        <v>-0.07986901481570641</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.1566142191142177</v>
+        <v>-0.1353585778984012</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.1593105658064928</v>
+        <v>-0.1139766555383233</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.276821865304953</v>
+        <v>-0.23126110687992</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-0.4709582379454673</v>
+        <v>-0.448699276255347</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-0.3734259895033958</v>
+        <v>-0.3751456876456913</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.2430069774489354</v>
+        <v>-0.2686782092385513</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.4044214748107819</v>
+        <v>-0.4298976962671688</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.1644534341746464</v>
+        <v>-0.190237848175947</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>0.2875150662916894</v>
+        <v>0.2610693840068379</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>0.2104169543460941</v>
+        <v>0.1838389411626409</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>0.07822089241612673</v>
+        <v>0.0518035388578113</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>0.1358087605704483</v>
+        <v>0.1094011080819683</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>0.2046783625730981</v>
+        <v>0.1781084435065736</v>
       </c>
     </row>
     <row r="26">
@@ -7468,161 +7468,161 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2647</v>
+        <v>2651</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.3941200640654756</v>
+        <v>0.383862733067474</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.5293377382695397</v>
+        <v>0.5187581106901291</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.6110401389708926</v>
+        <v>0.5998452370141294</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.044416509532795</v>
+        <v>1.032323559474627</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1.188800200741269</v>
+        <v>1.16790876017059</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.247383619414251</v>
+        <v>1.226454202161804</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.9095375097161522</v>
+        <v>0.8888401807363167</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.3520442549913767</v>
+        <v>0.3320762623088243</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.377668767137834</v>
+        <v>0.3576632030134874</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.4156198384411525</v>
+        <v>0.3952816206721295</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.02484406976329723</v>
+        <v>-0.02270973622263739</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.04058206654143248</v>
+        <v>-0.01658686880180227</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.114083976069999</v>
+        <v>0.1607569360163694</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.04729242629897357</v>
+        <v>-0.0003724977463832602</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.1567402593752121</v>
+        <v>-0.131803981933416</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-0.06639681629297911</v>
+        <v>-0.06412887338395024</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.0650448838284845</v>
+        <v>-0.08517919320566847</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.185253275928801</v>
+        <v>-0.2052557137699864</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>0.166462991709885</v>
+        <v>0.1459907872961708</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>0.6023670313089369</v>
+        <v>0.5812880301142442</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>0.7233090249643084</v>
+        <v>0.7018492493560871</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>0.5947460076131108</v>
+        <v>0.573440194481833</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>0.5525230251044064</v>
+        <v>0.5313604386167725</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>0.6126874294412517</v>
+        <v>0.5913942719552168</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 16.92</t>
+          <t>X &lt; 16.93</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2778</v>
+        <v>2782</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.3287377793814414</v>
+        <v>0.3206089893517543</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.3346430152502151</v>
+        <v>0.3264110757226817</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.3449940318277456</v>
+        <v>0.3363570391872273</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.8676207513416898</v>
+        <v>0.8580403902339526</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.7017176132213621</v>
+        <v>0.6855753777904923</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.945176453974625</v>
+        <v>0.9287260339738879</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.6942609208904003</v>
+        <v>0.6779519378162604</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.5080774767056369</v>
+        <v>0.4919499105545668</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.3911349016293357</v>
+        <v>0.3751756505601449</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.3909609951567461</v>
+        <v>0.3747838806690211</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.01992764843198813</v>
+        <v>0.02507267532740798</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.09938519709047</v>
+        <v>0.1253300876883117</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.2298240610701612</v>
+        <v>0.2775038737850366</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.1015388733890887</v>
+        <v>0.1494556052952021</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>0.03807830443871296</v>
+        <v>0.0649946311280587</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>0.08043635413272909</v>
+        <v>0.0856992296576351</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.003656672982884857</v>
+        <v>-0.01236276210649834</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.04397155625339622</v>
+        <v>-0.05996126673666424</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>0.3014129057809285</v>
+        <v>0.2849751423698592</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>0.6178109273903729</v>
+        <v>0.6009586187312621</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>0.6715155205238048</v>
+        <v>0.6544292106353637</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>0.5094416576615899</v>
+        <v>0.4925569176882618</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>0.374178535954556</v>
+        <v>0.3575514529035857</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>0.4998547484622264</v>
+        <v>0.4830158159597389</v>
       </c>
     </row>
     <row r="28">
@@ -7632,161 +7632,161 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2887</v>
+        <v>2892</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.1085470949369594</v>
+        <v>0.08383534451517249</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.1014701934679678</v>
+        <v>0.07657389041601448</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.2633219548167389</v>
+        <v>0.2373360841889394</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.6702557739262716</v>
+        <v>0.6431624699163052</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.5656034291472594</v>
+        <v>0.5331436575444073</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.7035409198363993</v>
+        <v>0.6709336163757413</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.4327576398807551</v>
+        <v>0.4001704690808907</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.5187485026840264</v>
+        <v>0.4858432433297679</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.3388545901721542</v>
+        <v>0.3062672323490006</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.343801399193147</v>
+        <v>0.3107587055707057</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.1062270535949352</v>
+        <v>-0.1184652318074839</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.1320988428611827</v>
+        <v>0.1395408730200174</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.2354411197060671</v>
+        <v>0.242921805310317</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.2072114412114345</v>
+        <v>0.214749061113011</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>0.08684457720869432</v>
+        <v>0.07384714284280136</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>0.08094469400629123</v>
+        <v>0.04754440961337991</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.03254774425379026</v>
+        <v>-0.06584246127947324</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.1169156623199612</v>
+        <v>-0.1501387304404176</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>0.3273061352232745</v>
+        <v>0.2934220726723993</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>0.6042459356623979</v>
+        <v>0.5699729881315392</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>0.6700348851196907</v>
+        <v>0.6353286131215441</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>0.6496659268443779</v>
+        <v>0.6149365537168308</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>0.4606751035036112</v>
+        <v>0.4264105908800815</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>0.6134071467781581</v>
+        <v>0.5788204004601809</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 22.27</t>
+          <t>X &lt; 22.28</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2989</v>
+        <v>2993</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.212921783617972</v>
+        <v>0.207858925055092</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.1043451091621534</v>
+        <v>-0.1090457504807532</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.1028643176464001</v>
+        <v>0.09764521979811036</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.3719615470878068</v>
+        <v>0.3662625348557498</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.291633462743988</v>
+        <v>0.2817985937088352</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.4311507193266237</v>
+        <v>0.4211556691536842</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.2763844696258033</v>
+        <v>0.2664598366382833</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.2500409950933786</v>
+        <v>0.2400986844649324</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.1108916229549024</v>
+        <v>0.1011353274840303</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.08929269742546353</v>
+        <v>0.07942937841622921</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.1361814243295782</v>
+        <v>-0.1264921913832708</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.05123583514120611</v>
+        <v>0.08015849110144302</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.2794714854755682</v>
+        <v>0.3088091684631351</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.01127683960737613</v>
+        <v>0.04091045559071915</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.02741207271260748</v>
+        <v>-0.01743277534539089</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.04626368881521614</v>
+        <v>-0.05616814597154018</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.1271221272366745</v>
+        <v>-0.1369474400077735</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.1788347381849746</v>
+        <v>-0.1886148638467446</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>0.0571946813334705</v>
+        <v>0.04712969918120535</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>0.2975693284330134</v>
+        <v>0.2872086399896574</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>0.3424947781678256</v>
+        <v>0.3319765328579365</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>0.4204215998863461</v>
+        <v>0.4097800673821936</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>0.3140645178950834</v>
+        <v>0.3036047764628975</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>0.4589440032556027</v>
+        <v>0.4482714339689835</v>
       </c>
     </row>
     <row r="30">
@@ -7796,161 +7796,161 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3075</v>
+        <v>3079</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.02425060471720286</v>
+        <v>-0.02794388762551847</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.1159205068248497</v>
+        <v>-0.119541304489104</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.1101493511360658</v>
+        <v>0.1060471618470089</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.09327137798027962</v>
+        <v>0.08909562549199279</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.06961092739209107</v>
+        <v>0.06216035081478566</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.2103820338993927</v>
+        <v>0.2027693633430587</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.07070401767177259</v>
+        <v>0.06316657170546591</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.1343910251216229</v>
+        <v>0.1267302761674998</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.09738594625578401</v>
+        <v>0.08977383313766296</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.08722017802877957</v>
+        <v>0.07951550684125408</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.05954138413997612</v>
+        <v>-0.04832241559348205</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.1796672715040089</v>
+        <v>0.2095855548114542</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.4026514379490962</v>
+        <v>0.43301393005558</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.2006322325179255</v>
+        <v>0.2312476145573754</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>0.1122833057022206</v>
+        <v>0.1238007860406327</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>0.07816607125083408</v>
+        <v>0.0703095090850212</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>0.02830899485645944</v>
+        <v>0.02049477213306972</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.1222111000647388</v>
+        <v>-0.129848651662563</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>0.1457484121717769</v>
+        <v>0.1377867649812288</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>0.2872279961026365</v>
+        <v>0.2791023609351697</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>0.3482063486368716</v>
+        <v>0.3399256997765789</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>0.4218341356194273</v>
+        <v>0.4134429936376236</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>0.3586431088636743</v>
+        <v>0.350364963503651</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>0.4648409641991194</v>
+        <v>0.4564099431481949</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 27.62</t>
+          <t>X &lt; 27.63</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3156</v>
+        <v>3160</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.1330449184986691</v>
+        <v>-0.1356600653338873</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.2309593889089783</v>
+        <v>-0.233485547001905</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.04706560764472556</v>
+        <v>0.0440481370167376</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.08213537316276387</v>
+        <v>-0.08506142330145394</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.08305575531113618</v>
+        <v>-0.08844977574896973</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.2164811794886461</v>
+        <v>0.2107248290124772</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.09216672736182829</v>
+        <v>0.08648831712077509</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.1155697880669706</v>
+        <v>0.1098313330695646</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.01410130802263865</v>
+        <v>-0.01967568207579262</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.01930340092832949</v>
+        <v>0.0136080172128672</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.1482565238755242</v>
+        <v>-0.1355204144484006</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.0801282051282044</v>
+        <v>-0.04908135422672188</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.1083105550471828</v>
+        <v>0.139846392201008</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.0004604314426828182</v>
+        <v>0.03219071907191307</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.07095874469087704</v>
+        <v>-0.05777076032683226</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.05742107460386592</v>
+        <v>-0.06313131313130782</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.0462470897222218</v>
+        <v>-0.0519879620580852</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.1639987106079062</v>
+        <v>-0.1696045262252497</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>0.1026192856829482</v>
+        <v>0.09669407437814925</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>0.1186708860759467</v>
+        <v>0.1127400289428664</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>0.1641041177510232</v>
+        <v>0.1580593234012895</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>0.2338369356127643</v>
+        <v>0.2276929075680911</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>0.2426089321234741</v>
+        <v>0.2364769533802757</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>0.3440953460965517</v>
+        <v>0.3378238495208805</v>
       </c>
     </row>
     <row r="32">
@@ -7960,79 +7960,79 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3216</v>
+        <v>3220</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.198681183322627</v>
+        <v>-0.2005509085569273</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.1774056966621131</v>
+        <v>-0.1793276154854837</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.05487064568682598</v>
+        <v>-0.05705142021381704</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.00942025858969231</v>
+        <v>-0.01171124832222148</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.04801099306035894</v>
+        <v>-0.05213104254637813</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.3113318530805955</v>
+        <v>0.3067789805133785</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.1440529162363475</v>
+        <v>0.1396470509498329</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.1618629192992032</v>
+        <v>0.1574118019300741</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.0353870919609065</v>
+        <v>0.0310929192599616</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.03913413427500956</v>
+        <v>-0.04339602808448006</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.1365220790555739</v>
+        <v>-0.1227831163894848</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.07484770495922533</v>
+        <v>-0.04312379936351363</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.08918122620482194</v>
+        <v>0.1214250584788559</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.02078592485617037</v>
+        <v>0.01165544063700708</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.07213439405346378</v>
+        <v>-0.05788810477502437</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.01675734210456881</v>
+        <v>-0.02112200067590919</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.008275072087741364</v>
+        <v>-0.01266275867320132</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.09474051534926531</v>
+        <v>-0.09903137590170275</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>0.1088658597660981</v>
+        <v>0.1043357952349027</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>0.06599378881987406</v>
+        <v>0.06152803796496187</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>0.1004389199862032</v>
+        <v>0.09588762415890528</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>0.1985107876900756</v>
+        <v>0.1938294192400889</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>0.2122330061623643</v>
+        <v>0.20755217244497</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>0.2482107008815575</v>
+        <v>0.2434768096592634</v>
       </c>
     </row>
     <row r="33">
@@ -8042,79 +8042,79 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3271</v>
+        <v>3275</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.1363139353590554</v>
+        <v>-0.1376624000561719</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.2122130807839397</v>
+        <v>-0.2134879894516786</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.2985871748185431</v>
+        <v>-0.2998341595988165</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.114158478829431</v>
+        <v>-0.1156680185068808</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.1887476216464705</v>
+        <v>-0.1915098336105601</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.04596544417692883</v>
+        <v>0.04292624240758869</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.1012886217639632</v>
+        <v>-0.1041915853572277</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.0581717902953045</v>
+        <v>-0.06114370537923008</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.151409410247723</v>
+        <v>-0.1542675183900499</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.05520846560546033</v>
+        <v>-0.05822643448278342</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.05490522772276307</v>
+        <v>-0.04032779522472651</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.04225518617842283</v>
+        <v>-0.02761565806041233</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.1001905592110859</v>
+        <v>0.1149860753856586</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.07259750680434962</v>
+        <v>-0.05758493023479616</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.04268648329527736</v>
+        <v>-0.04581348969111332</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>0.05224897450379018</v>
+        <v>0.04903589658387375</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>0.02785367535877725</v>
+        <v>0.02466133512933766</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>0.002119889174338141</v>
+        <v>-0.001048531922016593</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>0.1143908808142413</v>
+        <v>0.1110951070140729</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>0.0753816793893094</v>
+        <v>0.07214148378190544</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>0.100125797477304</v>
+        <v>0.09682468100909603</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>0.2258262035537584</v>
+        <v>0.2223656858705425</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>0.2439448852156474</v>
+        <v>0.2404748536135415</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>0.2474787294333822</v>
+        <v>0.2439983591353325</v>
       </c>
     </row>
     <row r="34">
@@ -8124,79 +8124,79 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3301</v>
+        <v>3305</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.04239981001808957</v>
+        <v>0.04114867857284565</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.005684638637148964</v>
+        <v>-0.006892703122730381</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.1644445389528002</v>
+        <v>-0.1655226600608941</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.07845334827682393</v>
+        <v>-0.07966557231327442</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.1556591569979489</v>
+        <v>-0.1578433661341165</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.01178194564104729</v>
+        <v>-0.01413288621172626</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.1345639312000273</v>
+        <v>-0.1368008449047053</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.09436731071420468</v>
+        <v>-0.0966657326982272</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.1562304464950302</v>
+        <v>-0.1584539603458452</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.09808197973405441</v>
+        <v>-0.1004095278069599</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.09529784840628963</v>
+        <v>-0.08020680443863171</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.05511768641861892</v>
+        <v>-0.03998674363968746</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.01473141307516812</v>
+        <v>0.0006586443781415596</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.127589543821145</v>
+        <v>-0.1120359471070813</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.1341498979294258</v>
+        <v>-0.1365039278499793</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.09514908070453743</v>
+        <v>-0.09752673124239664</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.06012429215466852</v>
+        <v>-0.06255130474207959</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.08660360808354994</v>
+        <v>-0.08900449337089356</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.003665090236282253</v>
+        <v>-0.006158595734440553</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>0.0501134644478114</v>
+        <v>0.04756131663123853</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>0.03942670964610784</v>
+        <v>0.03686317736419653</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>0.1632771723561035</v>
+        <v>0.1605591352066611</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>0.1837087387888729</v>
+        <v>0.1809759737879801</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>0.1865020523640695</v>
+        <v>0.183761152035288</v>
       </c>
     </row>
     <row r="35">
@@ -8206,79 +8206,79 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3338</v>
+        <v>3342</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.07587859424920396</v>
+        <v>0.07496739310786893</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.05441251693741833</v>
+        <v>0.05351673644896238</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.1184434833496297</v>
+        <v>-0.1191753819906438</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.1008306142666129</v>
+        <v>-0.1016044185179368</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.09182687125627353</v>
+        <v>-0.09333983375516652</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.02274049394468136</v>
+        <v>0.0210955537768811</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.07738752351076528</v>
+        <v>-0.07893635917229602</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.1003393135332757</v>
+        <v>-0.1018697480446917</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.1908960476354196</v>
+        <v>-0.1923182897154163</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.2016279357147326</v>
+        <v>-0.203060560111453</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.2256870511717679</v>
+        <v>-0.2099031393778645</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.1592213756392837</v>
+        <v>-0.1434175153555586</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.1615954996941369</v>
+        <v>-0.1454822426724789</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.1263536648658388</v>
+        <v>-0.1102079769301838</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.1998804028592147</v>
+        <v>-0.2013563476232463</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.1846367700055964</v>
+        <v>-0.1861148801447357</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.1216140357305164</v>
+        <v>-0.1231721837123629</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.1788846619015345</v>
+        <v>-0.1803783469352922</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.1543261767152586</v>
+        <v>-0.1558439793173392</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.06919509275882518</v>
+        <v>-0.07081026754111264</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.05588373734276075</v>
+        <v>-0.05753135109695506</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>0.0357846551199188</v>
+        <v>0.03402422231346947</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>0.0290473747975355</v>
+        <v>0.02730184654284074</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>0.06087968072767325</v>
+        <v>0.05909285390695374</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/nasdaq_hourly_24hrs/rsi/rsi_spread_7_14.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/rsi/rsi_spread_7_14.xlsx
@@ -618,1723 +618,1723 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -37.91</t>
+          <t>X ≈ -37.81</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>4.226209526959579</v>
+        <v>1.447617588142833</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>3.893343474652852</v>
+        <v>6.170337112503233</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>7.696851742778932</v>
+        <v>9.894144211572971</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>6.990745649666486</v>
+        <v>9.308841527277878</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-9.045634893462214</v>
+        <v>-5.877974069274089</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>6.8461865385094</v>
+        <v>9.195125180183176</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.8420719838848427</v>
+        <v>3.431795107063074</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.5654302351507994</v>
+        <v>3.129748131512983</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.6073595151389384</v>
+        <v>3.258747076558954</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-5.403343388466737</v>
+        <v>-2.512320463014944</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-15.61701321890901</v>
+        <v>-12.20282408063943</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-10.65505837107495</v>
+        <v>-7.499681207604887</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-11.7779922980207</v>
+        <v>-8.613365710842942</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-6.754241245000259</v>
+        <v>-3.877952133527451</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-7.412650609473346</v>
+        <v>-4.559417243143024</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-6.822070339617667</v>
+        <v>-4.001022709040662</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-12.21004618977633</v>
+        <v>-9.095756379931196</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-7.064499842213699</v>
+        <v>-4.239927748894956</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-12.10620604747096</v>
+        <v>-9.019497084329586</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-6.666415185831099</v>
+        <v>-8.807942625702836</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-7.210416151754089</v>
+        <v>-9.377456078779964</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-7.288303726744758</v>
+        <v>-4.458396533933737</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-7.016035537932204</v>
+        <v>-4.216159798685858</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-7.093888342351207</v>
+        <v>-4.379530298637277</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -35.23</t>
+          <t>X ≈ -35.14</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.6407228513376921</v>
+        <v>0.7820618409406705</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.3068044247806796</v>
+        <v>-5.493539890669112</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-1.122461717048061</v>
+        <v>-6.817169960069329</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1.00960460860307</v>
+        <v>-4.436055306841503</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>3.517959020725783</v>
+        <v>-1.715425709068136</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.8614957356852102</v>
+        <v>-4.550908235412777</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>2.937053623758729</v>
+        <v>-2.373069341825378</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>5.503744344114359</v>
+        <v>2.025808990248365</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.1411593281119465</v>
+        <v>-2.171443957204758</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-6.600889116479422</v>
+        <v>-8.999887718703576</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-12.02121117273575</v>
+        <v>-14.76775674609671</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-9.455800003178403</v>
+        <v>-12.02829494419748</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-7.730750513265448</v>
+        <v>-10.12305106158394</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-7.953271633149896</v>
+        <v>-10.3733016505826</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-2.913361910400312</v>
+        <v>-5.012529947598495</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-2.321478931356431</v>
+        <v>-4.454318339818713</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-11.00918225882914</v>
+        <v>-13.63132360681007</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-13.96899038418067</v>
+        <v>-16.79282391747866</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-5.19912171337625</v>
+        <v>-7.506413650829522</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-7.867834278645411</v>
+        <v>-7.294451355002153</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-11.26676252881605</v>
+        <v>-10.89110200251109</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-8.490510553421622</v>
+        <v>-10.96957410413163</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-8.218644115629488</v>
+        <v>-10.72932507136392</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>0.2745327102810293</v>
+        <v>-1.803772722879017</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -32.56</t>
+          <t>X ≈ -32.48</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>2.501683793494749</v>
+        <v>0.9965061149394003</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>9.619766871782986</v>
+        <v>7.528617716073562</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>3.186476440670766</v>
+        <v>1.764262222512315</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>7.43205525791312</v>
+        <v>3.436406815556587</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.604135060905243</v>
+        <v>3.163377298899221</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>4.800062254994018</v>
+        <v>3.319299939860144</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.9630334281807436</v>
+        <v>-4.258359763231233</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>6.218137192767628</v>
+        <v>2.225260032385911</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>5.191358548285777</v>
+        <v>2.353463603432672</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>4.423656009463642</v>
+        <v>1.561813862588046</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>9.67874558961352</v>
+        <v>6.361682237697941</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>11.89468629458615</v>
+        <v>8.352447057629405</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>8.287020423580948</v>
+        <v>7.243530396674863</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>5.577055965047307</v>
+        <v>4.732736360927703</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>4.9222505743654</v>
+        <v>4.053741226505515</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>5.516482391482697</v>
+        <v>4.614647631452719</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>2.889965282103908</v>
+        <v>2.244438252685043</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>2.786353316925876</v>
+        <v>2.112576289728572</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>5.498873846808699</v>
+        <v>4.596550631360707</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>10.68096596533788</v>
+        <v>9.352047878086353</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>7.644574121922339</v>
+        <v>6.517393114122953</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>7.571143933509425</v>
+        <v>6.444166779317378</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>5.348663197980912</v>
+        <v>4.417630964659239</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>0.2745327102803756</v>
+        <v>-0.2886212077287098</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -29.88</t>
+          <t>X ≈ -29.8</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-1.904277759024623</v>
+        <v>0.02915023915944914</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1.187250673071787</v>
+        <v>1.589805364968988</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>8.328331206385876</v>
+        <v>9.359350289932614</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>4.193171571421011</v>
+        <v>6.952854848069165</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.99902653337395</v>
+        <v>-2.370223049333575</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-4.530378271341611</v>
+        <v>-4.018245138483636</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-5.299674544771321</v>
+        <v>-3.015746707811317</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-3.86081332255366</v>
+        <v>-1.513727461490689</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-3.818752412511799</v>
+        <v>-3.196930913933535</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-2.872503398120692</v>
+        <v>-1.153832910201153</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-2.599978671384839</v>
+        <v>-0.8824906970959034</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-2.87866604062782</v>
+        <v>-1.158407914233592</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-2.280850726110593</v>
+        <v>-2.270091102724493</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.7828397653307775</v>
+        <v>-0.7053083931601876</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.2797562879219555</v>
+        <v>0.427208856824393</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.8725316652144528</v>
+        <v>0.9869771381645549</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.7393149161656751</v>
+        <v>0.8836244330126561</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>0.6350677088180419</v>
+        <v>0.751371161653438</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-4.3135953697521</v>
+        <v>-4.480442805761065</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-2.406480812583226</v>
+        <v>-2.451788610574987</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-2.949131448035196</v>
+        <v>-3.01933669705646</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-3.025806298043165</v>
+        <v>-3.095469733970667</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-1.028700253294218</v>
+        <v>-1.035258687122472</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-1.104777634547219</v>
+        <v>-1.197712116818693</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -27.21</t>
+          <t>X ≈ -27.13</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2.918542782842394</v>
+        <v>3.488213234002025</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-2.645169998458456</v>
+        <v>-3.216053623146642</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-1.459881432758259</v>
+        <v>-0.6201455514905589</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>4.372544609207267</v>
+        <v>3.942691895571471</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>6.658518843095962</v>
+        <v>4.951711664108217</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>8.154889585833274</v>
+        <v>7.127988100727478</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>11.31820627309846</v>
+        <v>10.2080098215781</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.5650382108653744</v>
+        <v>-0.4455396388522601</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.6071236909213127</v>
+        <v>-0.3184293009750121</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.1618466218568955</v>
+        <v>-1.121847942459873</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>6.663075637137474</v>
+        <v>5.620038429106053</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>6.387354156216659</v>
+        <v>6.086792455750327</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.64761431783667</v>
+        <v>3.683384293082391</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>3.739945036711212</v>
+        <v>4.732013404450328</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>3.084674249685165</v>
+        <v>4.053133451061719</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-1.571392369573005</v>
+        <v>-0.5675963221992149</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>6.171667861277811</v>
+        <v>7.103431729941697</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>6.069187282606578</v>
+        <v>6.973184530307705</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>4.973045974138763</v>
+        <v>5.892927591995942</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>1.218742118963753</v>
+        <v>3.514752992960062</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>1.991773114998054</v>
+        <v>4.246561434386166</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>3.23159321188983</v>
+        <v>5.470576601066448</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>2.191691737210711</v>
+        <v>4.417561220729375</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>2.116637973438273</v>
+        <v>4.256833337726349</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -24.54</t>
+          <t>X ≈ -24.46</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.8575108902273527</v>
+        <v>-2.201758627819551</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>5.707063430058533</v>
+        <v>4.654846274740578</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.518900482627636</v>
+        <v>0.5306071289405878</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>6.333304604899197</v>
+        <v>4.191816821603311</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.4778094352066447</v>
+        <v>-1.78487221514014</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.7186770019368538</v>
+        <v>-3.040024379122343</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-4.250996413727577</v>
+        <v>-6.701517029959192</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-3.144938506372675</v>
+        <v>-5.594831290038826</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-3.102824060623341</v>
+        <v>-5.469274026367032</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.2747612437499569</v>
+        <v>-2.016277095525908</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>3.313471447062199</v>
+        <v>1.925169076345625</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>1.653368344773064</v>
+        <v>0.22241375460721</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.5349024487811178</v>
+        <v>-2.328745130810461</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.3149472853436279</v>
+        <v>-1.74107569407888</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.3413067419928382</v>
+        <v>-2.421904183438791</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.2514727302641404</v>
+        <v>-1.862843753107981</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-1.268043296929989</v>
+        <v>-1.967522612651251</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-1.372850126465629</v>
+        <v>-2.100596416852618</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-1.157621055671399</v>
+        <v>-1.88703056960351</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>1.802679306385059</v>
+        <v>1.179921448237181</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>2.648919148530382</v>
+        <v>2.040738712836408</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>2.574024167107318</v>
+        <v>1.966203040137017</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>5.626197347803426</v>
+        <v>3.638526873663231</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>2.774532710280376</v>
+        <v>0.6204697013623885</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -21.86</t>
+          <t>X ≈ -21.8</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.44105536887853</v>
+        <v>0.1425851169096006</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-1.774975467057693</v>
+        <v>-0.1035550531884084</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>5.800897883817157</v>
+        <v>6.048570784961605</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>3.950488491215005</v>
+        <v>4.395414942320038</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>5.866251211394868</v>
+        <v>7.886500701207638</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.668981374288045</v>
+        <v>3.803529234565303</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.7508604003758776</v>
+        <v>3.012894959755307</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.6664949138833975</v>
+        <v>1.649745467476365</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-4.021549066311586</v>
+        <v>-1.40168663852571</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.889744097120733</v>
+        <v>-1.134955058597804</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.092825020686433</v>
+        <v>-1.924065005579415</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1.024223480926658</v>
+        <v>0.980152169196046</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.226348971336961</v>
+        <v>-0.1304119036861096</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.818221812019992</v>
+        <v>1.742968800344222</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-3.236496267860943</v>
+        <v>-2.118471863491045</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.3781921561168815</v>
+        <v>0.5625146537943735</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-1.645814792274237</v>
+        <v>-0.6027240294132596</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-1.750747416272645</v>
+        <v>-0.735349986756539</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-6.073455687209503</v>
+        <v>-3.707504039692687</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-3.619418591771662</v>
+        <v>-1.369929798806247</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-4.16249776764576</v>
+        <v>-1.937117549879112</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-4.239645543425553</v>
+        <v>-3.076070566440471</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-5.102599298977445</v>
+        <v>-3.896999120453145</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-5.180012744265085</v>
+        <v>-4.060381362467069</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -19.19</t>
+          <t>X ≈ -19.12</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.048207074348902</v>
+        <v>-0.3690170736914666</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-2.416830439586427</v>
+        <v>-3.004304129484495</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-2.292323045518366</v>
+        <v>-2.670536929759891</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.9088527048199069</v>
+        <v>0.360707368830731</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>4.489530365663633</v>
+        <v>4.070329371022609</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2.327783162663764</v>
+        <v>1.836070496100952</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>6.699398175177109</v>
+        <v>5.826614176419596</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>4.85575209602046</v>
+        <v>3.929787275447445</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>10.38490013529241</v>
+        <v>9.636936807145155</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>6.480035235830528</v>
+        <v>5.656169214853868</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>5.968446255399094</v>
+        <v>5.130064019821219</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>3.340426253843461</v>
+        <v>2.463493450134514</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>4.57635623555899</v>
+        <v>3.745379913843486</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.4345892531725042</v>
+        <v>-0.4879144334678003</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>3.703470818758184</v>
+        <v>2.819626626786196</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>4.297240820893116</v>
+        <v>3.380033217744369</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>3.37956973043201</v>
+        <v>2.479154094722496</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.1334682443831881</v>
+        <v>-0.8456420650413961</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.3493750927199315</v>
+        <v>-0.6315664105570349</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>2.894611534474066</v>
+        <v>1.978686192166293</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>2.353793642497166</v>
+        <v>1.412693123306404</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>2.278850321054499</v>
+        <v>2.13744028927011</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>0.9798361175245134</v>
+        <v>0.7823039869821358</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>2.479257119729198</v>
+        <v>2.220469701362717</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -16.51</t>
+          <t>X ≈ -16.45</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-5.636102199484448</v>
+        <v>-5.594055409773731</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3.722545441014923</v>
+        <v>2.318189887569275</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.747970623056851</v>
+        <v>-2.205256323926037</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.775159642763505</v>
+        <v>0.4661090849785836</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.4422295757261381</v>
+        <v>-0.6271300121677825</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-2.607770596668125</v>
+        <v>-1.285703544318288</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2.287645666896644</v>
+        <v>1.1825641316752</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.203011682548926</v>
+        <v>0.874960778691225</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>2.053617003491937</v>
+        <v>1.819722664675602</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>2.903149479627842</v>
+        <v>2.652760393958502</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.557119619122105</v>
+        <v>0.4765481163951435</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.147814289457685</v>
+        <v>-2.251479676240329</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.162684372520971</v>
+        <v>-0.4437044805710713</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>2.373333570206093</v>
+        <v>1.759750635196198</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>2.528373515447669</v>
+        <v>1.897324247261842</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.1207861513759951</v>
+        <v>0.005493868153372716</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.5565267937091107</v>
+        <v>0.7191730673629024</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-1.169629746989131</v>
+        <v>-0.2304377448687589</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.668812626021456</v>
+        <v>1.620170083837408</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>0.8550994147392217</v>
+        <v>1.834373319553585</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>1.125794836620585</v>
+        <v>2.087229498618115</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>1.86288833887555</v>
+        <v>2.012802564578564</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>1.325355218234151</v>
+        <v>1.437773533152189</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>4.502174986703146</v>
+        <v>3.735223799723371</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -13.84</t>
+          <t>X ≈ -13.77</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.7429410631307789</v>
+        <v>-0.7280281313071129</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-4.704709851155187</v>
+        <v>-1.679950090962649</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.110405185701055</v>
+        <v>3.09836901515559</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.575396129399344</v>
+        <v>5.332060391750048</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>5.144916513824704</v>
+        <v>7.176692158495328</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>7.914902848392401</v>
+        <v>8.039064639081857</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.6093087827027617</v>
+        <v>1.597591026688981</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>4.691744523110785</v>
+        <v>4.827495675607359</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.3506973116643763</v>
+        <v>-0.6967435601312744</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.3930984867603655</v>
+        <v>-0.7827854634850766</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.1207079221550984</v>
+        <v>0.9014344439332973</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.850383631095553</v>
+        <v>-0.7864276409908015</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.7888783158401651</v>
+        <v>0.2223661559050853</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.899483841222192</v>
+        <v>3.507970519493441</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.2105637313192901</v>
+        <v>1.415880382221289</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>3.292635978782073</v>
+        <v>4.804011552307038</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>3.160298286620318</v>
+        <v>4.701870658109875</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-2.039720971830015</v>
+        <v>-0.3811682094574564</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-2.553330476151906</v>
+        <v>-1.582822172546351</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-1.639562108628979</v>
+        <v>-0.6617718204617518</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>0.7344269626874151</v>
+        <v>0.8966540210941787</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-2.987807767734282</v>
+        <v>-3.430186600766675</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-2.714436974427677</v>
+        <v>-3.18786357675107</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-4.251014734975101</v>
+        <v>-4.769601220622945</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -11.16</t>
+          <t>X ≈ -11.11</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.983547252519237</v>
+        <v>0.5981117674969099</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>7.274826990397997</v>
+        <v>5.459902194647924</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-2.289454052853124</v>
+        <v>-4.096054960625089</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.5010930882189015</v>
+        <v>-2.135223623540753</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-2.088703265603819</v>
+        <v>-2.411397396940671</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.6017633602897732</v>
+        <v>-0.3387471104939408</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.1713437425258277</v>
+        <v>0.4962673862037263</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.075921366120454</v>
+        <v>0.1932444243943863</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.034736380447015</v>
+        <v>0.3221220748779032</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.182947956970146</v>
+        <v>-0.4701344571428905</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.785871477642246</v>
+        <v>-2.752907880088031</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.4521216482417</v>
+        <v>-1.750483442851831</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.944829920137444</v>
+        <v>-1.58431356352947</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.539506021069236</v>
+        <v>-1.831757007629832</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.3158180426641053</v>
+        <v>0.04283262765208207</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.9777333977838296</v>
+        <v>-0.6762292854105354</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-2.365861430037441</v>
+        <v>-2.058774334413833</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-1.214890547690885</v>
+        <v>-0.9116436466316529</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.9996914336419991</v>
+        <v>-0.05799900740947095</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-2.070139786379741</v>
+        <v>-1.764625579319308</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-2.612793874664902</v>
+        <v>-2.331905909022481</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-5.203048021268962</v>
+        <v>-3.688809406427708</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-5.559402179864946</v>
+        <v>-4.087514946928351</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-8.153140245694466</v>
+        <v>-6.815427734534865</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -8.486</t>
+          <t>X ≈ -8.436</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2.32182174662163</v>
+        <v>2.813787362553299</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>3.603526085544189</v>
+        <v>4.522426186018045</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.098292690633407</v>
+        <v>1.615167738426763</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.547686466535005</v>
+        <v>3.235146210812331</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>4.918678397423747</v>
+        <v>5.173240312281727</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.2385946374198653</v>
+        <v>1.456872867494532</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>3.255677493732989</v>
+        <v>2.877986237580153</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.358442550188144</v>
+        <v>0.9159601257046006</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.8606987636044323</v>
+        <v>-0.06121138274392024</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>2.795247973082382</v>
+        <v>2.465667798683995</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.7159539106184596</v>
+        <v>-1.134671625854153</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>3.872790163133601</v>
+        <v>4.674973100385884</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>2.216059297279905</v>
+        <v>2.458431970105444</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.455696526805063</v>
+        <v>2.211106173225936</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.2817996419246498</v>
+        <v>0.4258331809176994</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.8514233574143333</v>
+        <v>1.538282548506942</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>1.802137522217713</v>
+        <v>1.989126677072917</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.07413692423960327</v>
+        <v>-0.357195695010347</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.2524513427078503</v>
+        <v>-0.6975055195648281</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-2.779386275776105</v>
+        <v>-2.702751925638957</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-2.779629322743354</v>
+        <v>-2.715609365859898</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-3.399282777489226</v>
+        <v>-4.456910563288687</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-4.212938703760905</v>
+        <v>-4.215413388542032</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-2.11677163754571</v>
+        <v>-2.71286363197062</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -5.81</t>
+          <t>X ≈ -5.764</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.732087512667221</v>
+        <v>0.9982010225800479</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.287237281184311</v>
+        <v>-1.379836217021946</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.5749457903814346</v>
+        <v>-0.4972676720839786</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-5.586969320917689</v>
+        <v>-5.347943061935389</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-3.236599336487153</v>
+        <v>-1.897619081599665</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.1762073242310791</v>
+        <v>0.9197729732506659</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-6.509789776940856</v>
+        <v>-5.725623198918207</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-7.863288455347281</v>
+        <v>-7.091690444800079</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-4.595964100686885</v>
+        <v>-3.236810197403614</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-4.293607165659502</v>
+        <v>-3.4968352832718</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.868987678780002</v>
+        <v>-0.5632864459932421</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-4.298298342034904</v>
+        <v>-2.96836346561976</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-3.492704672697478</v>
+        <v>-2.480950128314831</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.562662474916905</v>
+        <v>-0.5994060638598526</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-4.908908191946388</v>
+        <v>-3.94051115841426</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-7.550704841429273</v>
+        <v>-6.58051182215862</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-7.149063169308171</v>
+        <v>-6.15446689066269</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-6.715522487555724</v>
+        <v>-5.754190735671791</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-4.346230298854216</v>
+        <v>-3.408901963611797</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-6.320374855473673</v>
+        <v>-5.86573659458648</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-4.166512113163073</v>
+        <v>-2.697172116241276</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-3.703948043898905</v>
+        <v>-1.704837693271045</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-3.431541993023345</v>
+        <v>-1.996886278722243</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-4.049791614043954</v>
+        <v>-2.695038320027656</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -3.135</t>
+          <t>X ≈ -3.094</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-6.902239417365003</v>
+        <v>-7.381806378905445</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-6.372195742500949</v>
+        <v>-5.487410853240085</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.4010990592529</v>
+        <v>-1.588365023432679</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.3432375929569602</v>
+        <v>1.678498712930143</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>3.272452229891464</v>
+        <v>3.116652830455713</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>3.026682542678088</v>
+        <v>2.4143672153618</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>5.283026238563508</v>
+        <v>4.198780827067026</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>5.870572784898734</v>
+        <v>5.613086523268848</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2.452978176100828</v>
+        <v>2.3117529570413</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.8160792246697639</v>
+        <v>1.091474450357182</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.2251823602501091</v>
+        <v>0.07684987688979561</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.05322354983770339</v>
+        <v>-0.1984192485374265</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.3102268833518451</v>
+        <v>-0.4496285261459718</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.694521250457178</v>
+        <v>-2.412362542630468</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-2.488138520440103</v>
+        <v>-2.2325176807053</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-1.028620352933771</v>
+        <v>-1.675351465798393</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.5702564360599993</v>
+        <v>-0.06289416088426236</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>1.331529371684063</v>
+        <v>0.6665759026791349</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>1.114518077918603</v>
+        <v>0.4504245821874377</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>3.472652096064877</v>
+        <v>3.244763708248065</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>0.3248545035553718</v>
+        <v>0.09747261180216071</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>1.116487622960825</v>
+        <v>0.4530838554995569</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>0.9573555858394798</v>
+        <v>1.127269052185717</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>2.448445753758634</v>
+        <v>2.258400735845477</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ -0.4606</t>
+          <t>X ≈ -0.4225</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.3487382871725302</v>
+        <v>0.4483560085197027</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.557358486654927</v>
+        <v>-2.143767393169654</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>3.542724879688961</v>
+        <v>2.700774306463131</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>10.37254924920649</v>
+        <v>9.61353839404326</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>8.622579009599747</v>
+        <v>7.930351304158869</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>5.510345492479296</v>
+        <v>4.803444721574934</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>6.624490383417147</v>
+        <v>5.885721559572062</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>3.990614040437549</v>
+        <v>3.235961683897699</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>5.917657977845415</v>
+        <v>5.240652685866365</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>2.789126205340104</v>
+        <v>2.099991280667801</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>6.833372125091962</v>
+        <v>6.124924199609694</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>4.669797992516408</v>
+        <v>3.972222815256309</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>4.490268334167006</v>
+        <v>3.796515071950999</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>3.329009457460621</v>
+        <v>2.610336056719994</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>3.616322590582968</v>
+        <v>3.149060414885916</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>1.380603058465091</v>
+        <v>1.361528259254754</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>2.192689302245142</v>
+        <v>2.196346554417417</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>3.505558575127282</v>
+        <v>3.478267573537345</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>3.72395742962135</v>
+        <v>3.693670720052289</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>3.441430147259126</v>
+        <v>3.437883488095231</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>2.898060492207485</v>
+        <v>2.873872419651946</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>2.348153349657323</v>
+        <v>2.329509626125962</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>3.383540318953997</v>
+        <v>3.045360287414731</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>0.4641061699960147</v>
+        <v>0.5261300787212093</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 2.214</t>
+          <t>X ≈ 2.248</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>196</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>3.949322965396682</v>
+        <v>3.583531246755832</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>3.109740084562993</v>
+        <v>1.812000588380201</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-4.419328277174962</v>
+        <v>-5.015358855549465</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.7978121543523145</v>
+        <v>-1.559945401375941</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.148370752635465</v>
+        <v>-3.358417896493059</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-4.497876343878588</v>
+        <v>-6.242668198837507</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-3.747299058332274</v>
+        <v>-5.509803987551969</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-4.024762941419858</v>
+        <v>-5.807757228421508</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-4.490398175790155</v>
+        <v>-5.677892984698687</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.711363765168045</v>
+        <v>-1.902104880403094</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.959568445859773</v>
+        <v>-3.153945421239683</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-4.759871988579199</v>
+        <v>-4.948022795420414</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-3.345739960262961</v>
+        <v>-3.520208541751508</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.538032841012914</v>
+        <v>-1.73776110755847</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-3.721899290526785</v>
+        <v>-4.44092031487645</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-4.145997294845401</v>
+        <v>-4.393068212021277</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-3.264562156714327</v>
+        <v>-4.50239362986585</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.1899436708130438</v>
+        <v>-0.06186419914608621</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>1.935256789629271</v>
+        <v>1.676571039465792</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>1.106266266966259</v>
+        <v>0.8725776946338186</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>2.394927121173971</v>
+        <v>1.83513652425583</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>2.320788210205272</v>
+        <v>2.27128209500281</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>2.085058841054668</v>
+        <v>2.006028764184975</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>2.009226587831336</v>
+        <v>1.844959497281138</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 4.889</t>
+          <t>X ≈ 4.92</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>5.323719138006112</v>
+        <v>5.942687218376122</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.001990246686546</v>
+        <v>-0.8086324559418046</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.744301180847927</v>
+        <v>2.675590098674256</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.7534423202958465</v>
+        <v>-0.2952471885531267</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-4.685214004151497</v>
+        <v>-4.117761542011174</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.3053058373654665</v>
+        <v>-0.4108794692658932</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.683354530295972</v>
+        <v>-1.198480848027586</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.571220132845866</v>
+        <v>-2.676410796458278</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.532779364151111</v>
+        <v>-2.545988342283877</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.2841933446809222</v>
+        <v>-0.3800922499613719</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.836698388191685</v>
+        <v>-1.88333017762865</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.8754488817017858</v>
+        <v>0.8010380376457746</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.2553292182040607</v>
+        <v>0.2846196862599371</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.278276400880721</v>
+        <v>-1.735097646260321</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-2.950814096918549</v>
+        <v>-1.815287299793887</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-0.5512723768874537</v>
+        <v>-0.07639966777875173</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-3.086316693645564</v>
+        <v>-1.95966581076874</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-3.800729512632174</v>
+        <v>-3.277199455336465</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-4.425211543740971</v>
+        <v>-4.253514475666663</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-1.226644377239573</v>
+        <v>-1.671159209283097</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-1.170645259286545</v>
+        <v>-1.050125744113494</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.2855555321109335</v>
+        <v>-1.125349987330559</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>1.193738457479554</v>
+        <v>0.306394185460249</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>0.5154965657021364</v>
+        <v>-0.4509588700659179</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 7.564</t>
+          <t>X ≈ 7.591</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.4778991560781094</v>
+        <v>0.4793673649106012</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>3.08770556893397</v>
+        <v>3.102638622840011</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>6.359658122314634</v>
+        <v>6.440011645609857</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.2404890796590422</v>
+        <v>0.1065656973303746</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-2.932498628337498</v>
+        <v>-2.463618234421126</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.199248092953674</v>
+        <v>1.136277892275935</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.16303796589191</v>
+        <v>-0.8044532867990384</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.3235470085966341</v>
+        <v>0.6145391340411877</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-2.580338316646753</v>
+        <v>-2.125814195839745</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.58717496751931</v>
+        <v>-0.6255761704231304</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-5.43561075064062</v>
+        <v>-4.370088103583406</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-3.948281128924478</v>
+        <v>-2.92442092278965</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-5.661879232730023</v>
+        <v>-4.61130575916966</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-5.889009788341539</v>
+        <v>-4.858771945687138</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-3.60742258258658</v>
+        <v>-2.669316630039482</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-4.785698433409934</v>
+        <v>-2.912786888042007</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-6.696833942300863</v>
+        <v>-4.745399205386953</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-5.264937978187199</v>
+        <v>-3.730087220461662</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-3.276014953279457</v>
+        <v>-1.795811358345418</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-2.50098389179275</v>
+        <v>-1.011600930981125</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-1.268382130764572</v>
+        <v>-0.4248991449436588</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-3.119376021167753</v>
+        <v>-2.230463674938143</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-3.436617285017064</v>
+        <v>-2.56736319646722</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-2.329017585577674</v>
+        <v>-0.9980274084638765</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 10.24</t>
+          <t>X ≈ 10.26</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.2593463048968374</v>
+        <v>0.09947258760282551</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.456912525406103</v>
+        <v>1.838389030196417</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.6725517835378554</v>
+        <v>-0.7392066976603502</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.371914048180329</v>
+        <v>-1.332785994842538</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.3500558312451076</v>
+        <v>-0.9460301164850051</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.5244722562509594</v>
+        <v>-0.1277241707292305</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.9447467253238031</v>
+        <v>-0.9214721381379931</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.1249821231199988</v>
+        <v>0.09831392859199184</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2.886620882142957</v>
+        <v>2.87377250115518</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>4.839681820986129</v>
+        <v>4.724858302690173</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>1.695348748727021</v>
+        <v>2.350740752789505</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>2.094452850391683</v>
+        <v>2.07447269121797</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>5.05200356901225</v>
+        <v>5.592561300743078</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>5.918377177881226</v>
+        <v>6.006484311317074</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>7.992742932436379</v>
+        <v>7.972330431660659</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>8.598020059910496</v>
+        <v>8.533006664680869</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>9.156967700313416</v>
+        <v>9.490636598744523</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>9.048920388314031</v>
+        <v>9.369782408036713</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>8.585652157109642</v>
+        <v>8.92519977152368</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>8.502501558478997</v>
+        <v>8.478609450244619</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>6.590092376814262</v>
+        <v>6.593419004687817</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>9.938903949651738</v>
+        <v>9.85323091191993</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>9.528447155284468</v>
+        <v>9.439906757775979</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>10.82247791575983</v>
+        <v>10.62046970136264</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 12.91</t>
+          <t>X ≈ 12.93</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>4.364181298420597</v>
+        <v>3.650209915024739</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2.182286904921689</v>
+        <v>2.204608762434823</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.97823608460962</v>
+        <v>1.554606599150937</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-3.044658990181098</v>
+        <v>-3.230911972561103</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.926082927793594</v>
+        <v>0.6788946119799135</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.7340684812581912</v>
+        <v>-0.9598374332193274</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.8843461366533631</v>
+        <v>-1.141506902548095</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.770593950597608</v>
+        <v>-2.028833295806933</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.192705403785382</v>
+        <v>2.880431672828664</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.03919898452054582</v>
+        <v>-0.3024120277347606</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.8539751875169728</v>
+        <v>-0.02145640883401256</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>1.806637514168408</v>
+        <v>1.496658331859159</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>4.376858471403999</v>
+        <v>3.374219314393137</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>3.543056311630409</v>
+        <v>2.533889742780339</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>4.739842376075636</v>
+        <v>4.251123994667452</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>4.722139575147978</v>
+        <v>4.207736074879385</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>2.74206490567127</v>
+        <v>2.310127924022858</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>3.254508152467409</v>
+        <v>3.380316424228667</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>5.322251385243554</v>
+        <v>5.388887557112838</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>5.509097195211538</v>
+        <v>5.603145972321613</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>8.670254730949218</v>
+        <v>8.64906713210398</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>8.594408769540117</v>
+        <v>9.188446312973134</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>7.017031630170308</v>
+        <v>7.037569779641892</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>6.941199376947075</v>
+        <v>8.090349219435076</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 15.59</t>
+          <t>X ≈ 15.61</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>131</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.9724348991200102</v>
+        <v>0.9692276628114982</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-3.588271984781201</v>
+        <v>-3.060957106506827</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-5.021299581673937</v>
+        <v>-4.33061134751582</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-2.699703131391523</v>
+        <v>-2.630220293752387</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-9.113953516148278</v>
+        <v>-8.215735652205858</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-5.130211636670126</v>
+        <v>-4.261701136207172</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-3.613612855041659</v>
+        <v>-2.056716484505642</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>3.716077511864157</v>
+        <v>4.43125632055866</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.7180227719155425</v>
+        <v>0.7706329711662292</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.05177324653467963</v>
+        <v>-0.03610433770833765</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.9876312768693154</v>
+        <v>0.9754615292242761</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>2.989318229215442</v>
+        <v>2.972438362745081</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>2.628381386015022</v>
+        <v>2.609700074009005</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>3.170775596258601</v>
+        <v>3.10720835309732</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>4.044299903174853</v>
+        <v>3.925087303179431</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>3.11992311383748</v>
+        <v>2.984220827300888</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>1.465088183401853</v>
+        <v>1.363209781760347</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>2.886965036832578</v>
+        <v>2.429459778235987</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>3.102856417756996</v>
+        <v>3.093933228494038</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>0.9996258918471099</v>
+        <v>1.041182030675628</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.306279054744877</v>
+        <v>-0.283192456260295</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-1.145483794779928</v>
+        <v>-0.3569894776631699</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-3.16108541817578</v>
+        <v>-2.728251472336858</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-1.710200114147064</v>
+        <v>-1.364263123064816</v>
       </c>
     </row>
     <row r="27">
@@ -2344,161 +2344,161 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-5.914327990716359</v>
+        <v>-4.916552693094339</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-6.249104789066173</v>
+        <v>-5.164678124255673</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-2.260162526825283</v>
+        <v>-1.050128307284957</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-4.775223314301769</v>
+        <v>-3.413050651749685</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-3.305604457667997</v>
+        <v>-1.909214264362909</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-5.828816366059236</v>
+        <v>-4.42913753369497</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-6.610672733391432</v>
+        <v>-5.250842691416672</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.3500915846030779</v>
+        <v>1.608405479725022</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.422086965531442</v>
+        <v>-0.06524609265112957</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.29353643740761</v>
+        <v>0.0250717826863962</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-3.742865134323402</v>
+        <v>-2.412829009900754</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.5071831304874053</v>
+        <v>0.9048756179190249</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.6184558572291152</v>
+        <v>-1.111916038290772</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>1.873120281673373</v>
+        <v>1.321143966521255</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>0.3067925023578155</v>
+        <v>-0.2717843359524252</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.9077660548248971</v>
+        <v>-1.49431203553366</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-1.421795924856305</v>
+        <v>-2.50009198601748</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-2.435727537768301</v>
+        <v>-3.53487562993805</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>0.5074365704287018</v>
+        <v>-0.603621809228656</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-0.2148085286941779</v>
+        <v>-0.7680199590138628</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>0.1517362124306985</v>
+        <v>0.06003150610749231</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>3.712253887385231</v>
+        <v>3.589425062936989</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>2.168546781685521</v>
+        <v>2.035607627716963</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>3.001805437553109</v>
+        <v>2.782631863524934</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 20.94</t>
+          <t>X ≈ 20.95</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>101</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>3.762301499575102</v>
+        <v>4.339336534240701</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-5.440832301539416</v>
+        <v>-4.797778332580613</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-3.920896476691205</v>
+        <v>-3.090646820993001</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-7.59823092536481</v>
+        <v>-6.633412251920483</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-6.944058715210836</v>
+        <v>-5.928381576653372</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-6.761682211507484</v>
+        <v>-5.765716779975314</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-3.581123656423522</v>
+        <v>-2.626981149382317</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-6.816372038576937</v>
+        <v>-5.893727206270221</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-5.784922173961078</v>
+        <v>-4.785209481219667</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-6.554166104082334</v>
+        <v>-5.586992167118865</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.3577711588105927</v>
+        <v>0.5959988954139845</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.627401181438479</v>
+        <v>-0.6597390767538087</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>2.179055562677711</v>
+        <v>3.159834431367472</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-4.937798442961558</v>
+        <v>-4.005534851420393</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-2.6355938567526</v>
+        <v>-1.73446040584615</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-3.034053405340558</v>
+        <v>-2.156610797732974</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-2.177871532416965</v>
+        <v>-1.277036798751496</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-1.292613226337181</v>
+        <v>-0.426466493206668</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-7.017315904818801</v>
+        <v>-6.118461920979378</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-7.820569104751783</v>
+        <v>-7.865053106653448</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-8.363115272717792</v>
+        <v>-7.449043197327676</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-5.468664204423924</v>
+        <v>-5.550797290676869</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-3.213991472139888</v>
+        <v>-2.346331349403961</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-3.289823725363192</v>
+        <v>-2.943886734280873</v>
       </c>
     </row>
     <row r="29">
@@ -2508,79 +2508,79 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-8.254757799385686</v>
+        <v>-8.695356298106667</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.4859850805211252</v>
+        <v>0.2337638395104165</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.3861763956475315</v>
+        <v>0.1236491774031023</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-9.581833867806317</v>
+        <v>-9.640950540103525</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-7.600276743547738</v>
+        <v>-7.621690891389093</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-7.42047762905657</v>
+        <v>-6.321592572918078</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-7.025152028616482</v>
+        <v>-5.96502150880999</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-3.833075735445703</v>
+        <v>-2.830544723620577</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.3184339869646777</v>
+        <v>0.7381961419728142</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.07019096404425795</v>
+        <v>1.090968268471563</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>2.663031617333388</v>
+        <v>3.658728435545335</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>4.688729081800069</v>
+        <v>5.670597996986871</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>4.718507156061861</v>
+        <v>5.700285319320336</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>6.821942948027342</v>
+        <v>7.75040586497925</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>5.033325887679787</v>
+        <v>5.925086770621228</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>4.483791402396093</v>
+        <v>5.338981895034081</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>5.512664963093002</v>
+        <v>6.382510377715882</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>1.919452166248561</v>
+        <v>2.813058498578989</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>3.298134244847304</v>
+        <v>4.16785598357508</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.003392038207920223</v>
+        <v>0.9388010181021329</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>0.6168524915004312</v>
+        <v>1.51876541112825</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>0.5410065300913303</v>
+        <v>1.45851444025886</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>1.978271940247801</v>
+        <v>2.85157421289356</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>0.7396489893501723</v>
+        <v>1.540009931247809</v>
       </c>
     </row>
     <row r="30">
@@ -2593,404 +2593,404 @@
         <v>81</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-4.228206960051054</v>
+        <v>-3.581322139940305</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-4.558217086967559</v>
+        <v>-3.834599530278439</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-2.329076913283771</v>
+        <v>-1.374534096514957</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-6.711573491157928</v>
+        <v>-5.678010553661075</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-5.817827548983637</v>
+        <v>-4.726371347160182</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.4810706749717184</v>
+        <v>1.62182815159634</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.9505750843863225</v>
+        <v>2.035517099378403</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.5547894393717243</v>
+        <v>0.4997140320523101</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-4.185228151605109</v>
+        <v>-3.079746039284416</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-2.501454333915028</v>
+        <v>-1.417717563985917</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-3.445014427891394</v>
+        <v>-2.391106282567549</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-9.864295897797398</v>
+        <v>-8.814730801991857</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-10.99460797180353</v>
+        <v>-9.918567087491262</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-7.524694268368606</v>
+        <v>-6.488894386440457</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-6.96116017078635</v>
+        <v>-5.954907253676545</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-5.148709315375953</v>
+        <v>-4.155350056305252</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-2.813490649884287</v>
+        <v>-3.028347844112787</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-1.683763452470927</v>
+        <v>-1.945090434625413</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-1.46787207154668</v>
+        <v>-1.697460711625581</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-6.219297866516882</v>
+        <v>-6.402719484919317</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-6.761844034482912</v>
+        <v>-5.739281362382577</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-6.837689995892013</v>
+        <v>-6.374606036539774</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-4.094079480940827</v>
+        <v>-3.661835748792264</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-4.169911734164103</v>
+        <v>-3.823974743081727</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 28.96</t>
+          <t>X ≈ 28.95</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-3.595377536712384</v>
+        <v>-4.362298859258139</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>2.675335082927255</v>
+        <v>1.949171354218372</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-5.384707775627589</v>
+        <v>-5.86289979685359</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3.818839527680986</v>
+        <v>3.380763578108635</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1.837877097461813</v>
+        <v>1.465861175714302</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>5.282118415834255</v>
+        <v>4.901483306302559</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>2.885665763689985</v>
+        <v>2.467057031774708</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>2.607454318936909</v>
+        <v>2.162136588366089</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>2.665475892385999</v>
+        <v>2.29006549805024</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-3.051222852433575</v>
+        <v>-3.424018784054383</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.5379822923737834</v>
+        <v>0.1269047551401528</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.250965693158669</v>
+        <v>-0.1496771993311867</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.8845971673482111</v>
+        <v>-1.264569316781916</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-1.089141652260459</v>
+        <v>-1.512803378215068</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.07159312173529742</v>
+        <v>-0.5556134978050409</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>2.196969696969646</v>
+        <v>1.645034783309754</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>2.063052559992173</v>
+        <v>1.541154371584746</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>3.624878522837641</v>
+        <v>3.047614528718178</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>0.5074365704287231</v>
+        <v>-0.01661176872621439</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-2.639050952936586</v>
+        <v>-3.080713848257339</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-3.181597120902616</v>
+        <v>-3.648158349638074</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-1.590776415645024</v>
+        <v>-2.083976609298333</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-1.316301703162971</v>
+        <v>-1.840342124019955</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-4.725467289719617</v>
+        <v>-5.281169642899577</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 31.64</t>
+          <t>X ≈ 31.63</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>55</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.517129713662477</v>
+        <v>2.821009635525762</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-2.220944767396752</v>
+        <v>-2.879442654723533</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-14.47670000181099</v>
+        <v>-15.04322766570608</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-6.16001944014856</v>
+        <v>-6.544720773605178</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-8.311763566884807</v>
+        <v>-8.638460731886333</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-15.27720379789968</v>
+        <v>-15.75425439861552</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-14.28333251744068</v>
+        <v>-14.73115459266643</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-12.75673112796915</v>
+        <v>-13.21789321789323</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-10.93271275175854</v>
+        <v>-11.2717824900273</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.8990330623761764</v>
+        <v>-1.15874307615573</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>4.778324262495246</v>
+        <v>4.568037392994057</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.9010900105623634</v>
+        <v>0.6550918021591272</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.2053608263472455</v>
+        <v>-0.4598003152916448</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-4.058347011171705</v>
+        <v>-4.344398013088394</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>0.6974582311586985</v>
+        <v>0.4279930595720103</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>4.166666666666664</v>
+        <v>2.807478896573485</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>2.214567711507371</v>
+        <v>0.8854166666666643</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>5.746090644049858</v>
+        <v>4.388896197868696</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>0.5074365704287587</v>
+        <v>0.9669947886508155</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>0.694282380396757</v>
+        <v>1.181581233709821</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>0.1517362124307269</v>
+        <v>-1.204045085852734</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>1.894072069203439</v>
+        <v>0.5389742103737802</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>2.168546781685492</v>
+        <v>0.7826086956521792</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>0.274532710280404</v>
+        <v>-1.197712116819105</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 34.31</t>
+          <t>X ≈ 34.3</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>19.52091759245041</v>
+        <v>20.65092165898617</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>22.49496432351232</v>
+        <v>23.63082127489517</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>14.48091863741147</v>
+        <v>15.92451426977787</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3.820683818856565</v>
+        <v>5.654692716130889</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>3.505703557186145</v>
+        <v>5.379134576031554</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-6.268484529746466</v>
+        <v>-4.141351172809074</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-3.696925999430356</v>
+        <v>-1.710626733428889</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-3.982074181142401</v>
+        <v>-2.015547176837508</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.6178899958980466</v>
+        <v>1.338188184459511</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-4.706565938305218</v>
+        <v>-2.683669762372737</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-4.439443033102265</v>
+        <v>-2.411434747768403</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-1.416305644097463</v>
+        <v>0.5377897493732107</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-12.46593829918885</v>
+        <v>-10.25452172291627</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-6.041623168976159</v>
+        <v>-4.051142881123582</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-10.06408389163996</v>
+        <v>-7.959103714621541</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-16.13636363636363</v>
+        <v>-13.84941259902769</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-9.603614106674442</v>
+        <v>-7.501680107526887</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-9.708454810495624</v>
+        <v>-7.634564212688488</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-12.82589676290468</v>
+        <v>-13.87171488876847</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-2.639050952936628</v>
+        <v>-3.979709088870827</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-6.514930454235966</v>
+        <v>-4.547153590251561</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-6.590776415645117</v>
+        <v>-4.622316112206789</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-6.316301703163063</v>
+        <v>-4.378681626928469</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-6.392133956386338</v>
+        <v>-4.540820621217932</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 36.99</t>
+          <t>X ≈ 36.98</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>3.017985632357309</v>
+        <v>4.790706605222738</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>5.346741932323205</v>
+        <v>4.544799769518868</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>3.990757337763057</v>
+        <v>3.290105667627287</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-2.090280105546505</v>
+        <v>-2.857852086736514</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>5.605545944088753</v>
+        <v>7.977700884275301</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>3.06061698647806</v>
+        <v>5.356856712495592</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>5.020563446295782</v>
+        <v>7.339552478040666</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.5983866041671746</v>
+        <v>1.479076479076454</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-3.193087702411233</v>
+        <v>-3.948550166794973</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-9.306741984157604</v>
+        <v>-10.30015721756987</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-11.70988784938987</v>
+        <v>-12.80569998074331</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-9.338776563600597</v>
+        <v>-10.30450415743681</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-13.12547172877244</v>
+        <v>-14.19717405266538</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.02580452267342537</v>
+        <v>-0.5565192252095841</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-6.010029837585904</v>
+        <v>-6.794229162650211</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-8.118345618345622</v>
+        <v>-9.010702921608328</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-5.549560052620386</v>
+        <v>-6.336805555555536</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-8.357103459144277</v>
+        <v>-9.247467438494937</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-13.54661748362537</v>
+        <v>-14.58856076690472</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-10.65706897095458</v>
+        <v>-11.59619654406796</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-8.496912436217933</v>
+        <v>-9.385863267670914</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-11.27546110032975</v>
+        <v>-12.23880356740398</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-13.7036890905504</v>
+        <v>-14.77294685990338</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-11.07681864107097</v>
+        <v>-12.15730807641506</v>
       </c>
     </row>
   </sheetData>
@@ -3180,1887 +3180,1887 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -39.25</t>
+          <t>X &gt; -39.15</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3342</v>
+        <v>3365</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.04524087705555502</v>
+        <v>0.02880184331797153</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.1843661062510051</v>
+        <v>-0.08318960160602984</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.1786637817526895</v>
+        <v>-0.08162105023055943</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.1016044185179368</v>
+        <v>0.02168180461423219</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1231017385170716</v>
+        <v>-0.03057334740320528</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.2468413322010861</v>
+        <v>-0.2118364264015113</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.2576141435677641</v>
+        <v>-0.2808562216111028</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.2082496502624736</v>
+        <v>-0.2142095309797298</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.1199595694067241</v>
+        <v>-0.06952321084494884</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.1607047643216362</v>
+        <v>-0.1089435120027957</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.1078384738362672</v>
+        <v>-0.02693542577981844</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.07124049750684236</v>
+        <v>0.0391605021887429</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.1630901697452245</v>
+        <v>-0.02195025066432521</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.06823176351047522</v>
+        <v>0.1027400340496598</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.08198899459430464</v>
+        <v>0.1197535812080517</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.1562641338760713</v>
+        <v>0.04651617118740603</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.272470481711764</v>
+        <v>-0.09916221826809135</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.2102469251909724</v>
+        <v>-0.03655079654893001</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-0.1857214815581543</v>
+        <v>0.01743989250839917</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.250128856901533</v>
+        <v>-0.04727005747451329</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.2667989146246086</v>
+        <v>-0.003440464820556599</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.265018839887496</v>
+        <v>-0.06096638956679357</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.3017439207320649</v>
+        <v>-0.09677336020046567</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.3298957756561833</v>
+        <v>-0.1819077131989459</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -36.57</t>
+          <t>X &gt; -36.48</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3323</v>
+        <v>3345</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.0213352483019662</v>
+        <v>0.02031864006042383</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.2076813280497305</v>
+        <v>-0.1205798958608</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.2236938133404465</v>
+        <v>-0.141266881392319</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.1421565254380397</v>
+        <v>-0.03384680359302195</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.07208514810359645</v>
+        <v>0.004388689797814038</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.2873973146095992</v>
+        <v>-0.268081338847459</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.2639018463729386</v>
+        <v>-0.3030544358333742</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.2126733390445565</v>
+        <v>-0.2342032987674258</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.1241181798811013</v>
+        <v>-0.08942318266799276</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.1307287986704964</v>
+        <v>-0.09457354518059446</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.01916127848376448</v>
+        <v>0.04586510429408008</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.01072513801307196</v>
+        <v>0.08423578894386452</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.09667935408551642</v>
+        <v>0.02941845163868351</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.03000300030002734</v>
+        <v>0.1265408840800148</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.0400742877984257</v>
+        <v>0.147730686286387</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.1181508874393913</v>
+        <v>0.0707167026087987</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.2042147072750424</v>
+        <v>-0.0453709228321415</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.1710561922919638</v>
+        <v>-0.01141849788020011</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.1175634295712982</v>
+        <v>0.07147240059113358</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.2134422964893545</v>
+        <v>0.005110645474530884</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.2270972211231168</v>
+        <v>0.052607461122399</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.224861628677651</v>
+        <v>-0.03467383264980128</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.2633534480486972</v>
+        <v>-0.07214324696587227</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.2912211266139906</v>
+        <v>-0.1568098203114232</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -33.9</t>
+          <t>X &gt; -33.81</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3288</v>
+        <v>3312</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.01474201043509993</v>
+        <v>0.01272880744295435</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.2131579099685439</v>
+        <v>-0.06704496837629392</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.2141266367498886</v>
+        <v>-0.07474973115186856</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.1544167564877483</v>
+        <v>0.01001578113137214</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.1103003384652226</v>
+        <v>0.02152452167056396</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2996270155707634</v>
+        <v>-0.225408244769369</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.2979752774722684</v>
+        <v>-0.2824292873135263</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.273523283968693</v>
+        <v>-0.2567215371543625</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.1239367807971377</v>
+        <v>-0.06867841045793455</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.06185543762325807</v>
+        <v>-0.005843059756010405</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.1085977684441062</v>
+        <v>0.1934645973686315</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.08981550075846201</v>
+        <v>0.2049222364661034</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.01541643116237168</v>
+        <v>0.1305753036726003</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.05433836288420224</v>
+        <v>0.2311588803492981</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.009488805197740646</v>
+        <v>0.1991463266602409</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.09469696969696884</v>
+        <v>0.1158031024880515</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.08919832518733273</v>
+        <v>0.08999635934517869</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.02418037212282798</v>
+        <v>0.1557875343802948</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.06347141620962304</v>
+        <v>0.1469767000165234</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.1319630631026598</v>
+        <v>0.07784178859522228</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.1095825356701852</v>
+        <v>0.1616480445462827</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.136875706425208</v>
+        <v>0.07427897802618588</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.1786712177064445</v>
+        <v>0.03404244150186031</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.2972434454373882</v>
+        <v>-0.1403998638546824</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -31.22</t>
+          <t>X &gt; -31.14</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3248</v>
+        <v>3268</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.01588535142523995</v>
+        <v>-0.0005166642614042871</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.3342530427487347</v>
+        <v>-0.169312152622247</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.2560059849939833</v>
+        <v>-0.09950999001393512</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.2478462147931779</v>
+        <v>-0.03611677869565</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.1683598877185588</v>
+        <v>-0.02077704570949379</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.3624310706269824</v>
+        <v>-0.2731338139626587</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.2897849061581255</v>
+        <v>-0.2288977876377629</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.353469841563971</v>
+        <v>-0.2901386696695951</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.1893960828794334</v>
+        <v>-0.1012898696412847</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.1170957263804837</v>
+        <v>-0.02694982370433507</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.009261194870795464</v>
+        <v>0.1104163794449775</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.05556468143154092</v>
+        <v>0.09522483985313812</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.1176631904572361</v>
+        <v>0.03480724244491284</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.01367540068923745</v>
+        <v>0.170550126020828</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.07022451184260348</v>
+        <v>0.1472484761115282</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.1638001638001612</v>
+        <v>0.05523114432573806</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.1258875321736781</v>
+        <v>0.0609891857506355</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.0587928559781048</v>
+        <v>0.1294415413462318</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.1319732051630567</v>
+        <v>0.08706811587357066</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.2651272136992162</v>
+        <v>-0.04702512325839336</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.20507707578831</v>
+        <v>0.07607497751403969</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.2318020566707162</v>
+        <v>-0.01148450522252631</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.2467418385893012</v>
+        <v>-0.0249777222126184</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.3042850237097738</v>
+        <v>-0.1384042276458501</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -28.55</t>
+          <t>X &gt; -28.47</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3190</v>
+        <v>3213</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.0184490559856556</v>
+        <v>-0.001024501076884121</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.3619167466727475</v>
+        <v>-0.1994246529233763</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.4120848430190662</v>
+        <v>-0.2614263657988971</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.3285919927243413</v>
+        <v>-0.1557537035235583</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.1168932214339122</v>
+        <v>0.01944067299555741</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.2866502124321713</v>
+        <v>-0.2090251545015178</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.1986960036378846</v>
+        <v>-0.1811926240493591</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.2896999600914256</v>
+        <v>-0.2691933277616698</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.1234077859770366</v>
+        <v>-0.04829881535057012</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.06699740507611551</v>
+        <v>-0.007659886026985419</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.03784275924765268</v>
+        <v>0.1274129213714517</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.004235565809786124</v>
+        <v>0.1166844730541214</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.07833250799081526</v>
+        <v>0.07426239619042008</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.0003094059406052452</v>
+        <v>0.1855430356239864</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.07658779911104574</v>
+        <v>0.1424561259903854</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.1826425606913418</v>
+        <v>0.03928155526220678</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.1416184857798513</v>
+        <v>0.04690734989647893</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-0.07140850261076537</v>
+        <v>0.1187953760437352</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-0.05594371126144182</v>
+        <v>0.1652545773394607</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.2261935119013287</v>
+        <v>-0.005860482174547599</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.155185178111104</v>
+        <v>0.1290621054634187</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.1810019795548499</v>
+        <v>0.04130702530381569</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.2325244128673916</v>
+        <v>-0.007683774789633446</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.2897306126036341</v>
+        <v>-0.1202710393780322</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -25.87</t>
+          <t>X &gt; -25.8</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3114</v>
+        <v>3136</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.05233036702048111</v>
+        <v>-0.08669774903640359</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.3061918760447071</v>
+        <v>-0.1253556380295038</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.3865124150100243</v>
+        <v>-0.2526185286502169</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.4433275038825926</v>
+        <v>-0.2563851802870474</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.2822533103562819</v>
+        <v>-0.1016641950897963</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.4926736628715389</v>
+        <v>-0.3891750335361621</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.4797764702505987</v>
+        <v>-0.4362846483839675</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.3105606219388051</v>
+        <v>-0.2648633960161462</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.1412370705769916</v>
+        <v>-0.04166614717675543</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.06468252374171612</v>
+        <v>0.01969741000149838</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.1238520701420853</v>
+        <v>-0.007450651363107852</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.1602281216460142</v>
+        <v>-0.02990299973529886</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.1448617176128053</v>
+        <v>-0.01435443609933884</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.09095980020536842</v>
+        <v>0.07391095067512765</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.1537412723636251</v>
+        <v>0.04643503095515911</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.148748859511187</v>
+        <v>0.05418257457488096</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.295699976587926</v>
+        <v>-0.1263555255064119</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-0.2212753233161351</v>
+        <v>-0.04950435765470473</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-0.1786807748742874</v>
+        <v>0.02461974885459739</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.2614584791286063</v>
+        <v>-0.09230411660865201</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.2075836464079259</v>
+        <v>0.0279627915836258</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.2642894665650601</v>
+        <v>-0.09200093302964518</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-0.2916896111351903</v>
+        <v>-0.1163393438760352</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.3484602248512871</v>
+        <v>-0.2277445843515764</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -23.2</t>
+          <t>X &gt; -23.13</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3042</v>
+        <v>3066</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.03327283984398122</v>
+        <v>-0.03840868787698071</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.448517445419931</v>
+        <v>-0.2344926680014225</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.4316109451316237</v>
+        <v>-0.270500392978775</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.6037211632620441</v>
+        <v>-0.3579423036178753</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.3002429611388422</v>
+        <v>-0.0632347882393347</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.4873244714143681</v>
+        <v>-0.3286533589793947</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.3905168266180041</v>
+        <v>-0.2932428131881792</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.2434747548516114</v>
+        <v>-0.1431746313124265</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.07114033708477052</v>
+        <v>0.08225184093261362</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.07271669575334982</v>
+        <v>0.06618084620075848</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.2052088397800631</v>
+        <v>-0.05157438943864889</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.2031534817979477</v>
+        <v>-0.03566365622713619</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.1609508103085204</v>
+        <v>0.03848553409954292</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.1005670685023858</v>
+        <v>0.1153490019252104</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.1493018529641219</v>
+        <v>0.1027898075394944</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.1582215598608983</v>
+        <v>0.09795029895119711</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-0.2726859335029133</v>
+        <v>-0.08431974726109814</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.1940191149575625</v>
+        <v>-0.002675771828272389</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.1555105907134049</v>
+        <v>0.06826473329427785</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.3103138113301185</v>
+        <v>-0.121350362381385</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.2751931800159326</v>
+        <v>-0.01799099657283421</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.3314684874803788</v>
+        <v>-0.138991891321119</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.4317579415242747</v>
+        <v>-0.2020668830892589</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.4223772173987825</v>
+        <v>-0.2471102073130851</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -20.52</t>
+          <t>X &gt; -20.46</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2954</v>
+        <v>2972</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.008665163729148162</v>
+        <v>-0.04413325639984578</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.4090021082824578</v>
+        <v>-0.2386340326691254</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.6172781004963781</v>
+        <v>-0.4703633440980113</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.7393915930501294</v>
+        <v>-0.5082840200102581</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.4839435322908301</v>
+        <v>-0.3146732593052946</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.5813511858428768</v>
+        <v>-0.4593482323956835</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.4245185855805857</v>
+        <v>-0.3978111007577283</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.2308729356252002</v>
+        <v>-0.1998820637774799</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.04654279364372371</v>
+        <v>0.1291866380621869</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.01858724033007775</v>
+        <v>0.10417101277244</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.1489765364896911</v>
+        <v>0.007649741758271489</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.2397171827863573</v>
+        <v>-0.06779242055747403</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.1292124764661011</v>
+        <v>0.04382751227984727</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.1279378950040666</v>
+        <v>0.06386977546108596</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.05733397601390067</v>
+        <v>0.1730450555465168</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.1516686104802218</v>
+        <v>0.08325680993529261</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.2317802667555</v>
+        <v>-0.0679233803289705</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.14764399968481</v>
+        <v>0.02049763873810662</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.02078567485587257</v>
+        <v>0.1876867604345165</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.2117351990488459</v>
+        <v>-0.08185962650522782</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.159389928928789</v>
+        <v>0.0427081609005171</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.2150434431597361</v>
+        <v>-0.046096401596607</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-0.2926130398804361</v>
+        <v>-0.08520159698151986</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.2806467074582883</v>
+        <v>-0.126502034841856</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -17.85</t>
+          <t>X &gt; -17.78</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2827</v>
+        <v>2847</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.03803516264110129</v>
+        <v>-0.0298689511095489</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.3188025334414135</v>
+        <v>-0.1172048924858018</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.5420284690786872</v>
+        <v>-0.3737628178571484</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.8134372335982292</v>
+        <v>-0.5464378393306433</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.7073716133096468</v>
+        <v>-0.5072005964289232</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.712040985015264</v>
+        <v>-0.5601305790982067</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.74455304918731</v>
+        <v>-0.6710998818069527</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.4593842122502494</v>
+        <v>-0.381198771681639</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.4178970303355456</v>
+        <v>-0.2882593651465797</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.310531016231181</v>
+        <v>-0.1395942753414232</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.4237953177312406</v>
+        <v>-0.2172542922276435</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.4005513591047105</v>
+        <v>-0.1789307183574351</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.3406051989376948</v>
+        <v>-0.1186923508025046</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.1532088351591554</v>
+        <v>0.08809633890194135</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.2262841737274073</v>
+        <v>0.05684460018825632</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.3515311848645126</v>
+        <v>-0.06149101267662616</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.3940163649666104</v>
+        <v>-0.1797550221910811</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.1602726714204366</v>
+        <v>0.05852625235679909</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.006024141050168907</v>
+        <v>0.223656780235693</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.3512845570811862</v>
+        <v>-0.1723296747433523</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.2722920561205413</v>
+        <v>-0.01744221503933119</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.3270789960621769</v>
+        <v>-0.1419664705668779</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.3497764792120464</v>
+        <v>-0.1232901807523135</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.4046324825034944</v>
+        <v>-0.2295478609836152</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -15.17</t>
+          <t>X &gt; -15.11</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2704</v>
+        <v>2725</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.2166106382212263</v>
+        <v>0.2192432499755981</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.5026360396759344</v>
+        <v>-0.2262390808038717</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.4871723725774757</v>
+        <v>-0.2917656774019548</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.8856995915096562</v>
+        <v>-0.5917702153914632</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.7596648626629801</v>
+        <v>-0.5018312794674102</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.6258077223550202</v>
+        <v>-0.527646211481013</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.882482206760649</v>
+        <v>-0.7540896101169849</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.5350035521394148</v>
+        <v>-0.4374378414597899</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.5303216701879023</v>
+        <v>-0.3826350743716489</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.4567154470709198</v>
+        <v>-0.2646097871412678</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.5139035045777405</v>
+        <v>-0.2483162716228549</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.3665597391219393</v>
+        <v>-0.08614137051828408</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.3634989183494568</v>
+        <v>-0.1041413490293834</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.2681366146931552</v>
+        <v>0.01325530251740048</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.3515884990855938</v>
+        <v>-0.02555485557063975</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.362027353177794</v>
+        <v>-0.06448996880919822</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.4372548296548899</v>
+        <v>-0.2200006100536811</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-0.1143588695362112</v>
+        <v>0.07146335608580046</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-0.02412489136531804</v>
+        <v>0.1611339827900338</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.4061607510656131</v>
+        <v>-0.2621710565063751</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.3358884643332445</v>
+        <v>-0.1116697192838103</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.4266965930286588</v>
+        <v>-0.2384368640669692</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.4259751474020774</v>
+        <v>-0.1931800057418087</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.6278341536249528</v>
+        <v>-0.4070532344170985</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -12.5</t>
+          <t>X &gt; -12.44</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2567</v>
+        <v>2584</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.2678216172181891</v>
+        <v>0.2709325939232983</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.2783726535549178</v>
+        <v>-0.1469150667046435</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.5724345952047187</v>
+        <v>-0.4767536772667498</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.070417204974611</v>
+        <v>-0.9150132941867213</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.074790553577976</v>
+        <v>-0.9208219159816267</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.081622817092999</v>
+        <v>-0.9951021828159128</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.9620986327663061</v>
+        <v>-0.882412740840536</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.8139534883720856</v>
+        <v>-0.7247271703709686</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.5399081669225083</v>
+        <v>-0.365495253747774</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.4601106646644268</v>
+        <v>-0.2363347212107456</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.5348882318048211</v>
+        <v>-0.3110542170150481</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.2873685146574303</v>
+        <v>-0.04792915529512953</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.3407965508168473</v>
+        <v>-0.1219577415200064</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.3838218513353056</v>
+        <v>-0.1774392971705367</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.3591149475405828</v>
+        <v>-0.1042090229578818</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.5570756104736603</v>
+        <v>-0.3301473660527705</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.629255132315464</v>
+        <v>-0.4885702109867509</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.01160288667129095</v>
+        <v>0.0961619051344087</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.1108580323260568</v>
+        <v>0.256295677024724</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.3403345001944871</v>
+        <v>-0.2403662160583409</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.3930108692813619</v>
+        <v>-0.1666904806589287</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.2900108778223114</v>
+        <v>-0.06427404948698978</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.3038406439729826</v>
+        <v>-0.02977041459926966</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.4344661210402307</v>
+        <v>-0.1690039828478191</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -9.823</t>
+          <t>X &gt; -9.771</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2408</v>
+        <v>2428</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.1545324245218254</v>
+        <v>0.2499111972686592</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.7771096732345271</v>
+        <v>-0.507155384979356</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.4590599715477097</v>
+        <v>-0.2442120791596949</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.10800961966072</v>
+        <v>-0.836614277967918</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.007841998257334</v>
+        <v>-0.8250518274191876</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.192776638606233</v>
+        <v>-1.037273266540055</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.014312099356097</v>
+        <v>-0.970993506828556</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.7966557755141181</v>
+        <v>-0.783707223411902</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.5072347093019047</v>
+        <v>-0.4096749503151642</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.4123817902970615</v>
+        <v>-0.2213129918839698</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.3862560324326623</v>
+        <v>-0.1541641134568223</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.2104599813352124</v>
+        <v>0.06146065889713981</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.2348823873110319</v>
+        <v>-0.02800077766765696</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.307512140792241</v>
+        <v>-0.07114870292357267</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.3619738378542792</v>
+        <v>-0.113656509570383</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.5292996187035897</v>
+        <v>-0.3079114601961734</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.5145871915605653</v>
+        <v>-0.387683949349757</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.06785007765682138</v>
+        <v>0.160913826911802</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.1841875028779327</v>
+        <v>0.2764892399455334</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.2261156295535258</v>
+        <v>-0.1424319241849119</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.2464388186767223</v>
+        <v>-0.02757449761743658</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>0.03439647508798771</v>
+        <v>0.1686038400034349</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>0.04318356043184224</v>
+        <v>0.2309413428320894</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>0.07519716210762084</v>
+        <v>0.2580314806048918</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -7.148</t>
+          <t>X &gt; -7.1</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2224</v>
+        <v>2248</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.02477568486053627</v>
+        <v>0.04461862175654119</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.139536372701833</v>
+        <v>-0.9098798879951602</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.5879056953972182</v>
+        <v>-0.3930948047671663</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.410459295856768</v>
+        <v>-1.162644922087345</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.498165628115842</v>
+        <v>-1.305342123302708</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.311199442018463</v>
+        <v>-1.236982476560613</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.367584619647644</v>
+        <v>-1.279185835117502</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.9749552772808556</v>
+        <v>-0.9198015841062883</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.6204090613768898</v>
+        <v>-0.4375768373982538</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.6777612311521963</v>
+        <v>-0.4364626993137861</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.3589788698489471</v>
+        <v>-0.0756537254534777</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.548282835014291</v>
+        <v>-0.3079487002967909</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.4376581381944646</v>
+        <v>-0.2270923677918475</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.4533891168884097</v>
+        <v>-0.253891531085003</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.3686069547837079</v>
+        <v>-0.1568540826521811</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-0.6435320951450052</v>
+        <v>-0.4557383826012327</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.7062586606861032</v>
+        <v>-0.577997967479682</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>0.06732994286760174</v>
+        <v>0.2023994647881153</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.2203122994551734</v>
+        <v>0.3544781441767952</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.01487381349913619</v>
+        <v>0.06257590511302169</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.03685830934747969</v>
+        <v>0.1876596110496536</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>0.3184778520997682</v>
+        <v>0.5389742103738016</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>0.3953087837283675</v>
+        <v>0.5869661878709422</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>0.2565470987695875</v>
+        <v>0.4959145412203654</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -4.473</t>
+          <t>X &gt; -4.429</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2039</v>
+        <v>2061</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.1841772010658502</v>
+        <v>-0.04190244032692192</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.126135358445204</v>
+        <v>-0.867239502974293</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.5890815573039987</v>
+        <v>-0.3836429240353638</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.031521407364238</v>
+        <v>-0.7829017138624081</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.340436233290589</v>
+        <v>-1.251603262942922</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.446152974022475</v>
+        <v>-1.432670622661881</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.9010284871811152</v>
+        <v>-0.8757487720264194</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.3499716392512795</v>
+        <v>-0.3598097272650733</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.2597039695316994</v>
+        <v>-0.183594965335665</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.3496928162998927</v>
+        <v>-0.1587869723850375</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.2219746375526057</v>
+        <v>-0.03140951451658225</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.2080411141713299</v>
+        <v>-0.06656220776142163</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.1604714737103734</v>
+        <v>-0.02259387132517787</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.3527439127514498</v>
+        <v>-0.2225420805130014</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>0.0433379833600398</v>
+        <v>0.1864471658522007</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.01683912895442319</v>
+        <v>0.09997856703353136</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.1216981731456031</v>
+        <v>-0.0720301418439675</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>0.6827432335141523</v>
+        <v>0.742856702772599</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.6346381359864353</v>
+        <v>0.6959396095608028</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>0.5572290274843397</v>
+        <v>0.6004674322570338</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>0.3378282790320668</v>
+        <v>0.4494080501585387</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>0.6834355719427165</v>
+        <v>0.7425612195836919</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>0.7425218262487476</v>
+        <v>0.8214059798422824</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>0.6472644415211803</v>
+        <v>0.7854381632744065</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -1.798</t>
+          <t>X &gt; -1.758</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1809</v>
+        <v>1829</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.6699711183088297</v>
+        <v>0.8891296612314363</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.4591403952982631</v>
+        <v>-0.2811926176480739</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.3586979058677144</v>
+        <v>-0.2308296232916902</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.206311108897623</v>
+        <v>-1.095118717151571</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.92692840937233</v>
+        <v>-1.805695889333563</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-2.014838528937403</v>
+        <v>-1.920649178387137</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.687281990177944</v>
+        <v>-1.519428852392558</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.140864517943662</v>
+        <v>-1.117443368666862</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.6045999858365505</v>
+        <v>-0.500118047889778</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.4979114837531995</v>
+        <v>-0.3173767209231428</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.2788271027237599</v>
+        <v>-0.04514170631880887</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.2277249393768201</v>
+        <v>-0.04983676573844065</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.1414312613181465</v>
+        <v>0.03157345503808529</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.05500550055005249</v>
+        <v>0.05522628865662682</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>0.3651951397304245</v>
+        <v>0.4932814164816932</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.111800827659863</v>
+        <v>0.3251707855228645</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.209674712735044</v>
+        <v>-0.07318899782134736</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>0.6002552225804507</v>
+        <v>0.7525325615050633</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.5736252080459181</v>
+        <v>0.7270820296541061</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.1865561110810603</v>
+        <v>0.2650509554774132</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>0.3394777916686849</v>
+        <v>0.4940493960845487</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>0.6283764388669013</v>
+        <v>0.779280054175004</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>0.7152074178983483</v>
+        <v>0.7826086956521792</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>0.4182585256479854</v>
+        <v>0.5985998271144908</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.8769</t>
+          <t>X &gt; 0.9129</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1598</v>
+        <v>1617</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.712386717413807</v>
+        <v>0.9469181673383531</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.1820915734733219</v>
+        <v>-0.03699604843930615</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.8738419657878964</v>
+        <v>-0.6151833852632507</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-2.735184410249289</v>
+        <v>-2.499098499200613</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-3.319885897108946</v>
+        <v>-3.082159714330707</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-3.008464203855382</v>
+        <v>-2.802224878320317</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-2.784768830496198</v>
+        <v>-2.490295820442334</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.818425203687354</v>
+        <v>-1.688205193740259</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.465799253882167</v>
+        <v>-1.252773209025392</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.9319321047786531</v>
+        <v>-0.6343105591032838</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.217922244819583</v>
+        <v>-0.8540804645481472</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.8743941124866197</v>
+        <v>-0.5771568839641006</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.7530011077808254</v>
+        <v>-0.4620367012918649</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.5018310050183032</v>
+        <v>-0.279766457681923</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.0640838916399602</v>
+        <v>0.1450902305437225</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-0.05573188241517357</v>
+        <v>0.1892970783916681</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-0.5268829775415682</v>
+        <v>-0.3707409688013215</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.2166388224631817</v>
+        <v>0.3951696533103615</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.1576551837953488</v>
+        <v>0.3381415210799403</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.2432176196032785</v>
+        <v>-0.1509295620952358</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>0.001642403800303782</v>
+        <v>0.1820379668969849</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>0.4012970094696584</v>
+        <v>0.5760341239006692</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>0.3628806080593492</v>
+        <v>0.4859461492986554</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.4122048003930132</v>
+        <v>0.6081011175655604</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 3.552</t>
+          <t>X &gt; 3.584</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1402</v>
+        <v>1421</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.2598621064261906</v>
+        <v>0.5832473977635289</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.6422905784484456</v>
+        <v>-0.2920300673109679</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.3781819679049718</v>
+        <v>-0.008262630741015187</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-3.006029604368983</v>
+        <v>-2.628636857521265</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-3.48366404854746</v>
+        <v>-3.044055137480733</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-2.800243961740868</v>
+        <v>-2.327680972042089</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.650206830028388</v>
+        <v>-2.073811935323768</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.509978558469406</v>
+        <v>-1.119991119991127</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.042959461661084</v>
+        <v>-0.6424118606566651</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.8229673362791345</v>
+        <v>-0.45944237685503</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.9744396090108296</v>
+        <v>-0.5368577119010425</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.3312031968559879</v>
+        <v>0.02572117278849362</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.3905354764780569</v>
+        <v>-0.04021989571122475</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.3569696927109263</v>
+        <v>-0.07866374735412762</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>0.4472797447236729</v>
+        <v>0.7776434092223639</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>0.5160883892227162</v>
+        <v>0.8213474632762114</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-0.1441546472149824</v>
+        <v>0.1991421568627416</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>0.22037081228018</v>
+        <v>0.4582088053733173</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-0.09085402786189434</v>
+        <v>0.1535305530267195</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.4318758519625021</v>
+        <v>-0.2921029768164942</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-0.3329394825087206</v>
+        <v>-0.0459756272214733</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>0.1329515919631064</v>
+        <v>0.3422068175417579</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>0.1221195997376014</v>
+        <v>0.2762795817281258</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>0.1889406988681159</v>
+        <v>0.4374999617427235</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 6.227</t>
+          <t>X &gt; 6.255</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1236</v>
+        <v>1253</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.4202351971678766</v>
+        <v>-0.1353367122627347</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.5939813997044823</v>
+        <v>-0.2227649425783369</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.6632403843232382</v>
+        <v>-0.3681088067520051</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-3.308561553524434</v>
+        <v>-2.941493572913636</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-3.322290834445297</v>
+        <v>-2.900094502236428</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-3.135324648347918</v>
+        <v>-2.584682290850076</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-2.780059161545843</v>
+        <v>-2.191174762670748</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.367449350260266</v>
+        <v>-0.9113091521966439</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.842870380905957</v>
+        <v>-0.3871837290418512</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.9716636736896263</v>
+        <v>-0.4700815000139613</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.8586346273409049</v>
+        <v>-0.3563250907978954</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.4932616475360803</v>
+        <v>-0.07823192641023979</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.4086942457931713</v>
+        <v>-0.08377380614310681</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.09893011863635337</v>
+        <v>0.1434279485886023</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>0.9036580438439046</v>
+        <v>1.125298923280404</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>0.6594394306258664</v>
+        <v>0.9417157936969858</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.2509900936486602</v>
+        <v>0.4885912698412653</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>0.7604215031664694</v>
+        <v>0.9590456671444585</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.4912684216817382</v>
+        <v>0.7444192719576748</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.3251350953314329</v>
+        <v>-0.1072015825192949</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-0.2204320723589461</v>
+        <v>0.08865902532271264</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>0.1891588594358353</v>
+        <v>0.5389742103738016</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-0.0218033212859936</v>
+        <v>0.272241869495879</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>0.1450828720926722</v>
+        <v>0.5566229336053325</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 8.902</t>
+          <t>X &gt; 8.926</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1067</v>
+        <v>1080</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.5624889044767443</v>
+        <v>-0.2338031986988369</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.177116449095209</v>
+        <v>-0.7554453285203522</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.775583259320236</v>
+        <v>-1.458668842176635</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-3.794507428016708</v>
+        <v>-3.42974751157309</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-3.384029243847564</v>
+        <v>-2.970011534025367</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-3.663480968197945</v>
+        <v>-3.180724986850812</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-3.036175920745009</v>
+        <v>-2.413306999083531</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.635282887886149</v>
+        <v>-1.15572744249215</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.5676763029863707</v>
+        <v>-0.108680885749223</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.8741740685750941</v>
+        <v>-0.4451735574391478</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.1336965159654113</v>
+        <v>0.2866202806945921</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.05397199103435213</v>
+        <v>0.3776853850468314</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.4233472376110754</v>
+        <v>0.6414697381842913</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.8181490417949391</v>
+        <v>0.944706264986479</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>1.618159099014242</v>
+        <v>1.733140118395539</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>1.521883947047655</v>
+        <v>1.559150019568143</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>1.351442073100841</v>
+        <v>1.326999003373196</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>1.714766163287145</v>
+        <v>1.710175287103588</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>1.087960914997986</v>
+        <v>1.151326585885862</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>0.01949325199935714</v>
+        <v>0.03766979459543052</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.05444935457961009</v>
+        <v>0.1709234359301917</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>0.7131910945080051</v>
+        <v>0.9825971308913637</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>0.5190622456029956</v>
+        <v>0.7271045328399737</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>0.5369507046571371</v>
+        <v>0.8056548865478987</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 11.58</t>
+          <t>X &gt; 11.6</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>921</v>
+        <v>930</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.6105440831289357</v>
+        <v>-0.2875573577797539</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.594671530829395</v>
+        <v>-1.17380570895854</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.950439497609302</v>
+        <v>-1.57471112355023</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-4.178545032203573</v>
+        <v>-3.767967111045756</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-3.864984855400188</v>
+        <v>-3.296460149757678</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-4.327369318653467</v>
+        <v>-3.673144473322033</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-3.367716270942076</v>
+        <v>-2.653925525042482</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.914325984093423</v>
+        <v>-1.357992179763791</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.115263044602962</v>
+        <v>-0.5897217546047671</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.779953612414339</v>
+        <v>-1.279049663911621</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.4236428880013463</v>
+        <v>-0.04630237609490706</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.2694918585488963</v>
+        <v>0.1040100130837445</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.3104028431539305</v>
+        <v>-0.1570934170671308</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.00964382152501031</v>
+        <v>0.1282904510621847</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>0.6076387519136688</v>
+        <v>0.7268191001269741</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>0.4001511864852461</v>
+        <v>0.4343344316467395</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>0.1140840475057985</v>
+        <v>0.01028326218427367</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>0.5521315087226242</v>
+        <v>0.4747547837272847</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.1005981744138538</v>
+        <v>-0.102523927926697</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-1.325261593544639</v>
+        <v>-1.323772085347997</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-1.107764330457464</v>
+        <v>-0.8649629461274984</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-0.7492997598361626</v>
+        <v>-0.4481502531455064</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-0.9091355793845111</v>
+        <v>-0.6781861486013128</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-1.093545465615385</v>
+        <v>-0.7773797610028694</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 14.25</t>
+          <t>X &gt; 14.27</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>759</v>
+        <v>764</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.6723431764241</v>
+        <v>-1.14314553485508</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-2.400820762175485</v>
+        <v>-1.907859115046627</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-2.788971044802274</v>
+        <v>-2.254641414084773</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-4.420560234848686</v>
+        <v>-3.884657101868349</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-4.887584303196491</v>
+        <v>-4.160215241967684</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-5.094318904500682</v>
+        <v>-4.262685008213452</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-3.897763651383151</v>
+        <v>-2.982540042495451</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.945003967527313</v>
+        <v>-1.212233507953357</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-2.034750381413126</v>
+        <v>-1.343707970513087</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.151498078446998</v>
+        <v>-1.491251035122829</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.6963360740803495</v>
+        <v>-0.05170084542122311</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.7126182859272916</v>
+        <v>-0.1985811137706008</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.310845969581315</v>
+        <v>-0.9243681728556155</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.7445232712247574</v>
+        <v>-0.3943921175571958</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.2743335631248485</v>
+        <v>-0.03893301046689857</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-0.5223285486443459</v>
+        <v>-0.3855407945006704</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.4468288629326835</v>
+        <v>-0.4894212062256784</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.02466034409246021</v>
+        <v>-0.1565583475858432</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-1.258044325486971</v>
+        <v>-1.295684014990258</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-2.78397848916849</v>
+        <v>-2.828835432956843</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-3.194772351469169</v>
+        <v>-2.932147491921242</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-2.743609090216879</v>
+        <v>-2.541965737406883</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-2.600886683400169</v>
+        <v>-2.354646206308608</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-2.808471242288789</v>
+        <v>-2.704137628480218</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 16.93</t>
+          <t>X &gt; 16.94</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.818343151466827</v>
+        <v>-1.580303337215781</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-2.153119949816642</v>
+        <v>-1.669224301648065</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-2.32331015574146</v>
+        <v>-1.825017304638543</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-4.779528834455199</v>
+        <v>-4.144264087434202</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-4.005969069284568</v>
+        <v>-3.320921128632442</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-5.086831726293362</v>
+        <v>-4.262888621535453</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-3.957037145524446</v>
+        <v>-3.174140178509148</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-3.125898352559609</v>
+        <v>-2.380159523016673</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-2.608975354480087</v>
+        <v>-1.781272999517803</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.589498003575216</v>
+        <v>-1.79239513837922</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.047609518307112</v>
+        <v>-0.264273153602204</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.484837527143377</v>
+        <v>-0.8548268506166607</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-2.132563777834683</v>
+        <v>-1.655747225524273</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.561249627339912</v>
+        <v>-1.119051930599447</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-1.175195002751067</v>
+        <v>-0.8592910848549948</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-1.282097605627015</v>
+        <v>-1.082916422393254</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.8456523232349511</v>
+        <v>-0.8728250915750877</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.6320216894765096</v>
+        <v>-0.6917374541935288</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-2.167722665240092</v>
+        <v>-2.204119811035198</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-3.573233543170154</v>
+        <v>-3.629739521007153</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-3.797308373556561</v>
+        <v>-3.480351456647291</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-3.076975991016617</v>
+        <v>-2.994148818017358</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-2.48402994095494</v>
+        <v>-2.277328212865172</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-3.037569200547651</v>
+        <v>-2.981426033234435</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 19.6</t>
+          <t>X &gt; 19.61</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.9485394211242735</v>
+        <v>-0.8708710029197562</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-1.283316219474088</v>
+        <v>-0.9259381439671444</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-2.336719883889693</v>
+        <v>-1.989792551202228</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-4.780443134101674</v>
+        <v>-4.299752001918847</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-4.154695145110473</v>
+        <v>-3.621111668735743</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-4.929267420551568</v>
+        <v>-4.227536841363609</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-3.393523796749605</v>
+        <v>-2.732542517718471</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-3.864042933810374</v>
+        <v>-3.22830265578358</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-2.861017290357211</v>
+        <v>-2.146175272817032</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-2.864702197162927</v>
+        <v>-2.178867989410413</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.475257939616391</v>
+        <v>0.1926036664153017</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.907853496910541</v>
+        <v>-1.229016455994937</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-2.454092486843585</v>
+        <v>-1.771389489476235</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-2.290555978674789</v>
+        <v>-1.637944161596373</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-1.489902774106241</v>
+        <v>-0.9842206808860041</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-1.361588861588864</v>
+        <v>-0.9954357460358096</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.7233052263655537</v>
+        <v>-0.5267970737913501</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.2489953510361644</v>
+        <v>-0.08716209498348348</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-2.73580667281454</v>
+        <v>-2.544455593028545</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-4.286412600298249</v>
+        <v>-4.23826609453446</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-4.635908575214089</v>
+        <v>-4.233191511945719</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-4.518704343572999</v>
+        <v>-4.39410418350765</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-3.47202885889017</v>
+        <v>-3.194446753678605</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-4.320061884314221</v>
+        <v>-4.20711650553384</v>
       </c>
     </row>
     <row r="29">
@@ -5070,79 +5070,79 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-2.089534464267281</v>
+        <v>-2.120825780243294</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.276339902235236</v>
+        <v>0.002935630498321018</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-1.953022435753105</v>
+        <v>-1.725692120682353</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-4.097957362117086</v>
+        <v>-3.739895267357873</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-3.479093896716869</v>
+        <v>-3.067586108879013</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-4.485445133053858</v>
+        <v>-3.858519801459124</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-3.348085941049213</v>
+        <v>-2.757867216535452</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-3.148970416828547</v>
+        <v>-2.588854010654963</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-2.152829296966345</v>
+        <v>-1.513057802392659</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.971091035055345</v>
+        <v>-1.361241999033801</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.503713970459053</v>
+        <v>0.09582713879328963</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.975780796341418</v>
+        <v>-1.365588938900764</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-3.576269832171285</v>
+        <v>-2.95441470564063</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-1.649377348236015</v>
+        <v>-1.069947345272794</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-1.212409250491639</v>
+        <v>-0.8042344285796545</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.9565075212557161</v>
+        <v>-0.7168640590490867</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.3710001978015427</v>
+        <v>-0.3468108214850005</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>0.003775405331708725</v>
+        <v>-0.0057612773574931</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-1.698798441561713</v>
+        <v>-1.687033647368118</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-3.430417859411428</v>
+        <v>-3.368181799465539</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-3.733155873900245</v>
+        <v>-3.461692651557172</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-4.288618142263779</v>
+        <v>-4.116607737369669</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-3.534527122827292</v>
+        <v>-3.397913869668486</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-4.569591989959434</v>
+        <v>-4.510171628803548</v>
       </c>
     </row>
     <row r="30">
@@ -5152,489 +5152,489 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.4876939602788113</v>
+        <v>-0.4082983699016367</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.2218701580280253</v>
+        <v>-0.05719028023237627</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-2.560790107959924</v>
+        <v>-2.20740677018366</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-2.673143526802058</v>
+        <v>-2.202794043618752</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-2.408333398748731</v>
+        <v>-1.881337258344949</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-3.722868714152852</v>
+        <v>-3.216940965779706</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-2.392715295941102</v>
+        <v>-1.922470739206453</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-2.971227040994485</v>
+        <v>-2.525898645301645</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-2.629439558779474</v>
+        <v>-2.099462272930964</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-2.501454333915063</v>
+        <v>-1.999991380090599</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-1.32649379085224</v>
+        <v>-0.8322339774265544</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-3.707345296402345</v>
+        <v>-3.198368170703837</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-5.731408264159356</v>
+        <v>-5.208782676214305</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-3.850385038503845</v>
+        <v>-3.367464498841443</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-2.835168228989353</v>
+        <v>-2.557081567293658</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-2.369999084500591</v>
+        <v>-2.294285011160568</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-1.899686614227313</v>
+        <v>-2.099657960199004</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.4939532999216141</v>
+        <v>-0.7400047519277706</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-2.997095151625686</v>
+        <v>-3.212109688961107</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-4.320823359784541</v>
+        <v>-4.490060557334964</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-4.863369527750571</v>
+        <v>-4.758997596029126</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-5.543445096410423</v>
+        <v>-5.568810220763922</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-4.966855580302997</v>
+        <v>-5.025774537880757</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-5.94903224440241</v>
+        <v>-6.08611712498459</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 27.63</t>
+          <t>X &gt; 27.62</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.7242322516473934</v>
+        <v>0.607570900347902</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>1.183106246948384</v>
+        <v>1.152177898636133</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-2.635865183034994</v>
+        <v>-2.474057705231743</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-1.364692218350747</v>
+        <v>-1.090175319059732</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-1.303657294072622</v>
+        <v>-0.9704765421630057</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-5.084945076229218</v>
+        <v>-4.766112106125398</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-3.475941379167189</v>
+        <v>-3.189652616381835</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-3.754152823920265</v>
+        <v>-3.494573059790454</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-2.125364054703965</v>
+        <v>-1.785616482122151</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-2.501454333915063</v>
+        <v>-2.186411060345449</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.6400931044515588</v>
+        <v>-0.3331483777569204</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-1.712493301550346</v>
+        <v>-1.400244166220318</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-4.026131558882646</v>
+        <v>-3.700907034659224</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-2.659908848027655</v>
+        <v>-2.368113428108153</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-1.49834683984713</v>
+        <v>-1.469240142009021</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-1.469696969696976</v>
+        <v>-1.698449957181445</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-1.603614106674449</v>
+        <v>-1.802330368906453</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.1084548104956298</v>
+        <v>-0.3541868060838667</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-3.492563429571291</v>
+        <v>-3.697036831902523</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-3.705717619603263</v>
+        <v>-3.877707303839578</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-4.248263787569293</v>
+        <v>-4.445151805220313</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-5.124109748978398</v>
+        <v>-5.310828161167699</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-5.249635036496343</v>
+        <v>-5.462450592885368</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-6.525467289719622</v>
+        <v>-6.81036033816298</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 30.3</t>
+          <t>X &gt; 30.29</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2.088319553234697</v>
+        <v>2.186539938556066</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.7118760882182187</v>
+        <v>0.8989664361855318</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-1.767809627479437</v>
+        <v>-1.397394332372713</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-3.001596980255513</v>
+        <v>-2.510629864514272</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-2.295720786136123</v>
+        <v>-1.744521337946942</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-8.358754600038736</v>
+        <v>-7.837587731948851</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-5.484869950595758</v>
+        <v>-4.986836410848241</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-5.763081395348834</v>
+        <v>-5.29175685425686</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-3.638260880100795</v>
+        <v>-3.080494611239416</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-2.327843222803956</v>
+        <v>-1.793212773125425</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-1.012116913975362</v>
+        <v>-0.4793110918544201</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-2.33253298409003</v>
+        <v>-1.797559712992388</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-5.018195050946147</v>
+        <v>-4.47495183044316</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-3.155940594059402</v>
+        <v>-2.639852558542934</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-1.94890064556666</v>
+        <v>-1.75950694042799</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-2.627591706539079</v>
+        <v>-2.760702921608328</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-2.761508843516552</v>
+        <v>-2.864583333333336</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-1.287402178916672</v>
+        <v>-1.434967438494937</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-4.755721324308134</v>
+        <v>-4.866338544682499</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-4.042559724866422</v>
+        <v>-4.130918766290179</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-4.585105892832452</v>
+        <v>-4.698363267670914</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-6.239899222662615</v>
+        <v>-6.336025789626198</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-6.491740299654246</v>
+        <v>-6.613224637681157</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-7.093888342351207</v>
+        <v>-7.296196965303949</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 32.98</t>
+          <t>X &gt; 32.97</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.506211710097446</v>
+        <v>1.931825826633926</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>1.90672902939469</v>
+        <v>2.415845998229322</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>3.409886450951937</v>
+        <v>4.080859925534831</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-1.714832274373165</v>
+        <v>-0.8911043170690149</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.1552596060207421</v>
+        <v>1.023118564729458</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-5.54012714905835</v>
+        <v>-4.659363887666615</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-1.900311127066345</v>
+        <v>-1.074883856103718</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-2.913816689466486</v>
+        <v>-2.109731306811604</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.6664471546106014</v>
+        <v>0.2079786247703126</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-2.909951065941208</v>
+        <v>-2.047926885047566</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-3.37118554142635</v>
+        <v>-2.505618877742499</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-3.649934944874346</v>
+        <v>-2.782200832213796</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-6.97897936467163</v>
+        <v>-6.086873971562376</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-2.788293535235873</v>
+        <v>-1.955545989199869</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-3.027046854602922</v>
+        <v>-2.637700371084925</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-5.395622895622893</v>
+        <v>-4.996104381462345</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-4.788799291859625</v>
+        <v>-4.370057785888079</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-4.152899254940067</v>
+        <v>-3.773014883750413</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-6.89997083697871</v>
+        <v>-7.208187693100982</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-5.972384286269936</v>
+        <v>-6.263674240742731</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-6.514930454235966</v>
+        <v>-6.101191734824198</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-9.553739378608036</v>
+        <v>-9.096062285976558</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-10.02000540686672</v>
+        <v>-9.582354807997454</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-10.09583766009</v>
+        <v>-9.744493802286918</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 35.65</t>
+          <t>X &gt; 35.64</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-3.640847113431967</v>
+        <v>-3.542626728110598</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-3.975623911781781</v>
+        <v>-3.788533563814468</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.2467343976777912</v>
+        <v>0.6171496927845155</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-3.296408301010231</v>
+        <v>-2.80544118526899</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.802010094312223</v>
+        <v>-0.2508106461230426</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-5.332025040290311</v>
+        <v>-4.810858172200426</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-1.386992592105194</v>
+        <v>-0.8889590523576771</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-2.608600263273367</v>
+        <v>-2.137275722181393</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.6803206285284702</v>
+        <v>-0.1225543596670917</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-2.396632530980057</v>
+        <v>-1.862002081301526</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-3.06596911523323</v>
+        <v>-2.533163293112288</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-4.288114745096316</v>
+        <v>-3.753141473998674</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-5.411276811952433</v>
+        <v>-4.868033591449446</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-1.858770782738645</v>
+        <v>-1.342682747222177</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-1.016464844020909</v>
+        <v>-1.081440902692144</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-2.32683982683983</v>
+        <v>-2.406929336702667</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-3.413137916198252</v>
+        <v>-3.454205974842772</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-2.565597667638485</v>
+        <v>-2.643693853589276</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-5.206849143857013</v>
+        <v>-5.259420305688785</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-6.924765238650885</v>
+        <v>-6.931626313459994</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-6.514930454235966</v>
+        <v>-6.555674588425632</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-10.40030022516888</v>
+        <v>-10.40442201604129</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-11.07820646506778</v>
+        <v>-11.10418375717801</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-11.15403871829105</v>
+        <v>-11.26632275146747</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 38.33</t>
+          <t>X &gt; 38.31</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-7.264035519229068</v>
+        <v>-7.828341013824883</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-9.048087679897726</v>
+        <v>-8.074247849528753</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-1.790454555015664</v>
+        <v>-0.7575133799917637</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-3.952683936777255</v>
+        <v>-2.77848700737141</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-4.288474409324529</v>
+        <v>-4.482616576042183</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-9.898609672502509</v>
+        <v>-10.03996868432981</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-4.8734569071175</v>
+        <v>-5.120764982276818</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-3.702392989551726</v>
+        <v>-3.997113997113999</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.6869202793194944</v>
+        <v>1.845100626855825</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>1.363279965601841</v>
+        <v>2.47762056020791</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>1.637339607763764</v>
+        <v>2.749855574812244</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-1.539960520321912</v>
+        <v>-0.3838692368019139</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-1.213847224859187</v>
+        <v>-0.07018992568124816</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-2.88420146362462</v>
+        <v>-1.746995415685795</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>1.700621990712982</v>
+        <v>1.856564488143441</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>0.8244206773618501</v>
+        <v>0.9892970783916724</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-2.250672930203855</v>
+        <v>-1.971726190476197</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>0.5856628365631948</v>
+        <v>0.7525325615050633</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.6690340178065881</v>
+        <v>-0.4615766399205867</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-4.893952913720923</v>
+        <v>-4.532704480575894</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-5.436499081686954</v>
+        <v>-5.100148981956629</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-9.924109748978402</v>
+        <v>-9.461025789626198</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-9.649635036496349</v>
+        <v>-9.217391304347821</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-11.19605552501374</v>
+        <v>-10.80810172720872</v>
       </c>
     </row>
   </sheetData>
@@ -5824,1887 +5824,1887 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -39.25</t>
+          <t>X &lt; -39.15</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-5.814760156910225</v>
+        <v>-4.971198156682028</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>2.546115218653</v>
+        <v>3.354323579042671</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.108096169622009</v>
+        <v>2.09962947715109</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-3.952683936777255</v>
+        <v>-2.77848700737141</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-2.839199047005678</v>
+        <v>-1.625473718899322</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>3.144868588367054</v>
+        <v>4.245745601384478</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>3.822195266795553</v>
+        <v>4.87923501772319</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1.497948016415876</v>
+        <v>1.717171717171716</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-2.872329507551783</v>
+        <v>-2.440613658858467</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.7040687130000336</v>
+        <v>-0.379522296934951</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-3.37118554142635</v>
+        <v>-2.964430139473471</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-5.120523180168455</v>
+        <v>-4.669583522516191</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.3613323058481015</v>
+        <v>-0.07018992568124816</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-4.994175888177054</v>
+        <v>-4.604138272828649</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-4.181730950463489</v>
+        <v>-3.857721226142274</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.6461675579322588</v>
+        <v>-0.4392743501797511</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>5.102268246266732</v>
+        <v>5.171130952380956</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>2.056251071857318</v>
+        <v>2.181103990076494</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.8015542174875208</v>
+        <v>0.9669947886508368</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>3.929576498043787</v>
+        <v>4.038724090852675</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>4.857618565371872</v>
+        <v>4.899851018043378</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>4.781772603962771</v>
+        <v>4.824688496088093</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>6.526835551738941</v>
+        <v>6.496894409937887</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>7.921591533809796</v>
+        <v>7.763326844219854</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -36.57</t>
+          <t>X &lt; -36.48</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-3.640847113431967</v>
+        <v>-3.542626728110598</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>2.842557906400039</v>
+        <v>3.989244213963303</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2.540902493732688</v>
+        <v>3.845661223182844</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-1.581142434800974</v>
+        <v>-0.08007430895871437</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-4.189660180075514</v>
+        <v>-2.577854671280271</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>3.951851460567319</v>
+        <v>5.356856712495592</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3.179902776676968</v>
+        <v>4.561774700262873</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1.295108259823571</v>
+        <v>2.034632034632033</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-2.111680420330686</v>
+        <v>-1.170772389017195</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-1.735170809010853</v>
+        <v>-0.8557127731254255</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-6.058812316274214</v>
+        <v>-5.027922202965527</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-6.33756171972221</v>
+        <v>-5.304504157436824</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-2.863022637153044</v>
+        <v>-1.97495183044316</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-5.382952088312273</v>
+        <v>-4.445408114098491</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-4.891670098536515</v>
+        <v>-4.016451384872433</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-1.998432601880879</v>
+        <v>-1.232925143830556</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>1.315926123210616</v>
+        <v>1.996527777777779</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0.06166013203311849</v>
+        <v>0.7525325615050633</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-2.021299061755208</v>
+        <v>-1.255227433571392</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>1.613822610281787</v>
+        <v>1.181581233709821</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>2.220701729672079</v>
+        <v>1.725247843440201</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>2.144855768262978</v>
+        <v>2.761196432596023</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>3.568755768101354</v>
+        <v>4.115942028985508</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>4.642348802234402</v>
+        <v>5.064914145807158</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -33.9</t>
+          <t>X &lt; -33.81</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-2.421334918310016</v>
+        <v>-2.342626728110595</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>2.121937063827978</v>
+        <v>1.411466436185535</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1.49692614487828</v>
+        <v>0.9567723342939587</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.842044134727054</v>
+        <v>-1.235629864514266</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-1.990842737355635</v>
+        <v>-2.311188004613605</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>3.074172229229553</v>
+        <v>2.645745601384476</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>3.11523167542051</v>
+        <v>2.650663589151755</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>2.510484178421656</v>
+        <v>2.016710887678627</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-1.546389295401347</v>
+        <v>-1.441775099044293</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-3.138977102585372</v>
+        <v>-3.050834724344938</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-7.782950247308698</v>
+        <v>-7.656648490228406</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-7.242027519609152</v>
+        <v>-7.120222314618402</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-4.266828930727563</v>
+        <v>-4.170073781662673</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-6.127252069469236</v>
+        <v>-6.044324103258383</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-4.326378973607177</v>
+        <v>-4.28745409489953</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-2.092647789369103</v>
+        <v>-2.100133815917275</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-2.226564926346576</v>
+        <v>-2.204014227642283</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-3.970749892462841</v>
+        <v>-3.962914592966477</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-2.935186380390974</v>
+        <v>-2.935444235739403</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-1.108996308127864</v>
+        <v>-1.094841530517819</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-1.651542476093894</v>
+        <v>-1.662286031898553</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.9077163063554536</v>
+        <v>-0.9244404237725448</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>0.1864305372741413</v>
+        <v>0.1322021915871403</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>3.389286808641032</v>
+        <v>3.222095717622871</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -31.22</t>
+          <t>X &lt; -31.14</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-1.201822723188066</v>
+        <v>-1.471620810950832</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>3.951205356510897</v>
+        <v>3.016200163996182</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1.90343020991893</v>
+        <v>1.169790085773236</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1.19047619047619</v>
+        <v>-0.01432808936634444</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.3648264771930272</v>
+        <v>-0.8816022057970372</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3.480676294270197</v>
+        <v>2.825627258189208</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2.098971512818871</v>
+        <v>0.8471132932937735</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>3.410614923669577</v>
+        <v>2.07431457431457</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.1233131939732743</v>
+        <v>-0.4389027948721562</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-1.266886432680501</v>
+        <v>-1.833756685301076</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-3.46196259298771</v>
+        <v>-3.956731251535061</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-2.506144095201137</v>
+        <v>-3.035708415587202</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-1.160170359588115</v>
+        <v>-1.156588556990066</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-3.23310108788656</v>
+        <v>-3.20122980405192</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-2.039392533615263</v>
+        <v>-2.086977000308231</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.2104377104377164</v>
+        <v>-0.3280681910694057</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.9616387980324603</v>
+        <v>-1.030750998003988</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-2.301047403088219</v>
+        <v>-2.361239893584752</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.8505881209293165</v>
+        <v>-0.9491728760198157</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>1.805393491507843</v>
+        <v>1.660623149877487</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>0.6455633729245278</v>
+        <v>0.4943762532871645</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>1.187001362132712</v>
+        <v>1.018016126541468</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>1.461476074614765</v>
+        <v>1.261650611819846</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>2.620211722626053</v>
+        <v>2.297116407949538</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -28.55</t>
+          <t>X &lt; -28.47</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-1.388594861179719</v>
+        <v>-1.098182283666148</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3.23158329542543</v>
+        <v>2.655910880629975</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3.595366048196233</v>
+        <v>3.178994556516173</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1.981511127852592</v>
+        <v>1.697703468819064</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-1.056982047397383</v>
+        <v>-1.244521337946942</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.382236390952251</v>
+        <v>1.134634490273363</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.1598372566114534</v>
+        <v>-0.1048919664037982</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1.497948016415876</v>
+        <v>1.181457431457432</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.9204578497977707</v>
+        <v>-1.120946778653462</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-1.693373525834261</v>
+        <v>-1.66652358393624</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-3.237495701854158</v>
+        <v>-3.1960903711337</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-2.607154196211241</v>
+        <v>-2.571771424704096</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-1.457588990340085</v>
+        <v>-1.434411289902613</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-2.587758775877582</v>
+        <v>-2.583546252236623</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-1.427720255276327</v>
+        <v>-1.463898832319884</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>0.07575757575757791</v>
+        <v>-0.001693912599321834</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.5127050157653485</v>
+        <v>-0.5560247747747766</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-1.526636628677444</v>
+        <v>-1.589809780837278</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-1.765290702298572</v>
+        <v>-1.825798004141951</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>0.6942823803967286</v>
+        <v>0.6410406931692805</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.3028092421147548</v>
+        <v>-0.3768542586619077</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>0.07589025102159752</v>
+        <v>-0.001566330166738794</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>0.8049104180491042</v>
+        <v>0.6925186055620856</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>1.638169073916742</v>
+        <v>1.431280512173529</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -25.87</t>
+          <t>X &lt; -25.8</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.2851424154453923</v>
+        <v>0.07579432452098445</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.729074074795399</v>
+        <v>1.145676962501319</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.304477844556359</v>
+        <v>2.193614439557102</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2.598235234509588</v>
+        <v>2.259106977590996</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.9201628827676842</v>
+        <v>0.3388119953863935</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>3.120551887657008</v>
+        <v>2.661587185542892</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.019744143363972</v>
+        <v>2.526571179910839</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.260277190509754</v>
+        <v>0.7616371854782358</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.5273374566773725</v>
+        <v>-0.9123744562006593</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.300253132713863</v>
+        <v>-1.522379439792083</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.688355652714101</v>
+        <v>-0.9168110918544201</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.2914293804864201</v>
+        <v>-0.336090928154043</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.4010779338290291</v>
+        <v>-0.113190403464337</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.959994648113458</v>
+        <v>-0.6958726254325711</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.2667865943426548</v>
+        <v>-0.04023436517714885</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.3480753480753478</v>
+        <v>-0.1478266674277222</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>1.207196704136372</v>
+        <v>1.420533723522858</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.4266803246395057</v>
+        <v>0.6187532972910219</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-0.03310397011183852</v>
+        <v>0.1643192033665599</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.8294175155318584</v>
+        <v>1.382250130030897</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>0.2868713475658282</v>
+        <v>0.8148056286501628</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>0.8867010618324116</v>
+        <v>1.408539427765113</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>1.161175774314465</v>
+        <v>1.652173913043491</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>1.761019196766867</v>
+        <v>2.158931239824255</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -23.2</t>
+          <t>X &lt; -23.13</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.3976038701887248</v>
+        <v>-0.3511373664084729</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>2.510862574704703</v>
+        <v>1.796572819164254</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.153924606754792</v>
+        <v>1.871665951315229</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>3.332862479203946</v>
+        <v>2.609050986549562</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.8349098444945113</v>
+        <v>-0.06012417482637744</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.373227381943238</v>
+        <v>1.579078934717813</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.601278698052887</v>
+        <v>0.7839969224850947</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.3979958404235262</v>
+        <v>-0.4371445547916153</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.03409421343413</v>
+        <v>-1.766542421784543</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.9917924981662765</v>
+        <v>-1.608400945168441</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.09748453529999068</v>
+        <v>-0.3768290613063527</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.09047426228679001</v>
+        <v>-0.2294290823617544</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.2174704132649836</v>
+        <v>-0.5335103890017194</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.7102884201463553</v>
+        <v>-0.8952726127434687</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.2814751959877881</v>
+        <v>-0.4934161545201334</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.2305665349143666</v>
+        <v>-0.474117555754674</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.7224728498472999</v>
+        <v>0.777015582655828</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.07415388515654797</v>
+        <v>0.1021260574400245</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.253432994788696</v>
+        <v>-0.2254171354684047</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>1.020369336918471</v>
+        <v>1.344182859726089</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>0.7495622993872146</v>
+        <v>1.047741068372446</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>1.217194598847684</v>
+        <v>1.514583966471363</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>2.035147572199307</v>
+        <v>2.029221161776839</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>1.959315318976032</v>
+        <v>1.867082167487375</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -20.52</t>
+          <t>X &lt; -20.46</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.597368852562397</v>
+        <v>-0.2517562397878805</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.676550001261695</v>
+        <v>1.413164949985955</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2.847226604404618</v>
+        <v>2.70624154873132</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>3.438620411048838</v>
+        <v>2.963096250135408</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.798482112414604</v>
+        <v>1.535620506024699</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2.420230907207639</v>
+        <v>2.028261592855692</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.430890918969453</v>
+        <v>1.233179580622974</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.1907584739322061</v>
+        <v>-0.01665001665002563</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.60723831823762</v>
+        <v>-1.694208030225852</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.164230896035178</v>
+        <v>-1.513795748804966</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.3268098964315058</v>
+        <v>-0.6910046402415233</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.2716336825766419</v>
+        <v>0.0163770686168121</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.4129318930514003</v>
+        <v>-0.4519633246960311</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.4147125238839635</v>
+        <v>-0.3585350639425045</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.8535575758504947</v>
+        <v>-0.8247067244452637</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.2591706539075034</v>
+        <v>-0.2634027056256016</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.2648069459571403</v>
+        <v>0.4966477681785406</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.2786302490921173</v>
+        <v>-0.06820177974763197</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-1.378528341852004</v>
+        <v>-0.9336531595133124</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>0.1241069418002354</v>
+        <v>0.7928123352216971</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.1991409805517605</v>
+        <v>0.4413505552232522</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>0.1636095492672069</v>
+        <v>0.5821707546502566</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>0.6573825073633017</v>
+        <v>0.8258052399286342</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>0.5815502541400264</v>
+        <v>0.6636662456391704</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -17.85</t>
+          <t>X &lt; -17.78</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.2394865692142787</v>
+        <v>-0.2762950698191418</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.786280850122985</v>
+        <v>0.4828232201051321</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.729214182044366</v>
+        <v>1.57318774467921</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2.887008461921361</v>
+        <v>2.418061410653515</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2.3811499621632</v>
+        <v>2.072005272697325</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2.398048121049698</v>
+        <v>1.989853345492222</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2.57784299659334</v>
+        <v>2.20487234336052</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.206841812842299</v>
+        <v>0.8185930614261068</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.006504077164166</v>
+        <v>0.7061044878596832</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.504633946145816</v>
+        <v>0.007231389311129988</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.050668963669011</v>
+        <v>0.5464657443037666</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.9434461468419286</v>
+        <v>0.5377897493732107</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.6779170130904504</v>
+        <v>0.441573353484408</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.2292682098398515</v>
+        <v>-0.3864511979987171</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.1417480123051433</v>
+        <v>-0.04819741661846422</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.7361349342481347</v>
+        <v>0.5131066022011979</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.9452709705125244</v>
+        <v>0.9194302721088334</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.1887292530342108</v>
+        <v>-0.2338619963180619</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-1.001997391835452</v>
+        <v>-0.8697399052267158</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>0.7285876977209185</v>
+        <v>1.045526811941116</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>0.357568116375802</v>
+        <v>0.6481503377712556</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>0.624775328208564</v>
+        <v>0.9131238702377402</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>0.7277234540696895</v>
+        <v>0.8166223010943483</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>0.99494437408827</v>
+        <v>0.9946193612266541</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -15.17</t>
+          <t>X &lt; -15.11</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.17952503185672</v>
+        <v>-1.181515616999484</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.298637691593747</v>
+        <v>0.7947997695188604</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.126441427372882</v>
+        <v>0.928994556516173</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.523192049280354</v>
+        <v>2.083424377488505</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2.046754600643062</v>
+        <v>1.609703360288897</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.53048590629038</v>
+        <v>1.428451319655053</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2.530094838136634</v>
+        <v>2.028069446892346</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.207563879686425</v>
+        <v>0.8273073915531981</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1.190482057752313</v>
+        <v>0.8960496778048679</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.9246025574883632</v>
+        <v>0.4608138375188418</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.140562500566652</v>
+        <v>0.5338667950085991</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.5785269781384912</v>
+        <v>0.05754328326229796</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.5885093872030538</v>
+        <v>0.2894644846060643</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.2257874512663776</v>
+        <v>-0.01661312192321418</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.5591455701164207</v>
+        <v>0.2871479891494744</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.5869602540990684</v>
+        <v>0.4259167967015287</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.8779722955918459</v>
+        <v>0.8854166666666643</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-0.3600128841500165</v>
+        <v>-0.233382931452681</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-0.7106937411860272</v>
+        <v>-0.4414559155745152</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>0.7509396041927658</v>
+        <v>1.181581233709821</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>0.4916795552069004</v>
+        <v>0.8958268731741512</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>0.8407627722680573</v>
+        <v>1.102354492063938</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>0.8319513657699389</v>
+        <v>0.9234537660747151</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>1.605977469487172</v>
+        <v>1.465540123897924</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -12.5</t>
+          <t>X &lt; -12.44</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>843</v>
+        <v>851</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.108456065139862</v>
+        <v>-1.10643183251895</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.3235515888071419</v>
+        <v>0.3878005429140714</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.123459512685464</v>
+        <v>1.286621347069797</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2.530646835998901</v>
+        <v>2.620184088974092</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>2.548213253910994</v>
+        <v>2.528858561160547</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2.568918355936098</v>
+        <v>2.520803876442756</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>2.220634771954415</v>
+        <v>1.958822097310261</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.776073450986857</v>
+        <v>1.488800321939173</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.9407578575717892</v>
+        <v>0.6334851395394026</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.7107626223777146</v>
+        <v>0.2553983379856817</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.9359109626557185</v>
+        <v>0.5952888300815644</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.1826657110463898</v>
+        <v>-0.08241219443044656</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.3643672266339237</v>
+        <v>0.2785692963174</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.4991602363083274</v>
+        <v>0.5696069009165257</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.4341367489294399</v>
+        <v>0.4749965848364113</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>1.028523670872431</v>
+        <v>1.153809416817055</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>1.250478420015952</v>
+        <v>1.519964257736</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.6337217144102141</v>
+        <v>-0.258043231679423</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-1.010950143687552</v>
+        <v>-0.6311250703385838</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.3621352866837952</v>
+        <v>0.876058319491257</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>0.5313328909597672</v>
+        <v>0.8961578839154569</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>0.2182390054699894</v>
+        <v>0.350960109316226</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>0.2554657938713802</v>
+        <v>0.2420681551116388</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>0.6541293888094444</v>
+        <v>0.4324556003051399</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -9.823</t>
+          <t>X &lt; -9.771</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1002</v>
+        <v>1007</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.6180522670494071</v>
+        <v>-0.8439024886601558</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.425763600606722</v>
+        <v>1.167305494085433</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.5823927180772159</v>
+        <v>0.4577546525650718</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.04981530913993</v>
+        <v>1.886494029291036</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.813132864342904</v>
+        <v>1.765977349717097</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.256324765040624</v>
+        <v>2.07825791665541</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.840415550893816</v>
+        <v>1.73468725779081</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.322529936659123</v>
+        <v>1.289869503097535</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.6263535477598978</v>
+        <v>0.5859250198541304</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.4091255686967159</v>
+        <v>0.143298107191093</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.3426728832994783</v>
+        <v>0.07658824807956677</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.0776677146289515</v>
+        <v>-0.3413943677660853</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.003224991065906124</v>
+        <v>-0.01066611615743795</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.1748977292938889</v>
+        <v>0.1965426748235046</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.3151576253261013</v>
+        <v>0.4081320863843274</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.7099437488659106</v>
+        <v>0.8701312392655609</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.6758270110900355</v>
+        <v>0.9648605594174171</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.7264188823519078</v>
+        <v>-0.3596819370053623</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-1.009529497435565</v>
+        <v>-0.5424391736133174</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.02428049385476783</v>
+        <v>0.4665861989531166</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>0.03197573338877646</v>
+        <v>0.3956660272645394</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.6426726232298989</v>
+        <v>-0.2753256903213384</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.6675991083526327</v>
+        <v>-0.4289106687966751</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.7434313615759081</v>
+        <v>-0.6903545290245745</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -7.148</t>
+          <t>X &lt; -7.1</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.1622217990983472</v>
+        <v>-0.2926267281105979</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.766203414286956</v>
+        <v>1.67435217430063</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.6634735521796813</v>
+        <v>0.6328992124241708</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>2.129899247741136</v>
+        <v>2.092022599980304</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2.297042555579445</v>
+        <v>2.282791928496756</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.946055243361705</v>
+        <v>1.986331375443051</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.062621653098617</v>
+        <v>1.909625063188614</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.32988078952512</v>
+        <v>1.234594780277931</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.6637611271882378</v>
+        <v>0.4884371560983851</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.7813739489132132</v>
+        <v>0.4960924325840637</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.1782965934663636</v>
+        <v>-0.107287282330617</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.5386376173714709</v>
+        <v>0.4211289609633155</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.3429629029605437</v>
+        <v>0.3651155096241823</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.3748351226353677</v>
+        <v>0.5035762535884842</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>0.2225940172976451</v>
+        <v>0.4111438599089894</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.7326639072001626</v>
+        <v>0.9724478787286515</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.8516978663441108</v>
+        <v>1.121305461948886</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.6022153501246308</v>
+        <v>-0.3595146162539962</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.8922261614431335</v>
+        <v>-0.5662823806836244</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.4524292553536924</v>
+        <v>-0.01471194236431472</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.4047561990364201</v>
+        <v>-0.07668045385457134</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-1.070821384728823</v>
+        <v>-0.9100569606455764</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-1.217931832449132</v>
+        <v>-1.003406468627517</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.9564959575105192</v>
+        <v>-0.9970534662868218</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -4.473</t>
+          <t>X &lt; -4.429</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1371</v>
+        <v>1374</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.09374316938166771</v>
+        <v>-0.1179691938640204</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.354325326796896</v>
+        <v>1.261971486690584</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.4964368071350123</v>
+        <v>0.4802380382650711</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.088776478772772</v>
+        <v>1.084023314676486</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.550665484108016</v>
+        <v>1.717156174706716</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.707162187576159</v>
+        <v>1.843430116579846</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.9046997661798386</v>
+        <v>0.8728214457773902</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.08720930232558999</v>
+        <v>0.102264884873577</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.04773057707048878</v>
+        <v>-0.01856869874243472</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.09437293440129224</v>
+        <v>-0.04777856896480159</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.09904638714846214</v>
+        <v>-0.1695344034012649</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.1170932367625213</v>
+        <v>-0.0412612633799867</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.1768383769855291</v>
+        <v>-0.02343667892801449</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.1126589683038404</v>
+        <v>0.3532333220975303</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.4725448690287308</v>
+        <v>-0.1833606522183757</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.3887341688216992</v>
+        <v>-0.05873785610614135</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.2308934648071954</v>
+        <v>0.1285025473071286</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-1.429826072348284</v>
+        <v>-1.096084614623024</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-1.359813611919947</v>
+        <v>-0.9544025912618253</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-1.245907262199921</v>
+        <v>-0.812596349987416</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.9131799071900204</v>
+        <v>-0.4338982021687272</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-1.42666263008708</v>
+        <v>-1.018522150616008</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-1.516885218844997</v>
+        <v>-1.138788684260483</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-1.37389909132429</v>
+        <v>-1.228147474765372</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -1.798</t>
+          <t>X &lt; -1.758</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1601</v>
+        <v>1606</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.9113185774518158</v>
+        <v>-1.164615610136543</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.2427383710966282</v>
+        <v>0.2905764485464744</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.07983934831199235</v>
+        <v>0.1824989885920303</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.9807897360697453</v>
+        <v>1.171300828555033</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.798482112414604</v>
+        <v>1.921629332847687</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.897356856352395</v>
+        <v>1.928521313899964</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.534719601643047</v>
+        <v>1.355189317608051</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.9195959537488676</v>
+        <v>0.9000855775049246</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.3124188625309969</v>
+        <v>0.3189855253217218</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.1984418239250161</v>
+        <v>0.1173721130029364</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.05227693060047045</v>
+        <v>-0.1339231697495933</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.1078630943000576</v>
+        <v>-0.064039812494876</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.1960976726689907</v>
+        <v>-0.0853023801216537</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.2923326040469192</v>
+        <v>-0.04800947012449797</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.7632099840244777</v>
+        <v>-0.4810978495188962</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.480932924753148</v>
+        <v>-0.2933928344352239</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.1154742814559668</v>
+        <v>0.1008587588210901</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-1.031800628223465</v>
+        <v>-0.8414898544351601</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-1.003175164902139</v>
+        <v>-0.7515606285347189</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.5666414647967812</v>
+        <v>-0.2256416803624077</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.7346557975568189</v>
+        <v>-0.3572206773844826</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-1.060189649103243</v>
+        <v>-0.8059822030757644</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-1.16024677182719</v>
+        <v>-0.8114137202880443</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.824780219138745</v>
+        <v>-0.7244867120868506</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.8769</t>
+          <t>X &lt; 0.9129</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1812</v>
+        <v>1818</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.7641347846648401</v>
+        <v>-0.9771245447044876</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.08308005213265801</v>
+        <v>0.007206468954514378</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.4832303249798784</v>
+        <v>0.4758980173540621</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>2.074170984637519</v>
+        <v>2.155512836415191</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2.593594984079758</v>
+        <v>2.622728844401713</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>2.318757755809692</v>
+        <v>2.264355344132149</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2.128454225228417</v>
+        <v>1.884398528910801</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.278046971885907</v>
+        <v>1.173140406017112</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.9667308690741194</v>
+        <v>0.8942860905149601</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.5010528513108952</v>
+        <v>0.3492607138008808</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.7522920434402067</v>
+        <v>0.5983736867771228</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.4506970434581774</v>
+        <v>0.4084740596600014</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.3520732327730798</v>
+        <v>0.3693705138791898</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.1309943563264895</v>
+        <v>0.2635284200167121</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.251514983150436</v>
+        <v>-0.05605534526847578</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-0.2635227690354469</v>
+        <v>-0.09981183249941949</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.1538280101943528</v>
+        <v>0.3463627612761186</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.5022806098341022</v>
+        <v>-0.3365763493860285</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-0.4517696037719574</v>
+        <v>-0.2321251233403601</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.09954341894174945</v>
+        <v>0.2024833239188482</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-0.3113288371834102</v>
+        <v>0.02007732638848836</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.6628087566961511</v>
+        <v>-0.4401236994171711</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.6314331611516124</v>
+        <v>-0.3615057157889652</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-0.6746946627880561</v>
+        <v>-0.5786502106284814</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 3.552</t>
+          <t>X &lt; 3.584</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2008</v>
+        <v>2014</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.3042183442772384</v>
+        <v>-0.5347371817595175</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.2281347430154455</v>
+        <v>0.1828527213359976</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.00446688579781096</v>
+        <v>-0.0580351681739586</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.7941950989524</v>
+        <v>1.796468900917823</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2.130975598212572</v>
+        <v>2.043357449931854</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.653220953314417</v>
+        <v>1.43803428156243</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.554514035522239</v>
+        <v>1.16579712030903</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.759736064968628</v>
+        <v>0.4935907459410629</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.4330273746551967</v>
+        <v>0.2538700752292229</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.2845988493575788</v>
+        <v>0.1299236805645165</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.3889325147380021</v>
+        <v>0.2325116699559473</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.05971157918611425</v>
+        <v>-0.1147283628023388</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.01032168777691567</v>
+        <v>-0.01066611615743795</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.03249454731648171</v>
+        <v>0.06796381862827872</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-0.5911848364435457</v>
+        <v>-0.4856117070615511</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-0.6432424694483316</v>
+        <v>-0.5201368838724818</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-0.1804415557047676</v>
+        <v>-0.1274929659053257</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-0.4344617722062196</v>
+        <v>-0.3100295040361445</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-0.2185703912818937</v>
+        <v>-0.04591484392115319</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.01800192291288738</v>
+        <v>0.2679764670762594</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-0.04726876269367608</v>
+        <v>0.1970562953876751</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.3718709430082541</v>
+        <v>-0.1760208243829027</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-0.3664095511802685</v>
+        <v>-0.1309960709813822</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.4127182857355578</v>
+        <v>-0.3427874982400638</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 6.227</t>
+          <t>X &lt; 6.255</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2174</v>
+        <v>2182</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.1245568117163671</v>
+        <v>-0.03625150042390146</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.1339651293141131</v>
+        <v>0.1066828370966917</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.1368367102699111</v>
+        <v>0.152761395369609</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.597351831444676</v>
+        <v>1.637511950351211</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.608028642304674</v>
+        <v>1.570563820203908</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.501339940979861</v>
+        <v>1.297320224844086</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.305032795399669</v>
+        <v>0.9849101644942237</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.5040889343215014</v>
+        <v>0.2494434655238678</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.2055988694792887</v>
+        <v>0.03784024555522336</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.2839616962305769</v>
+        <v>0.09078928448774803</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.217966763236916</v>
+        <v>0.06916024086896755</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.01169484465614801</v>
+        <v>-0.04388885105493756</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.02928576534112182</v>
+        <v>0.01222765673632864</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.2044720304981382</v>
+        <v>-0.07171238447055828</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.7708301054995275</v>
+        <v>-0.5894221558267034</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-0.6353692964523532</v>
+        <v>-0.4864132790785334</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-0.4021455431131784</v>
+        <v>-0.2694870913535041</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-0.6905566920926915</v>
+        <v>-0.5398597391365456</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-0.5393953854941671</v>
+        <v>-0.3712270261979285</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.07706748186222256</v>
+        <v>0.1183365041039579</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-0.133059377831124</v>
+        <v>0.100846173209014</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-0.3652862195666415</v>
+        <v>-0.2492934339891733</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-0.2473361859216396</v>
+        <v>-0.09731797712508694</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-0.3418426347058272</v>
+        <v>-0.3511159998288562</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 8.902</t>
+          <t>X &lt; 8.926</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2343</v>
+        <v>2355</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.1499195108797693</v>
+        <v>0.001677069357754135</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.3464099865233052</v>
+        <v>0.3271270524793266</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.5846614054441162</v>
+        <v>0.615556118077734</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.46458198496925</v>
+        <v>1.52533338009917</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.280506055894712</v>
+        <v>1.27393456512435</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.407091466741115</v>
+        <v>1.285914734576863</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.126727713947766</v>
+        <v>0.8533708649554796</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.4909011874888876</v>
+        <v>0.2765091211980746</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.004473572371225032</v>
+        <v>-0.1217555482984096</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.1487724234545453</v>
+        <v>0.03797634165644581</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.1904364234039733</v>
+        <v>-0.2586190014589391</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.2744656082034993</v>
+        <v>-0.2566967060685457</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.436458141623028</v>
+        <v>-0.3294895742938806</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.6149657111304947</v>
+        <v>-0.4257032161585457</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-0.9751098601371879</v>
+        <v>-0.7434840202242583</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-0.9341499284028032</v>
+        <v>-0.6667538770223445</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.8552105306846585</v>
+        <v>-0.6007829087048862</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-1.020209495333788</v>
+        <v>-0.7761298588771055</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.7367048867506725</v>
+        <v>-0.4767419417101024</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-0.2516059877327947</v>
+        <v>0.03508441842319598</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.2148452027440655</v>
+        <v>0.06211974719108326</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-0.5637685975924711</v>
+        <v>-0.3952083798597457</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-0.477280087690886</v>
+        <v>-0.278962429613216</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-0.485177063513909</v>
+        <v>-0.3986385788920614</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 11.58</t>
+          <t>X &lt; 11.6</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2489</v>
+        <v>2505</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.1255936996409659</v>
+        <v>0.007551772484404751</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.4103410004989243</v>
+        <v>0.4178156425347339</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.5097714787564342</v>
+        <v>0.5343824970569528</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.295589771540179</v>
+        <v>1.354044480203761</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.182323126039527</v>
+        <v>1.140858081997436</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.352374260451136</v>
+        <v>1.201230498045845</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1.002969641893252</v>
+        <v>0.7468862531676663</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.4681835926607505</v>
+        <v>0.2658704329348609</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.1729229796886216</v>
+        <v>0.05839151424142131</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.4229901105293763</v>
+        <v>0.3199772481059995</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.07986901481570641</v>
+        <v>-0.10159802932953</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.1353585778984012</v>
+        <v>-0.1163678139220039</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.1139766555383233</v>
+        <v>0.02717385043899867</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.23126110687992</v>
+        <v>-0.03817791739461285</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-0.448699276255347</v>
+        <v>-0.2181976065628106</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-0.3751456876456913</v>
+        <v>-0.1120596654231676</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.2686782092385513</v>
+        <v>0.007173153692612289</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.4298976962671688</v>
+        <v>-0.1656311111496294</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.190237848175947</v>
+        <v>0.08875127567678476</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>0.2610693840068379</v>
+        <v>0.5428586788196057</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>0.1838389411626409</v>
+        <v>0.454456093606538</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>0.0518035388578113</v>
+        <v>0.2196129329286904</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>0.1094011080819683</v>
+        <v>0.3035667794845125</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>0.1781084435065736</v>
+        <v>0.2611882642369636</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 14.25</t>
+          <t>X &lt; 14.27</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2651</v>
+        <v>2671</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.383862733067474</v>
+        <v>0.2348202387669645</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.5187581106901291</v>
+        <v>0.5301559373024318</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.5998452370141294</v>
+        <v>0.5992304348526076</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.032323559474627</v>
+        <v>1.070778481238342</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1.16790876017059</v>
+        <v>1.114529475818742</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.226454202161804</v>
+        <v>1.069011820623857</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.8888401807363167</v>
+        <v>0.6308202471152029</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.3320762623088243</v>
+        <v>0.1233550860416486</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.3576632030134874</v>
+        <v>0.2352248736430056</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.3952816206721295</v>
+        <v>0.2819521509472622</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.02270973622263739</v>
+        <v>-0.09661435421278952</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.01658686880180227</v>
+        <v>-0.01551561732721041</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.1607569360163694</v>
+        <v>0.2368861757873688</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.0003724977463832602</v>
+        <v>0.122862475114502</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.131803981933416</v>
+        <v>0.06136380405386177</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-0.06412887338395024</v>
+        <v>0.1584587550383816</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.08517919320566847</v>
+        <v>0.1516091039560621</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.2052557137699864</v>
+        <v>0.05616416015725889</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>0.1459907872961708</v>
+        <v>0.4203830327541738</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>0.5812880301142442</v>
+        <v>0.8596044459898593</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>0.7018492493560871</v>
+        <v>0.966064849139272</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>0.573440194481833</v>
+        <v>0.7785848430956293</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>0.5313604386167725</v>
+        <v>0.722706037471724</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>0.5913942719552168</v>
+        <v>0.7477628499961924</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 16.93</t>
+          <t>X &lt; 16.94</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2782</v>
+        <v>2802</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.3206089893517543</v>
+        <v>0.2680786954980547</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.3264110757226817</v>
+        <v>0.3604026063983028</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.3363570391872273</v>
+        <v>0.3664920930736599</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.8580403902339526</v>
+        <v>0.8938236486156086</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.6855753777904923</v>
+        <v>0.6738315197030431</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.9287260339738879</v>
+        <v>0.815347874111751</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.6779519378162604</v>
+        <v>0.5021733582458907</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.4919499105545668</v>
+        <v>0.3241368913010589</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.3751756505601449</v>
+        <v>0.2590968687937618</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.3747838806690211</v>
+        <v>0.2656717693117514</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.02507267532740798</v>
+        <v>-0.04630237609490706</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.1253300876883117</v>
+        <v>0.1245191719423744</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.2775038737850366</v>
+        <v>0.3473455470339957</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.1494556052952021</v>
+        <v>0.2625690938787173</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>0.0649946311280587</v>
+        <v>0.2427419017522752</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>0.0856992296576351</v>
+        <v>0.2907938709789875</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.01236276210649834</v>
+        <v>0.2080548128342272</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.05996126673666424</v>
+        <v>0.1676538168545676</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>0.2849751423698592</v>
+        <v>0.5460172645694996</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>0.6009586187312621</v>
+        <v>0.8676318937169611</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>0.6544292106353637</v>
+        <v>0.9066804355042564</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>0.4925569176882618</v>
+        <v>0.7244897294605011</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>0.3575514529035857</v>
+        <v>0.5613381745957966</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>0.4830158159597389</v>
+        <v>0.6490207363377323</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 19.6</t>
+          <t>X &lt; 19.61</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2892</v>
+        <v>2913</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.08383534451517249</v>
+        <v>0.07018854114638629</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.07657389041601448</v>
+        <v>0.149413930218941</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.2373360841889394</v>
+        <v>0.3114790191507097</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.6431624699163052</v>
+        <v>0.7273861709685008</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.5331436575444073</v>
+        <v>0.5734536336116491</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.6709336163757413</v>
+        <v>0.6131064754029154</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.4001704690808907</v>
+        <v>0.281264682047933</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.4858432433297679</v>
+        <v>0.3715716390810329</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.3062672323490006</v>
+        <v>0.24564744845528</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.3107587055707057</v>
+        <v>0.2553983379856817</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.1184652318074839</v>
+        <v>-0.1366013335324823</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.1395408730200174</v>
+        <v>0.1537388957429329</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.242921805310317</v>
+        <v>0.29061969590866</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.214749061113011</v>
+        <v>0.3022049560068751</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>0.07384714284280136</v>
+        <v>0.2225136075172145</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>0.04754440961337991</v>
+        <v>0.2219109872645717</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.06584246127947324</v>
+        <v>0.1040595727667366</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.1501387304404176</v>
+        <v>0.02575847854311775</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>0.2934220726723993</v>
+        <v>0.5006024704066689</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>0.5699729881315392</v>
+        <v>0.8042227431437823</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>0.6353286131215441</v>
+        <v>0.874946615650984</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>0.6149365537168308</v>
+        <v>0.8341011836064709</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>0.4264105908800815</v>
+        <v>0.6178301168674238</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>0.5788204004601809</v>
+        <v>0.7303220872192284</v>
       </c>
     </row>
     <row r="29">
@@ -7714,79 +7714,79 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2993</v>
+        <v>3014</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.207858925055092</v>
+        <v>0.212313983351855</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.1090457504807532</v>
+        <v>-0.01588117501710684</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.09764521979811036</v>
+        <v>0.1973787944126073</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.3662625348557498</v>
+        <v>0.480426845014243</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.2817985937088352</v>
+        <v>0.3553027605578976</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.4211556691536842</v>
+        <v>0.3988303918826617</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.2664598366382833</v>
+        <v>0.1833368564784834</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.2400986844649324</v>
+        <v>0.1612598179121676</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.1011353274840303</v>
+        <v>0.07684246493847269</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.07942937841622921</v>
+        <v>0.05938468310186096</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.1264921913832708</v>
+        <v>-0.1120082718500157</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.08015849110144302</v>
+        <v>0.1261661823244182</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.3088091684631351</v>
+        <v>0.3861592806679539</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.04091045559071915</v>
+        <v>0.1574514441034367</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.01743277534539089</v>
+        <v>0.1566495784336865</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.05616814597154018</v>
+        <v>0.1418955557170634</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.1369474400077735</v>
+        <v>0.05760209713024267</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.1886148638467446</v>
+        <v>0.01056502258488479</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>0.04712969918120535</v>
+        <v>0.2777966441843063</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>0.2872086399896574</v>
+        <v>0.5120419562819052</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>0.3319765328579365</v>
+        <v>0.594242833124845</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>0.4097800673821936</v>
+        <v>0.6185498071907816</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>0.3036047764628975</v>
+        <v>0.5172687288196798</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>0.4482714339689835</v>
+        <v>0.6071983012300066</v>
       </c>
     </row>
     <row r="30">
@@ -7796,489 +7796,489 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3079</v>
+        <v>3101</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.02794388762551847</v>
+        <v>-0.0363827319530543</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.119541304489104</v>
+        <v>-0.008905120508899245</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.1060471618470089</v>
+        <v>0.1954778773891093</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.08909562549199279</v>
+        <v>0.1977034688190642</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.06216035081478566</v>
+        <v>0.1324157145271485</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.2027693633430587</v>
+        <v>0.2111080131869087</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.06316657170546591</v>
+        <v>0.01145922598204407</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.1267302761674998</v>
+        <v>0.07770720222580252</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.08977383313766296</v>
+        <v>0.09550191096496974</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.07951550684125408</v>
+        <v>0.08841054094008882</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.04832241559348205</v>
+        <v>-0.006328170770800057</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.2095855548114542</v>
+        <v>0.2817569108293796</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.43301393005558</v>
+        <v>0.5354949712283243</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.2312476145573754</v>
+        <v>0.37059760222877</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>0.1238007860406327</v>
+        <v>0.3186331367672466</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>0.0703095090850212</v>
+        <v>0.2878813769759745</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>0.02049477213306972</v>
+        <v>0.2352718324214109</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.129848651662563</v>
+        <v>0.089300108188894</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>0.1377867649812288</v>
+        <v>0.387284643723298</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>0.2791023609351697</v>
+        <v>0.5243647388644632</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>0.3399256997765789</v>
+        <v>0.6205821077722078</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>0.4134429936376236</v>
+        <v>0.6421002174637138</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>0.350364963503651</v>
+        <v>0.5827376447173052</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>0.4564099431481949</v>
+        <v>0.6333687661805172</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 27.63</t>
+          <t>X &lt; 27.62</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3160</v>
+        <v>3182</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.1356600653338873</v>
+        <v>-0.1260900666441316</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.233485547001905</v>
+        <v>-0.1056371842888808</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.0440481370167376</v>
+        <v>0.1550239733823062</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.08506142330145394</v>
+        <v>0.04831766827772555</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.08844977574896973</v>
+        <v>0.008836987576337663</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.2107248290124772</v>
+        <v>0.2457456013844848</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.08648831712077509</v>
+        <v>0.06210466448780494</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.1098313330695646</v>
+        <v>0.08758179489885975</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.01967568207579262</v>
+        <v>0.0143664564281849</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.0136080172128672</v>
+        <v>0.04958551640315534</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.1355204144484006</v>
+        <v>-0.06704583363845984</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.04908135422672188</v>
+        <v>0.0499799446991176</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.139846392201008</v>
+        <v>0.2684973813743596</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.03219071907191307</v>
+        <v>0.195360474038516</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.05777076032683226</v>
+        <v>0.1584850683466925</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.06313131313130782</v>
+        <v>0.174250056448102</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.0519879620580852</v>
+        <v>0.1516443242395766</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.1696045262252497</v>
+        <v>0.03735062925913724</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>0.09669407437814925</v>
+        <v>0.3331698749388821</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>0.1127400289428664</v>
+        <v>0.3466785344003398</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>0.1580593234012895</v>
+        <v>0.4571508610574995</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>0.2276929075680911</v>
+        <v>0.4635973259516888</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>0.2364769533802757</v>
+        <v>0.4747230531765325</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>0.3378238495208805</v>
+        <v>0.519904019401686</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 30.3</t>
+          <t>X &lt; 30.29</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3220</v>
+        <v>3243</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.2005509085569273</v>
+        <v>-0.2052109289679152</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.1793276154854837</v>
+        <v>-0.06724719321722716</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.05705142021381704</v>
+        <v>0.04255664801944903</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.01171124832222148</v>
+        <v>0.1106159215721547</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.05213104254637813</v>
+        <v>0.03608360789405651</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.3067789805133785</v>
+        <v>0.3328354511238274</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.1396470509498329</v>
+        <v>0.1071053069431684</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.1574118019300741</v>
+        <v>0.1264120625887983</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.0310929192599616</v>
+        <v>0.05697469508347552</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.04339602808448006</v>
+        <v>-0.0154712420641232</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.1227831163894848</v>
+        <v>-0.06341223845556243</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.04312379936351363</v>
+        <v>0.04623829007981328</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.1214250584788559</v>
+        <v>0.2397582699461012</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.01165544063700708</v>
+        <v>0.1633291199077291</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.05788810477502437</v>
+        <v>0.1450902305437225</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.02112200067590919</v>
+        <v>0.2018470630117974</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.01266275867320132</v>
+        <v>0.177724358974352</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.09903137590170275</v>
+        <v>0.0938683571344896</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>0.1043357952349027</v>
+        <v>0.3266006999808866</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>0.06152803796496187</v>
+        <v>0.2822895798755098</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>0.09588762415890528</v>
+        <v>0.3800024131670483</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>0.1938294192400889</v>
+        <v>0.4157076464292757</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>0.20755217244497</v>
+        <v>0.4311906931860889</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>0.2434768096592634</v>
+        <v>0.4107873085165821</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 32.98</t>
+          <t>X &lt; 32.97</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3275</v>
+        <v>3298</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.1376624000561719</v>
+        <v>-0.155092852771844</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.2134879894516786</v>
+        <v>-0.1138347686337511</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.2998341595988165</v>
+        <v>-0.2074337518765788</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.1156680185068808</v>
+        <v>0.0002953916641459386</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.1915098336105601</v>
+        <v>-0.1077511640950704</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.04292624240758869</v>
+        <v>0.06601098136034977</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.1041915853572277</v>
+        <v>-0.1390800005918322</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.06114370537923008</v>
+        <v>-0.09505347465517389</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.1542675183900499</v>
+        <v>-0.1310970360306456</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.05822643448278342</v>
+        <v>-0.03445673447807707</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.04032779522472651</v>
+        <v>0.0135221408043904</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.02761565806041233</v>
+        <v>0.05635519133792144</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.1149860753856586</v>
+        <v>0.2281306718233935</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.05758493023479616</v>
+        <v>0.08838202428656672</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.04581348969111332</v>
+        <v>0.1497952972496677</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>0.04903589658387375</v>
+        <v>0.2451954449978473</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>0.02466133512933766</v>
+        <v>0.1895013867876969</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.001048531922016593</v>
+        <v>0.1653654912871403</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>0.1110951070140729</v>
+        <v>0.3372642406641617</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>0.07214148378190544</v>
+        <v>0.2972686958539725</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>0.09682468100909603</v>
+        <v>0.353609619333028</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>0.2223656858705425</v>
+        <v>0.4177620891616769</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>0.2404748536135415</v>
+        <v>0.4370494352702465</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>0.2439983591353325</v>
+        <v>0.3839627274391262</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 35.65</t>
+          <t>X &lt; 35.64</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3305</v>
+        <v>3329</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.04114867857284565</v>
+        <v>0.03732553919250137</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.006892703122730381</v>
+        <v>0.1058263287549082</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.1655226600608941</v>
+        <v>-0.05815303884038059</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.07966557231327442</v>
+        <v>0.05263528926298022</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.1578433661341165</v>
+        <v>-0.05694666650129676</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.01413288621172626</v>
+        <v>0.02704228498172512</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.1368008449047053</v>
+        <v>-0.1536400569928915</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.0966657326982272</v>
+        <v>-0.1128517720445998</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.1584539603458452</v>
+        <v>-0.1174762699316076</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.1004095278069599</v>
+        <v>-0.05902317296588677</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.08020680443863171</v>
+        <v>-0.008971474858611828</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.03998674363968746</v>
+        <v>0.06082225847323741</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.0006586443781415596</v>
+        <v>0.130836592710537</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.1120359471070813</v>
+        <v>0.0499497774858142</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.1365039278499793</v>
+        <v>0.07448796670202995</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.09752673124239664</v>
+        <v>0.1142596195963463</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.06255130474207959</v>
+        <v>0.1180305755395636</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.08900449337089356</v>
+        <v>0.09286239658752748</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.006158595734440553</v>
+        <v>0.2051471581769349</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>0.04756131663123853</v>
+        <v>0.2574888244689006</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>0.03686317736419653</v>
+        <v>0.3080142833495003</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>0.1605591352066611</v>
+        <v>0.370856527996132</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>0.1809759737879801</v>
+        <v>0.3922183052617925</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>0.183761152035288</v>
+        <v>0.338102624162353</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 38.33</t>
+          <t>X &lt; 38.31</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3342</v>
+        <v>3365</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.07496739310786893</v>
+        <v>0.08783372053166971</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.05351673644896238</v>
+        <v>0.1530076230765829</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.1191753819906438</v>
+        <v>-0.02255430480823861</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.1016044185179368</v>
+        <v>0.02168180461423219</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.09333983375516652</v>
+        <v>0.02852830744313906</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.0210955537768811</v>
+        <v>0.08375919878324112</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.07893635917229602</v>
+        <v>-0.073878102155156</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.1018697480446917</v>
+        <v>-0.09590133813736657</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.1923182897154163</v>
+        <v>-0.1582806072946497</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.203060560111453</v>
+        <v>-0.1681326212067162</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.2099031393778645</v>
+        <v>-0.145348688065198</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.1434175153555586</v>
+        <v>-0.04967574299929822</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.1454822426724789</v>
+        <v>-0.02195025066432521</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.1102079769301838</v>
+        <v>0.04348077479040313</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.2013563476232463</v>
+        <v>0.001199935683452225</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.1861148801447357</v>
+        <v>0.01686897284764655</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.1231721837123629</v>
+        <v>0.04911773428232635</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.1803783469352922</v>
+        <v>-0.006886008652159603</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.1558439793173392</v>
+        <v>0.04711348301285057</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.07081026754111264</v>
+        <v>0.1308243325522085</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.05753135109695506</v>
+        <v>0.2043980149894153</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>0.03402422231346947</v>
+        <v>0.2360339074334945</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>0.02730184654284074</v>
+        <v>0.2300240254204482</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>0.05909285390695374</v>
+        <v>0.2044221530714836</v>
       </c>
     </row>
   </sheetData>
